--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Newegg</t>
+          <t>PCComponentes</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Amazon (PC Section)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>PcComponentes</t>
+          <t>Coolmod</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Rity PC</t>
+          <t>PCity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -463,252 +463,320 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Website Description</t>
+          <t>Typography &amp; Readability</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minorista online líder en hardware y electrónica para PC, popular entre entusiastas y constructores de PC.</t>
+          <t>Utiliza fuentes sans-serif claras para nombres y descripciones de productos, asegurando excelente legibilidad. La jerarquía del texto está bien definida, haciendo que la información sea fácil de escanear y consumir.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>El gigante del comercio electrónico global que ofrece una vasta selección de componentes de PC y electrónica.</t>
+          <t>Emplea fuentes estándar de Amazon como Amazon Ember, ofreciendo buena legibilidad. Los tamaños de fuente varían apropiadamente para títulos y detalles, aunque la densidad de contenido puede ser alta.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tienda online española líder en informática y tecnología, conocida por precios competitivos y servicio al cliente.</t>
+          <t>Presenta una tipografía moderna y limpia. Los encabezados destacan y el texto principal es cómodamente legible, contribuyendo a una interfaz de usuario profesional y estéticamente atractiva.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Un sitio web de e-commerce especializado en componentes de PC, con una interfaz sencilla y enfocado en la exhibición de productos populares.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Utiliza una fuente sans-serif simple y limpia para títulos y descripciones, proporcionando una legibilidad decente. La tipografía general parece estándar y funcional, sin un estilo distintivo marcado.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Considerar diversificar los pesos o tamaños de fuente para crear una mejor jerarquía visual. Asegurar un espaciado consistente para mejorar el flujo del texto y la escaneabilidad, realzando el atractivo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Typography &amp; Readability</t>
+          <t>Colors &amp; Branding</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newegg utiliza una tipografía clara y legible, a menudo en tonos oscuros sobre fondos claros, lo que favorece una buena experiencia de lectura prolongada. Las jerarquías visuales están bien definidas mediante tamaños y pesos de fuente.</t>
+          <t>Los colores de marca dominantes son el rojo y el blanco, transmitiendo energía y fiabilidad. El esquema de color se aplica consistentemente en todos los elementos, reforzando el reconocimiento de marca.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon emplea una tipografía sencilla y universal (mayormente Arial o similar) para asegurar la máxima legibilidad en todos los dispositivos. El texto es claro y el tamaño de fuente es consistente para facilitar la lectura.</t>
+          <t>Utiliza la familiar paleta naranja, azul y blanco de Amazon, significando confianza y amplias ofertas. Los colores resaltan eficazmente las llamadas a la acción y la información crucial.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PcComponentes utiliza una tipografía moderna y clara, con un buen contraste que facilita la lectura de descripciones y especificaciones de productos. La coherencia tipográfica mejora la experiencia.</t>
+          <t>Predominantemente negro, blanco, con acentos azules o verdes. Esta paleta sugiere una imagen de marca moderna, tecnológica y premium. Los colores se usan estratégicamente para lograr impacto visual.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emplea una tipografía sans-serif clara y legible sobre fondos blancos, asegurando un buen contraste visual. Los títulos son prominentes, facilitando la jerarquía de la información presentada.</t>
+          <t>Presenta un encabezado azul brillante con texto blanco, ofreciendo un aspecto limpio y directo. Esta combinación de colores proporciona buen contraste, pero carece de una personalidad de marca distintiva.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Implementar una mayor variación tipográfica para destacar información crucial, como precios o promociones. Considerar el uso de fuentes web optimizadas para una carga más rápida.</t>
+          <t>Introducir un color de acento complementario para aumentar el interés visual y destacar elementos clave. Desarrollar una identidad de marca más allá del azul y blanco, reflejando su valor único.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colors &amp; Branding</t>
+          <t>Visual Elements</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Su paleta de colores predominante es el negro, gris y naranja, transmitiendo una imagen de tecnología, modernidad y fiabilidad. El naranja actúa como acento para llamadas a la acción importantes, reforzando la marca.</t>
+          <t>Abundancia de imágenes de productos de alta calidad, miniaturas detalladas y vídeos ocasionales. Los iconos son claros y funcionales, apoyando una rica experiencia visual para los compradores en línea.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>La marca se basa en el azul y naranja sobre fondos blancos, proyectando confianza, accesibilidad y eficiencia. El uso del naranja para acciones importantes es distintivo y efectivo en el branding.</t>
+          <t>Uso extensivo de imágenes de productos, fotos generadas por usuarios y reseñas en vídeo. Los elementos visuales son diversos e informativos, aunque la calidad puede variar entre los listados.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Su branding se caracteriza por el blanco, negro y rojo/naranja, transmitiendo energía, dinamismo y ofertas. El uso de colores vibrantes destaca promociones y elementos interactivos importantes.</t>
+          <t>Muestra fotografías de productos nítidas y profesionales, además de banners bien diseñados. Los iconos son modernos, y los elementos visuales contribuyen a una experiencia de usuario atractiva y de alta gama.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>La paleta se basa en un azul vibrante en la cabecera, con blanco y negro para el contenido principal. El branding es minimalista, con un logo de ratón sencillo y un nombre corto.</t>
+          <t>Muestra imágenes claras de productos en un carrusel, de apariencia estándar. Los iconos (búsqueda, usuario) son básicos. Se beneficiaría de imágenes de productos bien iluminadas y consistentes.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Podría introducir un color de acento secundario para elementos interactivos, haciendo el sitio más dinámico. Un uso más consistente del azul podría reforzar la identidad de marca.</t>
+          <t>Incorporar elementos visuales más diversos y de alta calidad, como gráficos explicativos o vídeos cortos. Asegurar que todas las imágenes mantengan un estilo y resolución consistentes para un aspecto profesional.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Visual Elements</t>
+          <t>Navigation &amp; UX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abundan las imágenes de productos de alta calidad, diagramas técnicos y videos, cruciales para informar al comprador de componentes. Los iconos son funcionales y ayudan a la navegación.</t>
+          <t>Navegación superior y lateral intuitiva con amplias opciones de filtrado. El viaje del usuario está optimizado para encontrar productos rápidamente, ofreciendo una experiencia de compra fluida y eficiente.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Muestra innumerables imágenes de productos desde múltiples ángulos y con zooms, así como videos explicativos. El diseño es funcional, priorizando el contenido sobre la estética elaborada.</t>
+          <t>Navegación integral con potente búsqueda y filtros. A pesar de su vastedad, la UX está refinada para el descubrimiento eficiente de productos, aunque puede ser abrumadora para usuarios nuevos.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Presenta imágenes de alta calidad de productos, banners de ofertas atractivos y maquetas de configuración de PC. El diseño visual es limpio y moderno, priorizando la información clave.</t>
+          <t>Estructura de navegación limpia y lógica. Los menús están bien organizados, y la experiencia de usuario general es fluida, haciendo que la navegación y compra sean sencillas y agradables.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Muestra imágenes de productos en cajas blancas uniformes, claras y funcionales. Los iconos son básicos y el diseño carece de elementos gráficos complejos o animaciones atractivas.</t>
+          <t>Navegación superior simple (Información, Arma tu PC, Comparar) y una barra de búsqueda prominente. La estructura parece básica pero funcional, sugiriendo facilidad de uso para su alcance limitado.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Integrar imágenes de productos con múltiples vistas o modelos 3D para una mejor apreciación. Añadir íconos más descriptivos o elementos gráficos para categorías.</t>
+          <t>Mejorar la navegación con categorías más detalladas o un mega-menú para una mejor descubribilidad. Mejorar la retroalimentación al usuario en elementos interactivos para guiar las acciones del usuario eficazmente.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Navigation &amp; UX</t>
+          <t>Organization &amp; Structure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ofrece una navegación robusta con múltiples filtros y categorías detalladas, optimizada para la búsqueda de componentes específicos. La experiencia de usuario se centra en la eficiencia y el acceso rápido a la información técnica.</t>
+          <t>Categorías altamente estructuradas, páginas de productos con especificaciones detalladas y secciones de reseñas. La información está agrupada lógicamente, facilitando la comparación y decisiones informadas.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Su navegación es extremadamente intuitiva, basada en una potente búsqueda y un sistema de categorías omnipresente. La UX está diseñada para la compra rápida y la gestión eficiente de grandes catálogos.</t>
+          <t>Amplios listados de productos con categorías jerárquicas, reseñas de clientes y artículos relacionados. La densidad de información es alta, pero la estructura permite una exploración detallada.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La navegación es lógica y bien estructurada, con un menú principal intuitivo y filtros eficaces. La experiencia de usuario se enfoca en la facilidad de búsqueda y configuración de productos.</t>
+          <t>Categorías de productos claras, páginas de productos bien estructuradas e información de soporte fácilmente accesible. El diseño del contenido es limpio, ayudando a los usuarios a encontrar detalles específicos.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>La navegación es directa con una barra de búsqueda y enlaces clave en la cabecera. La experiencia de usuario parece ser simple, aunque quizás limitada en opciones de filtrado.</t>
+          <t>El contenido se organiza en secciones principales como 'Aprende, Arma y Compara' y 'Componentes populares' en un flujo simple. La estructura actual es plana y directa.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Evaluar simplificar los menús de navegación para reducir la carga cognitiva del usuario y optimizar el flujo de búsqueda de productos. Añadir más opciones de filtrado inteligente.</t>
+          <t>Introducir una organización más jerárquica para componentes y guías para evitar la sobrecarga de contenido. Implementar divisores de sección claros o señales visuales para mejorar la escaneabilidad.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Organization &amp; Structure</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>El sitio está altamente estructurado por categorías de productos, con una organización lógica que facilita encontrar artículos específicos. Utiliza una arquitectura de información profunda pero bien indexada.</t>
+          <t>Generalmente sigue las mejores prácticas de accesibilidad, ofreciendo buen contraste y navegación con teclado. Realizan esfuerzos continuos para mejorar la experiencia para todos los usuarios.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La estructura de Amazon es masiva pero bien organizada con jerarquías claras de categorías y subcategorías. El sistema de listados de productos y páginas de detalle es altamente eficiente.</t>
+          <t>Busca una amplia accesibilidad, proporcionando funciones como compatibilidad con lectores de pantalla y navegación con teclado. Su gran base de usuarios impulsa mejoras continuas de accesibilidad.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Posee una organización clara por categorías y subcategorías de productos, permitiendo una exploración eficiente. La estructura de las fichas de producto es detallada y bien organizada.</t>
+          <t>Considera la accesibilidad en su diseño, ofreciendo ratios de contraste razonables y estados de enfoque claros. Se esfuerza por proporcionar una experiencia usable para diversos usuarios.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>La página principal está bien organizada con títulos claros y una cuadrícula de productos populares. La estructura es sencilla, priorizando la visibilidad de los artículos destacados.</t>
+          <t>El sitio web parece tener un buen contraste de color en el encabezado. Sin embargo, no se pueden discernir directamente detalles sobre texto alternativo o navegación con teclado desde la imagen.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revisar la estructura de las categorías de productos para asegurar una lógica intuitiva y evitar la confusión. La información de las fichas de producto podría ser más consistente y fácil de escanear.</t>
+          <t>Implementar texto alternativo completo para todas las imágenes y asegurar el soporte total de navegación por teclado. Revisar los ratios de contraste de color en todos los elementos para cumplir con WCAG.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aunque no se enfoca primariamente en esto en sus comunicaciones, las prácticas estándar de contraste y etiquetado suelen estar presentes, aunque podría mejorar en algunos aspectos para usuarios con discapacidades.</t>
+          <t>Ofrece búsqueda avanzada, filtros, herramientas de comparación de productos, un configurador de PC y reseñas de clientes. Las funcionalidades de e-commerce son robustas y de alto rendimiento.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Como plataforma global, Amazon suele incorporar características básicas de accesibilidad, como texto alternativo para imágenes y navegación por teclado, pero la variabilidad puede existir en el contenido generado por vendedores.</t>
+          <t>Proporciona una vasta gama de funcionalidades, incluyendo búsqueda avanzada, listas de deseos, compra con un clic, reseñas de clientes y recomendaciones personalizadas para los usuarios.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PcComponentes generalmente cumple con pautas de accesibilidad básicas, como buena legibilidad y navegación clara, pero como muchos sitios, podría beneficiarse de auditorías específicas para personas con diversas discapacidades.</t>
+          <t>Cuenta con un configurador de PC, especificaciones detalladas de productos, chat de soporte al cliente y procesos de pago eficientes. Las funcionalidades están diseñadas para entusiastas de PC.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El alto contraste entre el texto negro y el fondo blanco favorece la legibilidad. Sin embargo, no se aprecian características avanzadas de accesibilidad como texto alternativo específico.</t>
+          <t>Las funcionalidades clave incluyen una barra de búsqueda y, potencialmente, herramientas 'Arma tu PC' y 'Comparar'. La visualización de productos e información básica están presentes.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Implementar herramientas para ajustar el tamaño del texto y el contraste, y asegura la navegabilidad completa mediante teclado. Ofrece alternativas de texto para todos los elementos no textuales y subtítulos para videos.</t>
+          <t>Exponer y destacar claramente funcionalidades avanzadas como 'Arma tu PC' y 'Comparar'. Considerar añadir reseñas de usuarios, listas de deseos o filtros detallados para enriquecer la experiencia.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Functionality &amp; Interactivity</t>
+          <t>Interactivity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Presenta herramientas interactivas como filtros avanzados, constructores de PC y comparadores de productos. Los comentarios y valoraciones de usuarios son elementos interactivos clave para la toma de decisiones.</t>
+          <t>Incluye configuradores de productos interactivos, opciones de ordenar/filtrar, carrito de compras dinámico y sistemas de comentarios/valoración. El engagement es alto debido a los numerosos elementos interactivos.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ofrece funcionalidades como listas de deseos, comparaciones, reviews de usuarios, preguntas y respuestas, y un sofisticado sistema de recomendaciones personalizadas, fomentando la interacción.</t>
+          <t>Alta interactividad con carruseles de productos dinámicos, descripciones expandibles, preguntas y respuestas interactivas y un robusto sistema de reseñas que fomenta la participación del usuario.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Integra funcionalidades como configuradores de PC, comparadores de productos, un sistema de opiniones y un servicio de atención al cliente interactivo, enriqueciendo la experiencia de compra.</t>
+          <t>Los elementos interactivos incluyen filtros de productos, un configurador avanzado, efectos hover en productos y soporte por chat en vivo, mejorando la exploración y el engagement del usuario.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ofrece funcionalidad básica de búsqueda y navegación en el sitio. Faltan herramientas interactivas avanzadas como configuradores de PC o filtros detallados para refinar la búsqueda.</t>
+          <t>La interactividad visible es limitada: una barra de búsqueda, enlaces de navegación clicables y un carrusel de productos. La imagen sugiere una interacción básica en lugar de funciones avanzadas.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Podrías añadir más funcionalidades interactivas, como un configurador de productos más avanzado o herramientas de comparación visuales. Optimiza los tiempos de carga para todas las interacciones.</t>
+          <t>Introducir filtrado dinámico para listados de productos y estados interactivos al pasar el ratón sobre las tarjetas de productos. Implementar un sistema de calificación o comentarios para fomentar la participación comunitaria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SEO (Search Engine Optimization)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fuerte SEO con URLs bien estructuradas, títulos de productos descriptivos y contenido enriquecido. Parece altamente optimizado para palabras clave relevantes, logrando altas posiciones en búsquedas.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Aprovecha su autoridad de dominio y descripciones de productos extensas, contenido generado por usuarios y enlaces internos para un potente SEO. Posiciona bien para numerosas consultas.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Buenas prácticas de SEO con meta descripciones claras, palabras clave relevantes en el contenido y una estructura de sitio bien indexada. Se centra en palabras clave de nicho para entusiastas.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>No se puede evaluar directamente desde la imagen. Sin embargo, una estructura de sitio clara y títulos descriptivos ('Componentes populares') son señales iniciales positivas para el SEO.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Optimizar los títulos de página y meta descripciones con palabras clave relevantes. Asegurar que las imágenes tengan texto alternativo descriptivo e implementar una sección de blog para contenido SEO-friendly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Plataforma líder de e-commerce, reconocida por su extenso catálogo, precios competitivos y excelente servicio al cliente en el mercado de componentes de PC y tecnología en general.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ofrece una variedad de productos incomparable y eficiencia logística. Su robusta plataforma proporciona una experiencia de compra generalmente fiable, pese a la alta densidad de información.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Destaca por su enfoque especializado en hardware de PC de alto rendimiento, su excelente soporte al cliente y una selección de productos curada para entusiastas exigentes.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Presenta una interfaz limpia y funcional para la navegación y configuración de componentes de PC. Tiene un propósito claro pero actualmente carece de características avanzadas y branding distintivo.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>El sitio web tiene una base sólida para construir PCs. Se recomienda refinar el branding visual, enriquecer las funcionalidades interactivas y expandir el contenido para una experiencia más atractiva y competitiva.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PCComponentes</t>
+          <t>Newegg</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Amazon (PC Section)</t>
+          <t>Micro Center</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Coolmod</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PCity</t>
+          <t>Sitio Web de la Imagen</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,27 +468,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Utiliza fuentes sans-serif claras para nombres y descripciones de productos, asegurando excelente legibilidad. La jerarquía del texto está bien definida, haciendo que la información sea fácil de escanear y consumir.</t>
+          <t>Employs varied font sizes and weights for product details and reviews. Text is generally clear, but some dense pages can feel overwhelming.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Emplea fuentes estándar de Amazon como Amazon Ember, ofreciendo buena legibilidad. Los tamaños de fuente varían apropiadamente para títulos y detalles, aunque la densidad de contenido puede ser alta.</t>
+          <t>Features clean, modern typography that prioritizes clear product descriptions and specifications. Readability is consistently high across all content.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Presenta una tipografía moderna y limpia. Los encabezados destacan y el texto principal es cómodamente legible, contribuyendo a una interfaz de usuario profesional y estéticamente atractiva.</t>
+          <t>Uses a standardized, easily readable font for product titles and descriptions, maintaining consistency across its vast marketplace. Text can be small on some elements.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Utiliza una fuente sans-serif simple y limpia para títulos y descripciones, proporcionando una legibilidad decente. La tipografía general parece estándar y funcional, sin un estilo distintivo marcado.</t>
+          <t>Utilizes clear, legible fonts for titles and product names, contributing to good overall readability. Text contrast against backgrounds is effective.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Considerar diversificar los pesos o tamaños de fuente para crear una mejor jerarquía visual. Asegurar un espaciado consistente para mejorar el flujo del texto y la escaneabilidad, realzando el atractivo.</t>
+          <t>Consider introducing subtle font variations for emphasis without compromising clarity. Larger text for product descriptions or specifications could further improve user accessibility.</t>
         </is>
       </c>
     </row>
@@ -500,27 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Los colores de marca dominantes son el rojo y el blanco, transmitiendo energía y fiabilidad. El esquema de color se aplica consistentemente en todos los elementos, reforzando el reconocimiento de marca.</t>
+          <t>Recognizable black, red, and white color scheme, conveying a tech-focused, professional brand image. Consistent branding reinforces identity across sections.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Utiliza la familiar paleta naranja, azul y blanco de Amazon, significando confianza y amplias ofertas. Los colores resaltan eficazmente las llamadas a la acción y la información crucial.</t>
+          <t>Features a distinct red, black, and white palette, reflecting its retail presence and tech expertise. Branding is strong, highlighting categories effectively.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Predominantemente negro, blanco, con acentos azules o verdes. Esta paleta sugiere una imagen de marca moderna, tecnológica y premium. Los colores se usan estratégicamente para lograr impacto visual.</t>
+          <t>Employs its iconic orange and blue accents against a predominantly white background, establishing instant recognition. Branding is ubiquitous, focusing on trust.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Presenta un encabezado azul brillante con texto blanco, ofreciendo un aspecto limpio y directo. Esta combinación de colores proporciona buen contraste, pero carece de una personalidad de marca distintiva.</t>
+          <t>Adopts a clean blue and white color scheme, providing a fresh and simple aesthetic. The mouse-shaped logo offers a memorable, tech-centric brand identity.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Introducir un color de acento complementario para aumentar el interés visual y destacar elementos clave. Desarrollar una identidad de marca más allá del azul y blanco, reflejando su valor único.</t>
+          <t>While the current blue and white scheme is clean, exploring a secondary accent color could add depth. Ensure brand elements are consistently applied, perhaps with a more prominent logo presence.</t>
         </is>
       </c>
     </row>
@@ -532,27 +532,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abundancia de imágenes de productos de alta calidad, miniaturas detalladas y vídeos ocasionales. Los iconos son claros y funcionales, apoyando una rica experiencia visual para los compradores en línea.</t>
+          <t>Showcases high-quality product images, detailed specifications, and user-submitted photos. Videos and interactive elements enhance product understanding and engagement.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uso extensivo de imágenes de productos, fotos generadas por usuarios y reseñas en vídeo. Los elementos visuales son diversos e informativos, aunque la calidad puede variar entre los listados.</t>
+          <t>Provides excellent product photography, often with multiple angles and clear details. In-store pickup icons and comparison visuals are also well-integrated.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Muestra fotografías de productos nítidas y profesionales, además de banners bien diseñados. Los iconos son modernos, y los elementos visuales contribuyen a una experiencia de usuario atractiva y de alta gama.</t>
+          <t>Displays a wide array of product images, including customer-uploaded photos and videos. Visuals are crucial for comparison, though quality varies by seller.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Muestra imágenes claras de productos en un carrusel, de apariencia estándar. Los iconos (búsqueda, usuario) son básicos. Se beneficiaría de imágenes de productos bien iluminadas y consistentes.</t>
+          <t>Features clear product images for popular components, aiding quick identification. The overall layout is clean and uncluttered, focusing user attention on listed items.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Incorporar elementos visuales más diversos y de alta calidad, como gráficos explicativos o vídeos cortos. Asegurar que todas las imágenes mantengan un estilo y resolución consistentes para un aspecto profesional.</t>
+          <t>Consider increasing the size of product thumbnails and adding more visual details like multiple angles or zoom features. Implementing product comparison overlays could greatly enhance decision-making.</t>
         </is>
       </c>
     </row>
@@ -564,27 +564,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navegación superior y lateral intuitiva con amplias opciones de filtrado. El viaje del usuario está optimizado para encontrar productos rápidamente, ofreciendo una experiencia de compra fluida y eficiente.</t>
+          <t>Offers extensive categorization, advanced filters, and a robust search function, enabling precise product discovery. Navigation can be deep but is well-structured.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Navegación integral con potente búsqueda y filtros. A pesar de su vastedad, la UX está refinada para el descubrimiento eficiente de productos, aunque puede ser abrumadora para usuarios nuevos.</t>
+          <t>Features intuitive navigation with clear categories and an effective search bar. The distinction between online and in-store availability enhances user experience.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estructura de navegación limpia y lógica. Los menús están bien organizados, y la experiencia de usuario general es fluida, haciendo que la navegación y compra sean sencillas y agradables.</t>
+          <t>Known for its universal search bar and extensive filtering options, simplifying product discovery across diverse categories. Navigation is familiar and highly efficient.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Navegación superior simple (Información, Arma tu PC, Comparar) y una barra de búsqueda prominente. La estructura parece básica pero funcional, sugiriendo facilidad de uso para su alcance limitado.</t>
+          <t>Presents a clear top-level navigation with 'Información,' 'Arma tu PC,' and 'Comparar' options. The search bar is prominent, suggesting straightforward user interaction.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mejorar la navegación con categorías más detalladas o un mega-menú para una mejor descubribilidad. Mejorar la retroalimentación al usuario en elementos interactivos para guiar las acciones del usuario eficazmente.</t>
+          <t>Improving the visibility of sub-categories or adding hover-activated mega menus could streamline exploration. Implementing breadcrumbs or dynamic filtering would also greatly enhance navigation efficiency.</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Categorías altamente estructuradas, páginas de productos con especificaciones detalladas y secciones de reseñas. La información está agrupada lógicamente, facilitando la comparación y decisiones informadas.</t>
+          <t>Highly structured with detailed product pages, review sections, and comprehensive filtering. Information is logically grouped, supporting informed purchasing decisions.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amplios listados de productos con categorías jerárquicas, reseñas de clientes y artículos relacionados. La densidad de información es alta, pero la estructura permite una exploración detallada.</t>
+          <t>Well-organized product categories and dedicated sections for new arrivals or deals. Site structure supports both casual browsing and targeted searches effectively.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Categorías de productos claras, páginas de productos bien estructuradas e información de soporte fácilmente accesible. El diseño del contenido es limpio, ayudando a los usuarios a encontrar detalles específicos.</t>
+          <t>Employs a highly scalable structure with extensive product categories, subcategories, and detailed listing pages. Information is organized to handle millions of products efficiently.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El contenido se organiza en secciones principales como 'Aprende, Arma y Compara' y 'Componentes populares' en un flujo simple. La estructura actual es plana y directa.</t>
+          <t>Displays a clear 'Componentes populares' section with a consistent grid layout. The overall structure appears logical, separating main actions like 'Arma tu PC' clearly.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Introducir una organización más jerárquica para componentes y guías para evitar la sobrecarga de contenido. Implementar divisores de sección claros o señales visuales para mejorar la escaneabilidad.</t>
+          <t>Introducing more detailed product categories and subcategories would improve discoverability. Structuring product information with clear headings and bullet points on individual pages would enhance clarity.</t>
         </is>
       </c>
     </row>
@@ -628,27 +628,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Generalmente sigue las mejores prácticas de accesibilidad, ofreciendo buen contraste y navegación con teclado. Realizan esfuerzos continuos para mejorar la experiencia para todos los usuarios.</t>
+          <t>Generally good, with keyboard navigation support and clear alt-text for images. Efforts are made to meet WCAG standards, though complex layouts pose challenges.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Busca una amplia accesibilidad, proporcionando funciones como compatibilidad con lectores de pantalla y navegación con teclado. Su gran base de usuarios impulsa mejoras continuas de accesibilidad.</t>
+          <t>Strives for good accessibility with clear form labels and sufficient color contrast. Its focus on customer service extends to ensuring a usable online experience.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Considera la accesibilidad en su diseño, ofreciendo ratios de contraste razonables y estados de enfoque claros. Se esfuerza por proporcionar una experiencia usable para diversos usuarios.</t>
+          <t>Benefits from extensive resources dedicated to accessibility, aiming for compliance with WCAG standards. Features like screen reader support are well-implemented.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El sitio web parece tener un buen contraste de color en el encabezado. Sin embargo, no se pueden discernir directamente detalles sobre texto alternativo o navegación con teclado desde la imagen.</t>
+          <t>Features high color contrast between text and background, ensuring good readability. The layout appears simple and straightforward, potentially aiding keyboard navigation for all users.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Implementar texto alternativo completo para todas las imágenes y asegurar el soporte total de navegación por teclado. Revisar los ratios de contraste de color en todos los elementos para cumplir con WCAG.</t>
+          <t>Enhancing alt-text for all images and interactive elements would improve screen reader compatibility. Ensuring all form inputs have proper labels and focus indicators would further boost accessibility.</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ofrece búsqueda avanzada, filtros, herramientas de comparación de productos, un configurador de PC y reseñas de clientes. Las funcionalidades de e-commerce son robustas y de alto rendimiento.</t>
+          <t>Offers robust search, filtering, comparison tools, and a comprehensive checkout process. The PC builder tool is a standout feature for enthusiasts.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Proporciona una vasta gama de funcionalidades, incluyendo búsqueda avanzada, listas de deseos, compra con un clic, reseñas de clientes y recomendaciones personalizadas para los usuarios.</t>
+          <t>Provides accurate stock availability (online/in-store), reliable checkout, and effective product filtering. Its custom PC configurator is highly valued by users.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cuenta con un configurador de PC, especificaciones detalladas de productos, chat de soporte al cliente y procesos de pago eficientes. Las funcionalidades están diseñadas para entusiastas de PC.</t>
+          <t>Features a highly optimized shopping cart, one-click ordering, and robust customer support. Product reviews, Q&amp;A, and recommendation engines are key functionalities.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Las funcionalidades clave incluyen una barra de búsqueda y, potencialmente, herramientas 'Arma tu PC' y 'Comparar'. La visualización de productos e información básica están presentes.</t>
+          <t>Includes a visible search bar and main navigation points, suggesting core functionality like product searching and information access. Advanced tools are implied.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Exponer y destacar claramente funcionalidades avanzadas como 'Arma tu PC' y 'Comparar'. Considerar añadir reseñas de usuarios, listas de deseos o filtros detallados para enriquecer la experiencia.</t>
+          <t>Ensure all promised functionalities like 'Arma tu PC' and 'Comparar' are fully realized and highly intuitive. Implementing detailed product filtering options would significantly enhance user control.</t>
         </is>
       </c>
     </row>
@@ -692,27 +692,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Incluye configuradores de productos interactivos, opciones de ordenar/filtrar, carrito de compras dinámico y sistemas de comentarios/valoración. El engagement es alto debido a los numerosos elementos interactivos.</t>
+          <t>Engages users with product reviews, Q&amp;A sections, wishlists, and a robust community forum. Dynamic product displays and interactive configurators are present.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alta interactividad con carruseles de productos dinámicos, descripciones expandibles, preguntas y respuestas interactivas y un robusto sistema de reseñas que fomenta la participación del usuario.</t>
+          <t>Encourages interaction through customer reviews, in-store pickup options, and personalized recommendations. Live chat support offers direct engagement.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Los elementos interactivos incluyen filtros de productos, un configurador avanzado, efectos hover en productos y soporte por chat en vivo, mejorando la exploración y el engagement del usuario.</t>
+          <t>Highly interactive with user reviews, ratings, Q&amp;A, and personalized recommendations. Its seamless purchase flow and wishlists foster strong engagement.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>La interactividad visible es limitada: una barra de búsqueda, enlaces de navegación clicables y un carrusel de productos. La imagen sugiere una interacción básica en lugar de funciones avanzadas.</t>
+          <t>Displays popular components in an engaging grid, and implied features suggest interactive tools. Clear clickable elements guide user actions effectively.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Introducir filtrado dinámico para listados de productos y estados interactivos al pasar el ratón sobre las tarjetas de productos. Implementar un sistema de calificación o comentarios para fomentar la participación comunitaria.</t>
+          <t>Adding interactive elements like hover-over product details or quick-view options could enrich engagement. Incorporating customer reviews or a basic Q&amp;A section would foster community and trust.</t>
         </is>
       </c>
     </row>
@@ -724,27 +724,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fuerte SEO con URLs bien estructuradas, títulos de productos descriptivos y contenido enriquecido. Parece altamente optimizado para palabras clave relevantes, logrando altas posiciones en búsquedas.</t>
+          <t>Benefits from high domain authority, relevant keywords in product titles/descriptions, and a vast content library. Structured data markup is likely used.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aprovecha su autoridad de dominio y descripciones de productos extensas, contenido generado por usuarios y enlaces internos para un potente SEO. Posiciona bien para numerosas consultas.</t>
+          <t>Leverages local SEO for its physical stores and optimizes product pages for specific component searches. Blog content and guides contribute to organic visibility.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Buenas prácticas de SEO con meta descripciones claras, palabras clave relevantes en el contenido y una estructura de sitio bien indexada. Se centra en palabras clave de nicho para entusiastas.</t>
+          <t>Dominates search results due to its massive product catalog, high authority, and user-generated content (reviews). Product-specific pages are highly optimized.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>No se puede evaluar directamente desde la imagen. Sin embargo, una estructura de sitio clara y títulos descriptivos ('Componentes populares') son señales iniciales positivas para el SEO.</t>
+          <t>While content is minimal, proper use of titles, descriptions, and structured URLs would be crucial. Focus on long-tail keywords relevant to PC components.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Optimizar los títulos de página y meta descripciones con palabras clave relevantes. Asegurar que las imágenes tengan texto alternativo descriptivo e implementar una sección de blog para contenido SEO-friendly.</t>
+          <t>Implement descriptive page titles, meta descriptions, and clean URLs for every product. Utilizing structured data markup (Schema.org) for products would improve search engine visibility and rich snippets.</t>
         </is>
       </c>
     </row>
@@ -756,27 +756,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plataforma líder de e-commerce, reconocida por su extenso catálogo, precios competitivos y excelente servicio al cliente en el mercado de componentes de PC y tecnología en general.</t>
+          <t>Newegg remains a premier destination for PC hardware, praised for its vast selection, competitive pricing, and comprehensive feature set, catering to enthusiasts.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ofrece una variedad de productos incomparable y eficiencia logística. Su robusta plataforma proporciona una experiencia de compra generalmente fiable, pese a la alta densidad de información.</t>
+          <t>Micro Center offers a unique blend of online convenience and invaluable in-store expertise, making it a strong choice for builders needing immediate support.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Destaca por su enfoque especializado en hardware de PC de alto rendimiento, su excelente soporte al cliente y una selección de productos curada para entusiastas exigentes.</t>
+          <t>Amazon provides unparalleled convenience and selection across a broad spectrum of PC components, leveraging its extensive logistics and trusted marketplace for a diverse audience.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Presenta una interfaz limpia y funcional para la navegación y configuración de componentes de PC. Tiene un propósito claro pero actualmente carece de características avanzadas y branding distintivo.</t>
+          <t>The site presents a clean, user-friendly interface with clear goals for PC enthusiasts. It establishes a solid foundation for guiding users through component selection.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El sitio web tiene una base sólida para construir PCs. Se recomienda refinar el branding visual, enriquecer las funcionalidades interactivas y expandir el contenido para una experiencia más atractiva y competitiva.</t>
+          <t>The site has a good foundational design, but expanding content, visual details, and advanced interactive tools would elevate the user experience significantly. Focus on detailed product information and community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Overall Conclusion</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Newegg stands out with its extensive inventory, specialized focus on PC components, and strong community support, making it a go-to for enthusiasts and builders.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Micro Center excels in customer service, offering a valuable blend of in-store expertise and online convenience, particularly for local pick-ups and bundles.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Amazon provides unmatched accessibility and a vast product range, favored for its swift delivery, competitive pricing, and robust customer review system across various sellers.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>The Image Site, 'Rity', offers a clean, intuitive platform for PC enthusiasts to learn, build, and compare. Its direct approach simplifies navigation and component display.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>To elevate the user experience, the site should prioritize richer content, advanced filtering, and interactive tools beyond basic browsing. Enhancing product imagery and fostering community engagement would be beneficial additions.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>PcComponentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Newegg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Micro Center</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sitio Web de la Imagen</t>
+          <t>PCPartPicker</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,29 +468,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Employs varied font sizes and weights for product details and reviews. Text is generally clear, but some dense pages can feel overwhelming.</t>
+          <t>Utiliza tipografías Sans-serif claras que garantizan una excelente legibilidad en todas las secciones. El tamaño y espaciado favorecen una lectura cómoda y eficiente.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Features clean, modern typography that prioritizes clear product descriptions and specifications. Readability is consistently high across all content.</t>
+          <t>Presenta tipografías estándar y un diseño funcional que prioriza la información. La legibilidad es alta, aunque el volumen de texto puede resultar denso en ocasiones.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Uses a standardized, easily readable font for product titles and descriptions, maintaining consistency across its vast marketplace. Text can be small on some elements.</t>
+          <t>Emplea fuentes limpias y tamaños adecuados para asegurar una lectura fluida. La jerarquía visual de los textos ayuda a identificar rápidamente la información clave.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Utilizes clear, legible fonts for titles and product names, contributing to good overall readability. Text contrast against backgrounds is effective.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Consider introducing subtle font variations for emphasis without compromising clarity. Larger text for product descriptions or specifications could further improve user accessibility.</t>
-        </is>
-      </c>
+          <t>La tipografía es funcional y clara, aunque en ocasiones la uniformidad de tamaño puede dificultar la jerarquía visual de contenidos importantes.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,29 +496,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Recognizable black, red, and white color scheme, conveying a tech-focused, professional brand image. Consistent branding reinforces identity across sections.</t>
+          <t>Su vibrante paleta de colores corporativos (naranja y blanco/gris) es consistente, creando una identidad de marca moderna y fácilmente reconocible en todo el sitio.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Features a distinct red, black, and white palette, reflecting its retail presence and tech expertise. Branding is strong, highlighting categories effectively.</t>
+          <t>Utiliza una paleta de colores simple y reconocible (azul, naranja, blanco). El branding se centra en la familiaridad y confianza, con un logo omnipresente.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Employs its iconic orange and blue accents against a predominantly white background, establishing instant recognition. Branding is ubiquitous, focusing on trust.</t>
+          <t>Predominan los tonos azules y grises, que transmiten profesionalidad y tecnología. El branding es sutil pero consistente, reforzando su imagen en el sector.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adopts a clean blue and white color scheme, providing a fresh and simple aesthetic. The mouse-shaped logo offers a memorable, tech-centric brand identity.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>While the current blue and white scheme is clean, exploring a secondary accent color could add depth. Ensure brand elements are consistently applied, perhaps with a more prominent logo presence.</t>
-        </is>
-      </c>
+          <t>La interfaz usa colores básicos (azul, blanco, negro) de forma consistente. El branding es funcional, centrado en la herramienta más que en una estética llamativa.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,29 +524,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Showcases high-quality product images, detailed specifications, and user-submitted photos. Videos and interactive elements enhance product understanding and engagement.</t>
+          <t>Destaca por imágenes de producto de alta resolución y vídeos descriptivos. Los iconos son intuitivos y complementan la información textual, mejorando la experiencia de compra.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Provides excellent product photography, often with multiple angles and clear details. In-store pickup icons and comparison visuals are also well-integrated.</t>
+          <t>Abundantes imágenes de productos y vistas de 360 grados. Los elementos visuales son informativos y funcionales, aunque el diseño general puede parecer menos moderno.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Displays a wide array of product images, including customer-uploaded photos and videos. Visuals are crucial for comparison, though quality varies by seller.</t>
+          <t>Ofrece imágenes de productos detalladas y galerías interactivas. Los elementos gráficos son limpios y contribuyen a una presentación profesional del hardware.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Features clear product images for popular components, aiding quick identification. The overall layout is clean and uncluttered, focusing user attention on listed items.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Consider increasing the size of product thumbnails and adding more visual details like multiple angles or zoom features. Implementing product comparison overlays could greatly enhance decision-making.</t>
-        </is>
-      </c>
+          <t>Los elementos visuales son principalmente imágenes de productos, esquemas y gráficos para compatibilidad. Son funcionales, pero la estética es secundaria a la claridad informativa.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,29 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Offers extensive categorization, advanced filters, and a robust search function, enabling precise product discovery. Navigation can be deep but is well-structured.</t>
+          <t>Navegación intuitiva con menús desplegables claros y un buscador eficiente. La experiencia de usuario es fluida, facilitando la búsqueda y compra de componentes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Features intuitive navigation with clear categories and an effective search bar. The distinction between online and in-store availability enhances user experience.</t>
+          <t>La navegación es amplia y familiar, aunque a veces saturada. La UX se enfoca en la eficiencia del proceso de compra, con un flujo bien establecido y conocido.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Known for its universal search bar and extensive filtering options, simplifying product discovery across diverse categories. Navigation is familiar and highly efficient.</t>
+          <t>Presenta una navegación lógica y estructurada, con categorías bien definidas. La UX está diseñada para exploradores de tecnología, con filtros avanzados y fácil acceso a comparativas.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Presents a clear top-level navigation with 'Información,' 'Arma tu PC,' and 'Comparar' options. The search bar is prominent, suggesting straightforward user interaction.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Improving the visibility of sub-categories or adding hover-activated mega menus could streamline exploration. Implementing breadcrumbs or dynamic filtering would also greatly enhance navigation efficiency.</t>
-        </is>
-      </c>
+          <t>Navegación clara y orientada a la función, facilitando la búsqueda y compatibilidad de componentes. La UX es altamente funcional, ideal para construir PCs paso a paso.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,29 +580,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Highly structured with detailed product pages, review sections, and comprehensive filtering. Information is logically grouped, supporting informed purchasing decisions.</t>
+          <t>Contenido bien jerarquizado y organizado por categorías y subcategorías claras. La estructura facilita la exploración y búsqueda de productos específicos.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Well-organized product categories and dedicated sections for new arrivals or deals. Site structure supports both casual browsing and targeted searches effectively.</t>
+          <t>Organización de contenido vasta y compleja, pero con una estructura de categorías coherente. Permite una buena visibilidad de productos, a pesar de la enorme oferta.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Employs a highly scalable structure with extensive product categories, subcategories, and detailed listing pages. Information is organized to handle millions of products efficiently.</t>
+          <t>Estructura lógica y bien definida, optimizada para el hardware. Las fichas de producto son detalladas, y las guías de compra están bien integradas.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Displays a clear 'Componentes populares' section with a consistent grid layout. The overall structure appears logical, separating main actions like 'Arma tu PC' clearly.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Introducing more detailed product categories and subcategories would improve discoverability. Structuring product information with clear headings and bullet points on individual pages would enhance clarity.</t>
-        </is>
-      </c>
+          <t>La estructura se centra en la compatibilidad de componentes, con listas y filtros. Es muy organizada para su propósito específico de montaje de PCs.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -628,29 +608,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Generally good, with keyboard navigation support and clear alt-text for images. Efforts are made to meet WCAG standards, though complex layouts pose challenges.</t>
+          <t>Cumple con estándares básicos de accesibilidad, aunque siempre hay margen de mejora. Se percibe un esfuerzo por hacer el sitio usable para diversos usuarios.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Strives for good accessibility with clear form labels and sufficient color contrast. Its focus on customer service extends to ensuring a usable online experience.</t>
+          <t>Invierte en accesibilidad para un público global. Presenta opciones para personalizar la experiencia, buscando ser inclusivo para usuarios con diversas necesidades.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Benefits from extensive resources dedicated to accessibility, aiming for compliance with WCAG standards. Features like screen reader support are well-implemented.</t>
+          <t>Se esfuerza en ofrecer un sitio accesible, con etiquetas Alt en imágenes y buen contraste. Apunta a la inclusión, aunque no es su característica principal.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Features high color contrast between text and background, ensuring good readability. The layout appears simple and straightforward, potentially aiding keyboard navigation for all users.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Enhancing alt-text for all images and interactive elements would improve screen reader compatibility. Ensuring all form inputs have proper labels and focus indicators would further boost accessibility.</t>
-        </is>
-      </c>
+          <t>La accesibilidad básica está presente en su diseño funcional y textual. Sin embargo, podría beneficiarse de una auditoría WCAG para optimizar la experiencia inclusiva.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -660,29 +636,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Offers robust search, filtering, comparison tools, and a comprehensive checkout process. The PC builder tool is a standout feature for enthusiasts.</t>
+          <t>Ofrece filtros avanzados, comparadores de productos y un configurador de PC muy completo. Estas funcionalidades mejoran significativamente la decisión de compra.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provides accurate stock availability (online/in-store), reliable checkout, and effective product filtering. Its custom PC configurator is highly valued by users.</t>
+          <t>Funcionalidades robustas, incluyendo el carrito, la lista de deseos y el seguimiento de pedidos. Su proceso de compra es altamente eficiente y consolidado.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Features a highly optimized shopping cart, one-click ordering, and robust customer support. Product reviews, Q&amp;A, and recommendation engines are key functionalities.</t>
+          <t>Dispone de herramientas como configuradores de PC, filtros exhaustivos y listas de compatibilidad. Su funcionalidad es clave para usuarios expertos en hardware.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Includes a visible search bar and main navigation points, suggesting core functionality like product searching and information access. Advanced tools are implied.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ensure all promised functionalities like 'Arma tu PC' and 'Comparar' are fully realized and highly intuitive. Implementing detailed product filtering options would significantly enhance user control.</t>
-        </is>
-      </c>
+          <t>Su funcionalidad principal es la verificación de compatibilidad de componentes, filtros potentes y guías de montaje. Es esencialmente una herramienta interactiva.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -692,123 +664,95 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Engages users with product reviews, Q&amp;A sections, wishlists, and a robust community forum. Dynamic product displays and interactive configurators are present.</t>
+          <t>Incorpora chats en vivo, opiniones de usuarios, y opciones de personalización en configuradores. Fomenta la participación y la toma de decisiones informada.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Encourages interaction through customer reviews, in-store pickup options, and personalized recommendations. Live chat support offers direct engagement.</t>
+          <t>Alta interactividad a través de reseñas, preguntas y respuestas, y recomendaciones personalizadas. Fomenta un ecosistema de compra y comunidad activo.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Highly interactive with user reviews, ratings, Q&amp;A, and personalized recommendations. Its seamless purchase flow and wishlists foster strong engagement.</t>
+          <t>Ofrece foros de discusión, comentarios detallados de productos y guías interactivas. Mantiene a los usuarios comprometidos y explorando su catálogo técnico.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Displays popular components in an engaging grid, and implied features suggest interactive tools. Clear clickable elements guide user actions effectively.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Adding interactive elements like hover-over product details or quick-view options could enrich engagement. Incorporating customer reviews or a basic Q&amp;A section would foster community and trust.</t>
-        </is>
-      </c>
+          <t>La interactividad se centra en la selección de componentes y la visualización de compatibilidades. Podría añadir más elementos sociales o de gamificación para engagement.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEO (Search Engine Optimization)</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Benefits from high domain authority, relevant keywords in product titles/descriptions, and a vast content library. Structured data markup is likely used.</t>
+          <t>Goza de una excelente visibilidad en buscadores, con una estrategia SEO bien definida y un contenido optimizado para el mercado de PC en español.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Leverages local SEO for its physical stores and optimizes product pages for specific component searches. Blog content and guides contribute to organic visibility.</t>
+          <t>Domina el SEO por su autoridad de dominio y la vasta cantidad de contenido. Su visibilidad es inigualable en un amplio espectro de búsquedas de productos.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dominates search results due to its massive product catalog, high authority, and user-generated content (reviews). Product-specific pages are highly optimized.</t>
+          <t>Presenta un SEO sólido, especialmente para búsquedas de hardware específico. Su contenido técnico y la estructura del sitio favorecen un buen posicionamiento.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>While content is minimal, proper use of titles, descriptions, and structured URLs would be crucial. Focus on long-tail keywords relevant to PC components.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Implement descriptive page titles, meta descriptions, and clean URLs for every product. Utilizing structured data markup (Schema.org) for products would improve search engine visibility and rich snippets.</t>
-        </is>
-      </c>
+          <t>Su SEO es bueno para búsquedas específicas de compatibilidad y construcción de PCs. La optimización de palabras clave podría enfocarse en guías y tutoriales para mejorar aún más.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Performance/Loading Speed</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newegg remains a premier destination for PC hardware, praised for its vast selection, competitive pricing, and comprehensive feature set, catering to enthusiasts.</t>
+          <t>Mantiene una velocidad de carga rápida y un rendimiento optimizado. Esto asegura una experiencia de navegación fluida y satisfactoria para el usuario.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Micro Center offers a unique blend of online convenience and invaluable in-store expertise, making it a strong choice for builders needing immediate support.</t>
+          <t>A pesar de su enorme complejidad, Amazon carga relativamente rápido. Su rendimiento está altamente optimizado para manejar un volumen masivo de tráfico y productos.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazon provides unparalleled convenience and selection across a broad spectrum of PC components, leveraging its extensive logistics and trusted marketplace for a diverse audience.</t>
+          <t>Ofrece una buena velocidad de carga y un rendimiento web estable. La optimización de imágenes y scripts contribuye a una experiencia ágil.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The site presents a clean, user-friendly interface with clear goals for PC enthusiasts. It establishes a solid foundation for guiding users through component selection.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>The site has a good foundational design, but expanding content, visual details, and advanced interactive tools would elevate the user experience significantly. Focus on detailed product information and community.</t>
-        </is>
-      </c>
+          <t>La velocidad de carga es eficiente, dado el volumen de datos de compatibilidad que maneja. La optimización continua de recursos es clave para mantener la fluidez.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Overall Conclusion</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Newegg stands out with its extensive inventory, specialized focus on PC components, and strong community support, making it a go-to for enthusiasts and builders.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Micro Center excels in customer service, offering a valuable blend of in-store expertise and online convenience, particularly for local pick-ups and bundles.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Amazon provides unmatched accessibility and a vast product range, favored for its swift delivery, competitive pricing, and robust customer review system across various sellers.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>The Image Site, 'Rity', offers a clean, intuitive platform for PC enthusiasts to learn, build, and compare. Its direct approach simplifies navigation and component display.</t>
-        </is>
-      </c>
+          <t>+Final Conclusion</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>To elevate the user experience, the site should prioritize richer content, advanced filtering, and interactive tools beyond basic browsing. Enhancing product imagery and fostering community engagement would be beneficial additions.</t>
+          <t>El sitio web analizado posee una base sólida en su estructura y funcionalidades esenciales, ofreciendo una experiencia adecuada para el usuario. Sin embargo, para capitalizar su potencial, se sugiere optimizar la jerarquía visual y la interactividad. Mejorar el rendimiento de carga e implementar una estrategia SEO más robusta también potenciarían su visibilidad y engagement. Se recomienda explorar nuevas funcionalidades para enriquecer la oferta y destacarse en el competitivo mercado.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PcComponentes</t>
+          <t>Newegg</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -446,12 +446,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Newegg</t>
+          <t>Micro Center</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PCPartPicker</t>
+          <t>PCity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,25 +468,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Utiliza tipografías Sans-serif claras que garantizan una excelente legibilidad en todas las secciones. El tamaño y espaciado favorecen una lectura cómoda y eficiente.</t>
+          <t>Newegg es conocido por su enfoque limpio. Su tipografía clara y el espaciado adecuado mejoran la legibilidad de descripciones de productos y especificaciones técnicas, facilitando la navegación.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Presenta tipografías estándar y un diseño funcional que prioriza la información. La legibilidad es alta, aunque el volumen de texto puede resultar denso en ocasiones.</t>
+          <t>Amazon utiliza una tipografía sencilla y familiar. La consistencia en el tamaño y estilo de fuente en todo el sitio garantiza una experiencia de lectura cómoda y accesible para los usuarios.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Emplea fuentes limpias y tamaños adecuados para asegurar una lectura fluida. La jerarquía visual de los textos ayuda a identificar rápidamente la información clave.</t>
+          <t>Micro Center presenta una fuente estándar para su contenido. El contraste de colores y la jerarquía visual de su texto ayudan a los usuarios a diferenciar fácilmente la información clave del producto y las ofertas.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>La tipografía es funcional y clara, aunque en ocasiones la uniformidad de tamaño puede dificultar la jerarquía visual de contenidos importantes.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>PCity emplea una tipografía limpia y estándar que asegura una buena legibilidad general. Los títulos son claros, aunque la jerarquía visual entre diferentes elementos de texto podría ser más pronunciada para guiar mejor al usuario.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Se podría mejorar la jerarquía visual del texto y el contraste para destacar información crucial, haciendo que la lectura sea más dinámica y menos monótona.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,25 +500,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Su vibrante paleta de colores corporativos (naranja y blanco/gris) es consistente, creando una identidad de marca moderna y fácilmente reconocible en todo el sitio.</t>
+          <t>Newegg emplea una paleta de colores corporativos. Su combinación de azul y blanco se asocia fuertemente con la tecnología, transmitiendo una imagen de fiabilidad y modernidad en el mercado de PC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Utiliza una paleta de colores simple y reconocible (azul, naranja, blanco). El branding se centra en la familiaridad y confianza, con un logo omnipresente.</t>
+          <t>Amazon se distingue por su distintivo esquema de colores. El negro, naranja y blanco son inmediatamente reconocibles, proyectando una imagen de marca global que es confiable y de fácil acceso.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Predominan los tonos azules y grises, que transmiten profesionalidad y tecnología. El branding es sutil pero consistente, reforzando su imagen en el sector.</t>
+          <t>Micro Center utiliza un esquema de color vibrante en su diseño. La combinación de rojo y negro crea una identidad de marca enérgica, atrayendo a entusiastas de la tecnología con su estilo audaz.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>La interfaz usa colores básicos (azul, blanco, negro) de forma consistente. El branding es funcional, centrado en la herramienta más que en una estética llamativa.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>PCity utiliza un esquema de colores azul y blanco, que es común en tecnología y transmite limpieza. La identidad de marca es funcional, pero podría desarrollarse para ser más distintiva y memorable.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>La identidad de marca podría reforzarse con una paleta de colores más consistente que refleje mejor su propuesta de valor, creando una impresión más cohesionada y memorable.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -524,25 +532,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Destaca por imágenes de producto de alta resolución y vídeos descriptivos. Los iconos son intuitivos y complementan la información textual, mejorando la experiencia de compra.</t>
+          <t>Newegg muestra imágenes de productos de alta calidad y diseños consistentes. La disposición de los elementos visuales es ordenada y profesional, mejorando la experiencia de compra y la presentación de los artículos.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abundantes imágenes de productos y vistas de 360 grados. Los elementos visuales son informativos y funcionales, aunque el diseño general puede parecer menos moderno.</t>
+          <t>Amazon gestiona una vasta cantidad de elementos visuales con gran eficacia. Desde imágenes de productos hasta banners promocionales, todo está optimizado para cargar rápidamente y ser visualmente atractivo.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ofrece imágenes de productos detalladas y galerías interactivas. Los elementos gráficos son limpios y contribuyen a una presentación profesional del hardware.</t>
+          <t>Micro Center incorpora elementos visuales dinámicos y organizados. Sus banners y gráficos promocionales son efectivos para destacar ofertas, manteniendo una estética limpia que facilita la exploración de productos.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Los elementos visuales son principalmente imágenes de productos, esquemas y gráficos para compatibilidad. Son funcionales, pero la estética es secundaria a la claridad informativa.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>PCity presenta imágenes de productos claras y bien enmarcadas sobre un fondo blanco, lo que contribuye a una apariencia limpia. Se observa una consistencia en el tamaño de las miniaturas, pero faltan elementos gráficos más dinámicos o iconos informativos.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Considerar la inclusión de elementos gráficos más dinámicos y el uso de iconos informativos para mejorar la interacción visual, aportando mayor riqueza sin sobrecargar el diseño.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,25 +564,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navegación intuitiva con menús desplegables claros y un buscador eficiente. La experiencia de usuario es fluida, facilitando la búsqueda y compra de componentes.</t>
+          <t>Newegg ofrece una navegación estructurada y lógica. Sus menús desplegables y filtros avanzados permiten a los usuarios encontrar productos específicos con facilidad, proporcionando una experiencia de usuario eficiente.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>La navegación es amplia y familiar, aunque a veces saturada. La UX se enfoca en la eficiencia del proceso de compra, con un flujo bien establecido y conocido.</t>
+          <t>Amazon es un referente en navegación, con menús intuitivos y una barra de búsqueda potente. La experiencia del usuario es fluida, permitiendo una exploración y compra de productos sin esfuerzo y altamente eficiente.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Presenta una navegación lógica y estructurada, con categorías bien definidas. La UX está diseñada para exploradores de tecnología, con filtros avanzados y fácil acceso a comparativas.</t>
+          <t>Micro Center proporciona una navegación clara y categorizada. Sus opciones de filtro y búsqueda permiten una exploración eficiente del inventario, mejorando la usabilidad para compradores de tecnología.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Navegación clara y orientada a la función, facilitando la búsqueda y compatibilidad de componentes. La UX es altamente funcional, ideal para construir PCs paso a paso.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>PCity ofrece una navegación sencilla con enlaces en el encabezado que son fáciles de entender. La barra de búsqueda es prominente. Sin embargo, se podrían añadir más opciones de filtrado o categorización para una mejor experiencia.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Se podría optimizar la navegación añadiendo filtros más específicos y una categorización más profunda para facilitar la búsqueda de productos, mejorando la experiencia del usuario y la eficiencia.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,25 +596,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contenido bien jerarquizado y organizado por categorías y subcategorías claras. La estructura facilita la exploración y búsqueda de productos específicos.</t>
+          <t>Newegg organiza su contenido de manera lógica y coherente. Las categorías de productos están bien definidas, facilitando que los usuarios exploren y encuentren rápidamente lo que buscan en un catálogo extenso.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Organización de contenido vasta y compleja, pero con una estructura de categorías coherente. Permite una buena visibilidad de productos, a pesar de la enorme oferta.</t>
+          <t>Amazon presenta una estructura de contenido ejemplar. La organización por categorías, recomendaciones y la clara disposición de la información del producto facilitan una interacción intuitiva y eficiente para el usuario.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estructura lógica y bien definida, optimizada para el hardware. Las fichas de producto son detalladas, y las guías de compra están bien integradas.</t>
+          <t>Micro Center mantiene una organización clara y estructurada. Las secciones de productos y las páginas de categorías están bien definidas, lo que ayuda a los usuarios a navegar sin problemas a través de su amplio inventario.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>La estructura se centra en la compatibilidad de componentes, con listas y filtros. Es muy organizada para su propósito específico de montaje de PCs.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>PCity presenta una estructura organizada con una sección destacada para 'Componentes populares'. El diseño es limpio y los elementos principales están bien posicionados, pero una mayor profundidad en la categorización sería beneficiosa.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Se sugiere una estructura de contenido más jerárquica con categorías y subcategorías más detalladas, lo que permitiría una exploración más profunda y organizada de la oferta de productos.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -608,25 +628,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cumple con estándares básicos de accesibilidad, aunque siempre hay margen de mejora. Se percibe un esfuerzo por hacer el sitio usable para diversos usuarios.</t>
+          <t>Newegg se esfuerza por una buena accesibilidad, usando alto contraste en su texto y un diseño responsive. Se enfoca en garantizar que la información sea legible para una amplia gama de usuarios, mejorando la inclusión.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Invierte en accesibilidad para un público global. Presenta opciones para personalizar la experiencia, buscando ser inclusivo para usuarios con diversas necesidades.</t>
+          <t>Amazon es un líder en accesibilidad, con características como descripciones de imágenes y navegación por teclado. Se aseguran de que su plataforma sea utilizable por personas con diversas necesidades, promoviendo la inclusión.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Se esfuerza en ofrecer un sitio accesible, con etiquetas Alt en imágenes y buen contraste. Apunta a la inclusión, aunque no es su característica principal.</t>
+          <t>Micro Center tiene un diseño con buen contraste y tamaños de fuente legibles. La accesibilidad general parece pensada, aunque se podría profundizar en características para usuarios con necesidades especiales.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>La accesibilidad básica está presente en su diseño funcional y textual. Sin embargo, podría beneficiarse de una auditoría WCAG para optimizar la experiencia inclusiva.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>PCity muestra un buen contraste entre el texto y el fondo, lo cual es positivo para la legibilidad. Los tamaños de fuente son adecuados. Sin embargo, no se observa evidencia de características avanzadas de accesibilidad.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Podría explorar la implementación de funciones de accesibilidad avanzadas, como etiquetas alt para imágenes y navegación por teclado, para asegurar una experiencia inclusiva para todos los usuarios.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -636,25 +660,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ofrece filtros avanzados, comparadores de productos y un configurador de PC muy completo. Estas funcionalidades mejoran significativamente la decisión de compra.</t>
+          <t>Newegg ofrece una funcionalidad robusta, incluyendo búsqueda avanzada, filtrado detallado y comparación de productos. Estas herramientas son esenciales para una experiencia de compra eficiente y satisfactoria en línea.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Funcionalidades robustas, incluyendo el carrito, la lista de deseos y el seguimiento de pedidos. Su proceso de compra es altamente eficiente y consolidado.</t>
+          <t>Amazon es sinónimo de funcionalidad integral, desde la búsqueda de productos hasta el proceso de compra. Ofrece características avanzadas como seguimiento de pedidos y reseñas de usuarios, enriqueciendo la experiencia.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dispone de herramientas como configuradores de PC, filtros exhaustivos y listas de compatibilidad. Su funcionalidad es clave para usuarios expertos en hardware.</t>
+          <t>Micro Center proporciona funcionalidades sólidas, como filtros de búsqueda detallados y una interfaz de carrito de compras intuitiva. Estas herramientas mejoran la capacidad del usuario para encontrar y adquirir productos.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Su funcionalidad principal es la verificación de compatibilidad de componentes, filtros potentes y guías de montaje. Es esencialmente una herramienta interactiva.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>PCity parece ofrecer las funcionalidades básicas esperadas, como una barra de búsqueda y visualización de productos. Sin embargo, la imagen no permite evaluar características avanzadas como filtros detallados o una herramienta de comparación de productos.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sería beneficioso integrar funcionalidades avanzadas como filtros de búsqueda más potentes, herramientas de comparación de productos y un sistema de reseñas para enriquecer la experiencia del usuario.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -664,25 +692,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Incorpora chats en vivo, opiniones de usuarios, y opciones de personalización en configuradores. Fomenta la participación y la toma de decisiones informada.</t>
+          <t>Newegg fomenta la interactividad a través de reseñas de productos, preguntas y respuestas, y configuradores de PC. Estas características permiten a los usuarios participar activamente, mejorando la toma de decisiones de compra.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alta interactividad a través de reseñas, preguntas y respuestas, y recomendaciones personalizadas. Fomenta un ecosistema de compra y comunidad activo.</t>
+          <t>Amazon potencia la interactividad con un sistema de valoraciones, preguntas y respuestas, y recomendaciones personalizadas. Esto crea una comunidad activa y mejora la relevancia del contenido para cada usuario.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ofrece foros de discusión, comentarios detallados de productos y guías interactivas. Mantiene a los usuarios comprometidos y explorando su catálogo técnico.</t>
+          <t>Micro Center permite la interacción a través de las valoraciones de productos y las secciones de preguntas. Esta interactividad contribuye a la confianza del cliente, ofreciendo una perspectiva comunitaria valiosa.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>La interactividad se centra en la selección de componentes y la visualización de compatibilidades. Podría añadir más elementos sociales o de gamificación para engagement.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>PCity, por lo que se ve en la imagen, tiene una interactividad limitada a los elementos de navegación. No se observan características como reseñas de usuarios o herramientas de configuración de productos, lo cual es una oportunidad de mejora.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Se sugiere incorporar elementos interactivos como valoraciones y comentarios de usuarios, además de herramientas configurables, para fomentar una mayor participación y generar confianza en la plataforma.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,67 +724,91 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Goza de una excelente visibilidad en buscadores, con una estrategia SEO bien definida y un contenido optimizado para el mercado de PC en español.</t>
+          <t>Newegg optimiza su sitio para SEO, utilizando descripciones detalladas, palabras clave relevantes y una estructura de URL amigable. Esto asegura una alta visibilidad en los motores de búsqueda, atrayendo a más usuarios.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Domina el SEO por su autoridad de dominio y la vasta cantidad de contenido. Su visibilidad es inigualable en un amplio espectro de búsquedas de productos.</t>
+          <t>Amazon tiene una estrategia de SEO robusta, capitalizando su autoridad de dominio y optimizando las páginas de productos. Esto garantiza que sus vastos listados sean fácilmente descubiertos por los usuarios que buscan productos específicos.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Presenta un SEO sólido, especialmente para búsquedas de hardware específico. Su contenido técnico y la estructura del sitio favorecen un buen posicionamiento.</t>
+          <t>Micro Center utiliza descripciones de productos optimizadas y categorías claras para SEO. Esto les permite clasificar bien para términos de búsqueda relevantes, atrayendo tráfico orgánico interesado en hardware.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Su SEO es bueno para búsquedas específicas de compatibilidad y construcción de PCs. La optimización de palabras clave podría enfocarse en guías y tutoriales para mejorar aún más.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Aunque no se puede evaluar directamente desde la imagen, un buen SEO es crucial. La estructura de URL y las descripciones de los productos serían puntos clave de optimización para mejorar la visibilidad orgánica.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Para mejorar la visibilidad orgánica, se recomienda optimizar la estructura de las URL, implementar meta descripciones y títulos atractivos, y asegurar que el contenido esté enriquecido con palabras clave relevantes.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance/Loading Speed</t>
+          <t>Performance &amp; Loading Speed</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mantiene una velocidad de carga rápida y un rendimiento optimizado. Esto asegura una experiencia de navegación fluida y satisfactoria para el usuario.</t>
+          <t>Newegg optimiza continuamente su rendimiento. Sus páginas cargan rápidamente, incluso con gran cantidad de contenido, lo que es crucial para retener a los usuarios y mejorar la experiencia de compra en línea.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A pesar de su enorme complejidad, Amazon carga relativamente rápido. Su rendimiento está altamente optimizado para manejar un volumen masivo de tráfico y productos.</t>
+          <t>Amazon invierte fuertemente en la velocidad de carga de su sitio. Esto garantiza una experiencia de usuario fluida, reduciendo la tasa de rebote y mejorando la satisfacción general del cliente, incluso con contenido masivo.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ofrece una buena velocidad de carga y un rendimiento web estable. La optimización de imágenes y scripts contribuye a una experiencia ágil.</t>
+          <t>Micro Center tiene un rendimiento decente, con tiempos de carga de página aceptables. Mantener una velocidad de carga rápida es vital para la satisfacción del usuario y las clasificaciones de los motores de búsqueda.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La velocidad de carga es eficiente, dado el volumen de datos de compatibilidad que maneja. La optimización continua de recursos es clave para mantener la fluidez.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>Sin datos de prueba, la velocidad de carga no es visible. Sin embargo, un diseño limpio y pocas animaciones pueden contribuir a un rendimiento rápido, fundamental para la retención de usuarios y el SEO.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asegurar que el sitio web cargue rápidamente es primordial; se debería optimizar imágenes, usar caché y minificar recursos para una experiencia fluida, especialmente en dispositivos móviles.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>+Final Conclusion</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>Final Conclusion</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Newegg es un referente en e-commerce de hardware. Su sólida interfaz, extenso catálogo y servicio al cliente lo posicionan como una opción preferente para entusiastas y profesionales de la tecnología, destacando en todos los criterios.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Amazon es un gigante del comercio electrónico. Su escala, conveniencia y experiencia de usuario optimizada, respaldadas por un robusto sistema logístico, lo convierten en una plataforma dominante y globalmente accesible para cualquier compra.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Micro Center sobresale en la venta minorista de componentes. Su combinación de presencia en línea y tiendas físicas, junto con un enfoque en el servicio experto, ofrece una experiencia de compra completa y especializada.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PCity presenta una base prometedora con un diseño limpio y navegación directa. Sus elementos visuales son claros, ofreciendo una experiencia básica pero funcional para el usuario. La usabilidad es notable, aunque sin lujos. Se enfoca en la simplicidad.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El sitio web analizado posee una base sólida en su estructura y funcionalidades esenciales, ofreciendo una experiencia adecuada para el usuario. Sin embargo, para capitalizar su potencial, se sugiere optimizar la jerarquía visual y la interactividad. Mejorar el rendimiento de carga e implementar una estrategia SEO más robusta también potenciarían su visibilidad y engagement. Se recomienda explorar nuevas funcionalidades para enriquecer la oferta y destacarse en el competitivo mercado.</t>
+          <t>En general, el sitio presenta un diseño limpio y una navegación intuitiva, lo que son puntos fuertes. Las principales oportunidades de mejora residen en enriquecer la interactividad y la funcionalidad avanzada, así como en profundizar la estructura del contenido para ofrecer una experiencia más completa y distintiva a los usuarios.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Newegg</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center</t>
+          <t>GamersNexus</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PCity</t>
+          <t>Pcity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,27 +468,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newegg es conocido por su enfoque limpio. Su tipografía clara y el espaciado adecuado mejoran la legibilidad de descripciones de productos y especificaciones técnicas, facilitando la navegación.</t>
+          <t>Presenta un estilo tipográfico claro y profesional. Facilita la lectura de artículos extensos con buen contraste y tamaño de fuente, optimizando la experiencia de usuario.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Amazon utiliza una tipografía sencilla y familiar. La consistencia en el tamaño y estilo de fuente en todo el sitio garantiza una experiencia de lectura cómoda y accesible para los usuarios.</t>
+          <t>Utiliza fuentes estándar de e-commerce, con buena legibilidad en listados de productos. La densidad de información podría beneficiarse de un enfoque más organizado, mejorando la claridad.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Micro Center presenta una fuente estándar para su contenido. El contraste de colores y la jerarquía visual de su texto ayudan a los usuarios a diferenciar fácilmente la información clave del producto y las ofertas.</t>
+          <t>Exhibe una tipografía técnica y directa. Proporciona una experiencia de lectura enfocada en el detalle, ideal para usuarios que buscan información muy específica sobre hardware.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PCity emplea una tipografía limpia y estándar que asegura una buena legibilidad general. Los títulos son claros, aunque la jerarquía visual entre diferentes elementos de texto podría ser más pronunciada para guiar mejor al usuario.</t>
+          <t>Emplea tipografía sencilla y legible. El texto principal es claro, pero la consistencia y jerarquía en diversas secciones podrían optimizarse para una mejor comprensión visual del contenido.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Se podría mejorar la jerarquía visual del texto y el contraste para destacar información crucial, haciendo que la lectura sea más dinámica y menos monótona.</t>
+          <t>The site in the image uses clear fonts for main headings and product names, but body text consistency and hierarchical sizing could enhance information consumption across various screen sizes.</t>
         </is>
       </c>
     </row>
@@ -500,27 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newegg emplea una paleta de colores corporativos. Su combinación de azul y blanco se asocia fuertemente con la tecnología, transmitiendo una imagen de fiabilidad y modernidad en el mercado de PC.</t>
+          <t>Mantiene una paleta de colores sobria y tecnológica. Su branding global es consistente, transmitiendo autoridad y fiabilidad en el ámbito de la tecnología.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon se distingue por su distintivo esquema de colores. El negro, naranja y blanco son inmediatamente reconocibles, proyectando una imagen de marca global que es confiable y de fácil acceso.</t>
+          <t>Adopta una combinación de colores vibrante y comercial. El branding minorista es reconocible, con un enfoque claro en ofertas y categorías de productos destacadas.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Micro Center utiliza un esquema de color vibrante en su diseño. La combinación de rojo y negro crea una identidad de marca enérgica, atrayendo a entusiastas de la tecnología con su estilo audaz.</t>
+          <t>Usa una estética oscura enfocada en el rendimiento. El branding es distintivo en su nicho, reflejando contenido técnico y análisis de hardware sin concesiones.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PCity utiliza un esquema de colores azul y blanco, que es común en tecnología y transmite limpieza. La identidad de marca es funcional, pero podría desarrollarse para ser más distintiva y memorable.</t>
+          <t>Presenta una combinación de azul brillante y blanco. El logo y esquema de color sugieren un enfoque moderno y accesible, aunque el branding general podría ser más sofisticado.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>La identidad de marca podría reforzarse con una paleta de colores más consistente que refleje mejor su propuesta de valor, creando una impresión más cohesionada y memorable.</t>
+          <t>The color scheme is functional and distinctive, but expanding the brand identity beyond the basic blue and white, perhaps with secondary accent colors or graphic elements, could create a more memorable and unique user experience.</t>
         </is>
       </c>
     </row>
@@ -532,27 +532,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newegg muestra imágenes de productos de alta calidad y diseños consistentes. La disposición de los elementos visuales es ordenada y profesional, mejorando la experiencia de compra y la presentación de los artículos.</t>
+          <t>Integra imágenes de alta calidad y gráficos informativos. Ofrece visuales pertinentes que complementan eficazmente sus extensas reseñas y análisis técnicos detallados.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amazon gestiona una vasta cantidad de elementos visuales con gran eficacia. Desde imágenes de productos hasta banners promocionales, todo está optimizado para cargar rápidamente y ser visualmente atractivo.</t>
+          <t>Destaca por fotografías de productos claras y detalladas. Las imágenes cumplen su función de mostrar artículos, pero gráficos adicionales son limitados en su presentación general.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Micro Center incorpora elementos visuales dinámicos y organizados. Sus banners y gráficos promocionales son efectivos para destacar ofertas, manteniendo una estética limpia que facilita la exploración de productos.</t>
+          <t>Incorpora imágenes de hardware detalladas y capturas de pantalla de benchmarks. Los elementos visuales son cruciales para sus análisis, apoyando la información técnica con evidencia gráfica.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PCity presenta imágenes de productos claras y bien enmarcadas sobre un fondo blanco, lo que contribuye a una apariencia limpia. Se observa una consistencia en el tamaño de las miniaturas, pero faltan elementos gráficos más dinámicos o iconos informativos.</t>
+          <t>Muestra imágenes de productos consistentes y bien alineadas. Las miniaturas de componentes populares son claras, pero la inclusión de gráficos o íconos adicionales realzaría la experiencia.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Considerar la inclusión de elementos gráficos más dinámicos y el uso de iconos informativos para mejorar la interacción visual, aportando mayor riqueza sin sobrecargar el diseño.</t>
+          <t>Product images are uniformly presented, which is a good starting point. However, incorporating more diverse visual elements such as infographics, comparison charts, or detailed product galleries could significantly improve user engagement and information retention.</t>
         </is>
       </c>
     </row>
@@ -564,27 +564,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Newegg ofrece una navegación estructurada y lógica. Sus menús desplegables y filtros avanzados permiten a los usuarios encontrar productos específicos con facilidad, proporcionando una experiencia de usuario eficiente.</t>
+          <t>Ofrece navegación estructurada y lógica. La experiencia de usuario es intuitiva, permitiendo acceso rápido a categorías de productos, noticias y guías relevantes.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amazon es un referente en navegación, con menús intuitivos y una barra de búsqueda potente. La experiencia del usuario es fluida, permitiendo una exploración y compra de productos sin esfuerzo y altamente eficiente.</t>
+          <t>Proporciona navegación robusta orientada al comercio. La experiencia de usuario se centra en búsqueda y filtrado de productos, diseñada para facilitar transacciones eficientes.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Micro Center proporciona una navegación clara y categorizada. Sus opciones de filtro y búsqueda permiten una exploración eficiente del inventario, mejorando la usabilidad para compradores de tecnología.</t>
+          <t>Cuenta con navegación directa a sus categorías de contenido principal. La UX está diseñada para exploradores técnicos, priorizando el acceso a sus profundos análisis y videos.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PCity ofrece una navegación sencilla con enlaces en el encabezado que son fáciles de entender. La barra de búsqueda es prominente. Sin embargo, se podrían añadir más opciones de filtrado o categorización para una mejor experiencia.</t>
+          <t>Tiene una barra de navegación superior clara con enlaces esenciales. La experiencia de usuario parece sencilla, aunque opciones de filtrado o categorías secundarias no son visibles.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Se podría optimizar la navegación añadiendo filtros más específicos y una categorización más profunda para facilitar la búsqueda de productos, mejorando la experiencia del usuario y la eficiencia.</t>
+          <t>The main navigation is clear and concise, offering immediate access to key sections. To enhance user experience, implementing more dynamic filters, detailed category breakdowns, and a consistent breadcrumb trail would be beneficial for deeper exploration.</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Newegg organiza su contenido de manera lógica y coherente. Las categorías de productos están bien definidas, facilitando que los usuarios exploren y encuentren rápidamente lo que buscan en un catálogo extenso.</t>
+          <t>Organiza su contenido en secciones bien definidas. La estructura facilita la búsqueda de información específica, categorizando artículos por tipo de componente y temática tecnológica.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amazon presenta una estructura de contenido ejemplar. La organización por categorías, recomendaciones y la clara disposición de la información del producto facilitan una interacción intuitiva y eficiente para el usuario.</t>
+          <t>Presenta organización de productos por categorías lógicas. La estructura está optimizada para la compra, con listados claros y opciones de clasificación para la elección del cliente.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Micro Center mantiene una organización clara y estructurada. Las secciones de productos y las páginas de categorías están bien definidas, lo que ayuda a los usuarios a navegar sin problemas a través de su amplio inventario.</t>
+          <t>Estructura su contenido por tipos de análisis y publicaciones. La organización es coherente con su enfoque en rendimiento de hardware, permitiendo encontrar rápidamente estudios detallados.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PCity presenta una estructura organizada con una sección destacada para 'Componentes populares'. El diseño es limpio y los elementos principales están bien posicionados, pero una mayor profundidad en la categorización sería beneficiosa.</t>
+          <t>Muestra componentes populares en un diseño de cuadrícula ordenado. La organización es limpia y funcional, pero no se aprecian categorías avanzadas o árboles de productos.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Se sugiere una estructura de contenido más jerárquica con categorías y subcategorías más detalladas, lo que permitiría una exploración más profunda y organizada de la oferta de productos.</t>
+          <t>The current layout for popular components is clean and easy to scan. Expanding this structure to include clear hierarchical categories, advanced sorting options, and dedicated landing pages for different component types would greatly improve overall site navigability.</t>
         </is>
       </c>
     </row>
@@ -628,27 +628,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Newegg se esfuerza por una buena accesibilidad, usando alto contraste en su texto y un diseño responsive. Se enfoca en garantizar que la información sea legible para una amplia gama de usuarios, mejorando la inclusión.</t>
+          <t>Se esfuerza por buena accesibilidad en su contenido. Utiliza atributos ALT en imágenes y estructura HTML semántica, aunque siempre hay margen para mejoras.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amazon es un líder en accesibilidad, con características como descripciones de imágenes y navegación por teclado. Se aseguran de que su plataforma sea utilizable por personas con diversas necesidades, promoviendo la inclusión.</t>
+          <t>Implementa características básicas de accesibilidad para su plataforma. Se enfoca en cumplir estándares para facilitar navegación y compra a un amplio rango de usuarios.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Micro Center tiene un diseño con buen contraste y tamaños de fuente legibles. La accesibilidad general parece pensada, aunque se podría profundizar en características para usuarios con necesidades especiales.</t>
+          <t>Prioriza la claridad del contenido. La accesibilidad es razonable, pero la complejidad técnica de algunos gráficos podría ser un desafío para usuarios con ciertas discapacidades.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PCity muestra un buen contraste entre el texto y el fondo, lo cual es positivo para la legibilidad. Los tamaños de fuente son adecuados. Sin embargo, no se observa evidencia de características avanzadas de accesibilidad.</t>
+          <t>Parece tener contraste de color adecuado para el texto principal. La disposición simple sugiere una accesibilidad básica, pero se necesita una evaluación completa.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Podría explorar la implementación de funciones de accesibilidad avanzadas, como etiquetas alt para imágenes y navegación por teclado, para asegurar una experiencia inclusiva para todos los usuarios.</t>
+          <t>The high contrast between blue and white is a positive step for visual accessibility. Further improvements should focus on providing alternative text for all images, ensuring keyboard navigation, and implementing ARIA labels for interactive elements to support screen reader users.</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Newegg ofrece una funcionalidad robusta, incluyendo búsqueda avanzada, filtrado detallado y comparación de productos. Estas herramientas son esenciales para una experiencia de compra eficiente y satisfactoria en línea.</t>
+          <t>Ofrece funcionalidad robusta para publicación de contenido. Incluye búsqueda avanzada, comentarios y una base de datos extensa de especificaciones de componentes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amazon es sinónimo de funcionalidad integral, desde la búsqueda de productos hasta el proceso de compra. Ofrece características avanzadas como seguimiento de pedidos y reseñas de usuarios, enriqueciendo la experiencia.</t>
+          <t>Dispone de funcionalidad completa de comercio electrónico. Permite búsqueda de productos, gestión de carritos, procesamiento de pagos y seguimiento de pedidos, con experiencia fluida.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Micro Center proporciona funcionalidades sólidas, como filtros de búsqueda detallados y una interfaz de carrito de compras intuitiva. Estas herramientas mejoran la capacidad del usuario para encontrar y adquirir productos.</t>
+          <t>Proporciona funcionalidad para entrega de contenido multimedia. Integra videos y artículos, con herramientas para compartir y comentar, facilitando el engagement con su audiencia.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PCity parece ofrecer las funcionalidades básicas esperadas, como una barra de búsqueda y visualización de productos. Sin embargo, la imagen no permite evaluar características avanzadas como filtros detallados o una herramienta de comparación de productos.</t>
+          <t>Presenta un buscador visible y enlaces a secciones clave. La función 'Arma tu PC' sugiere un configurador, indicando funcionalidad orientada a la utilidad del usuario.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sería beneficioso integrar funcionalidades avanzadas como filtros de búsqueda más potentes, herramientas de comparación de productos y un sistema de reseñas para enriquecer la experiencia del usuario.</t>
+          <t>The presence of a search bar and a 'Build your PC' section indicates a focus on practical functionality. Enhancements could include advanced comparison tools, a more robust component compatibility checker within the builder, and real-time stock updates for parts.</t>
         </is>
       </c>
     </row>
@@ -692,27 +692,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Newegg fomenta la interactividad a través de reseñas de productos, preguntas y respuestas, y configuradores de PC. Estas características permiten a los usuarios participar activamente, mejorando la toma de decisiones de compra.</t>
+          <t>Permite comentarios en artículos y foros activos. Ofrece oportunidades de interacción para los usuarios, fomentando discusiones y el intercambio de conocimientos sobre tecnología.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Amazon potencia la interactividad con un sistema de valoraciones, preguntas y respuestas, y recomendaciones personalizadas. Esto crea una comunidad activa y mejora la relevancia del contenido para cada usuario.</t>
+          <t>Habilita reseñas de productos, preguntas y respuestas de usuarios. La interacción se centra en la comunidad de compradores, facilitando decisiones informadas y el soporte entre pares.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Micro Center permite la interacción a través de las valoraciones de productos y las secciones de preguntas. Esta interactividad contribuye a la confianza del cliente, ofreciendo una perspectiva comunitaria valiosa.</t>
+          <t>Fomenta la interacción a través de comentarios en videos y artículos. La comunidad es activa, participando en debates técnicos, enriqueciendo el contenido con perspectivas adicionales.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PCity, por lo que se ve en la imagen, tiene una interactividad limitada a los elementos de navegación. No se observan características como reseñas de usuarios o herramientas de configuración de productos, lo cual es una oportunidad de mejora.</t>
+          <t>La imagen no muestra elementos interactivos más allá de navegación básica. Secciones como 'Arma tu PC' o 'Comparar' podrían ofrecer interfaces más dinámicas para el usuario.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Se sugiere incorporar elementos interactivos como valoraciones y comentarios de usuarios, además de herramientas configurables, para fomentar una mayor participación y generar confianza en la plataforma.</t>
+          <t>While basic navigation is present, the site could significantly benefit from more interactive elements. Implementing user ratings, a comment section, forums, or a more engaging 'Build your PC' wizard would foster a stronger community and user engagement.</t>
         </is>
       </c>
     </row>
@@ -724,59 +724,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Newegg optimiza su sitio para SEO, utilizando descripciones detalladas, palabras clave relevantes y una estructura de URL amigable. Esto asegura una alta visibilidad en los motores de búsqueda, atrayendo a más usuarios.</t>
+          <t>Aplica estrategias SEO sólidas para su vasto contenido. Su alta autoridad de dominio le permite posicionarse bien en búsquedas relacionadas con hardware y tecnología.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amazon tiene una estrategia de SEO robusta, capitalizando su autoridad de dominio y optimizando las páginas de productos. Esto garantiza que sus vastos listados sean fácilmente descubiertos por los usuarios que buscan productos específicos.</t>
+          <t>Maneja un SEO robusto enfocado en productos y categorías. Su optimización es clave para captar tráfico de búsqueda transaccional con descripciones y metadatos efectivos.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Micro Center utiliza descripciones de productos optimizadas y categorías claras para SEO. Esto les permite clasificar bien para términos de búsqueda relevantes, atrayendo tráfico orgánico interesado en hardware.</t>
+          <t>Optimiza su contenido para búsquedas de nicho y términos técnicos. Su SEO se centra en rendimiento y análisis detallados, atrayendo audiencia especializada en hardware para PC.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aunque no se puede evaluar directamente desde la imagen, un buen SEO es crucial. La estructura de URL y las descripciones de los productos serían puntos clave de optimización para mejorar la visibilidad orgánica.</t>
+          <t>La estructura de títulos y claridad del contenido son positivos para el SEO básico. La optimización de metadescripciones, encabezados y URLs amigables es crucial para visibilidad.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Para mejorar la visibilidad orgánica, se recomienda optimizar la estructura de las URL, implementar meta descripciones y títulos atractivos, y asegurar que el contenido esté enriquecido con palabras clave relevantes.</t>
+          <t>The clear title and content visible suggest a good foundation for SEO. To improve organic reach, a focused strategy including keyword-rich content, optimized meta descriptions, structured data, and a robust internal linking structure should be developed.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance &amp; Loading Speed</t>
+          <t>Customer Support &amp; Community</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newegg optimiza continuamente su rendimiento. Sus páginas cargan rápidamente, incluso con gran cantidad de contenido, lo que es crucial para retener a los usuarios y mejorar la experiencia de compra en línea.</t>
+          <t>Ofrece foros comunitarios activos y guías extensas. El soporte se centra en autoayuda a través de una rica base de conocimientos generada por expertos y usuarios.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amazon invierte fuertemente en la velocidad de carga de su sitio. Esto garantiza una experiencia de usuario fluida, reduciendo la tasa de rebote y mejorando la satisfacción general del cliente, incluso con contenido masivo.</t>
+          <t>Proporciona soporte al cliente integral y herramientas de comunidad. Incluye chat en vivo, RMA, FAQs y foros, facilitando una experiencia de compra asistida.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Micro Center tiene un rendimiento decente, con tiempos de carga de página aceptables. Mantener una velocidad de carga rápida es vital para la satisfacción del usuario y las clasificaciones de los motores de búsqueda.</t>
+          <t>No tiene soporte al cliente tradicional, pero sí una comunidad. Sus videos y artículos sirven como apoyo indirecto, respondiendo preguntas comunes a través del contenido.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sin datos de prueba, la velocidad de carga no es visible. Sin embargo, un diseño limpio y pocas animaciones pueden contribuir a un rendimiento rápido, fundamental para la retención de usuarios y el SEO.</t>
+          <t>La imagen no revela información sobre soporte o comunidad explícita. La sección 'Información' podría albergar FAQs o enlaces de contacto para consultas de usuarios.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asegurar que el sitio web cargue rápidamente es primordial; se debería optimizar imágenes, usar caché y minificar recursos para una experiencia fluida, especialmente en dispositivos móviles.</t>
+          <t>The current layout doesn't explicitly display customer support or community features. Incorporating a dedicated help center, live chat, or a user forum would significantly boost user confidence and provide valuable resources for building or comparing PCs.</t>
         </is>
       </c>
     </row>
@@ -786,29 +786,13 @@
           <t>Final Conclusion</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Newegg es un referente en e-commerce de hardware. Su sólida interfaz, extenso catálogo y servicio al cliente lo posicionan como una opción preferente para entusiastas y profesionales de la tecnología, destacando en todos los criterios.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Amazon es un gigante del comercio electrónico. Su escala, conveniencia y experiencia de usuario optimizada, respaldadas por un robusto sistema logístico, lo convierten en una plataforma dominante y globalmente accesible para cualquier compra.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Micro Center sobresale en la venta minorista de componentes. Su combinación de presencia en línea y tiendas físicas, junto con un enfoque en el servicio experto, ofrece una experiencia de compra completa y especializada.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PCity presenta una base prometedora con un diseño limpio y navegación directa. Sus elementos visuales son claros, ofreciendo una experiencia básica pero funcional para el usuario. La usabilidad es notable, aunque sin lujos. Se enfoca en la simplicidad.</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>En general, el sitio presenta un diseño limpio y una navegación intuitiva, lo que son puntos fuertes. Las principales oportunidades de mejora residen en enriquecer la interactividad y la funcionalidad avanzada, así como en profundizar la estructura del contenido para ofrecer una experiencia más completa y distintiva a los usuarios.</t>
+          <t>El sitio de la imagen posee una base sólida con una interfaz limpia y una propuesta de valor clara para construir y comparar PCs. Para mejorar, debería expandir la interactividad con herramientas de configuración más robustas, optimizar la organización del contenido con categorías detalladas, y desarrollar una estrategia SEO y de comunidad más profunda. Se recomienda integrar más elementos visuales informativos y asegurar una accesibilidad completa para todos los usuarios.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,225 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tom's Hardware</t>
+          <t>Newegg.com: Se observa una tipografía clara y bien contrastada. El texto es fácilmente legible, con tamaños adecuados para el contenido principal y secundario.</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Newegg</t>
+          <t>PcComponentes.com: Presenta una combinación de fuentes que favorece la legibilidad. La jerarquía visual del texto está bien definida, mejorando la experiencia de lectura.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GamersNexus</t>
+          <t>Amazon.com (Sección de Componentes PC): Emplea fuentes estándar que aseguran una alta legibilidad en diversos dispositivos. La densidad del texto se gestiona para evitar la sobrecarga visual.</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pcity</t>
+          <t>Sitio Web de la Imagen: La selección tipográfica parece moderna y funcional. La claridad del texto es un punto fuerte, aunque el espaciado en algunos bloques podría optimizarse.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Utiliza una paleta de colores distintiva que refuerza su identidad. Los tonos fríos predominan, aportando una sensación de tecnología y profesionalismo.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: Su identidad de marca se transmite eficazmente a través de una paleta vibrante. Los colores se usan estratégicamente para destacar promociones y áreas clave.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Los colores reflejan una marca reconocida globalmente, con un uso consistente en elementos clave. La neutralidad del fondo permite que los productos resalten fácilmente.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: La paleta de colores es coherente con el sector tecnológico. La marca se expresa con tonos modernos y un logotipo bien integrado, aunque podría explorar más dinamismo en las llamadas a la acción.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Las imágenes de productos son de alta calidad y se complementan con gráficos informativos. Los iconos son intuitivos, facilitando la comprensión rápida del contenido.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: Incorpora elementos visuales atractivos y bien organizados. Las animaciones y los banners promocionales son impactantes sin distraer la navegación principal.</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Destaca por la gran cantidad de imágenes y vídeos de productos. La organización visual es crucial para manejar el vasto catálogo, utilizando miniaturas claras.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: Las imágenes de productos son nítidas y detalladas, con una buena integración en el diseño. Se usan gráficos claros, pero la variedad en los tipos de visuales podría ampliarse.</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Ofrece una navegación intuitiva y eficiente, con menús bien estructurados. La experiencia de usuario se optimiza con filtros avanzados y una búsqueda robusta.</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: La estructura de navegación es clara, permitiendo a los usuarios encontrar productos fácilmente. El flujo de compra se diseña para ser directo y sin fricciones.</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): La navegación es excepcionalmente funcional para un catálogo tan extenso. La experiencia de usuario se ve reforzada por un sistema de categorías y subcategorías detallado.</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: La navegación es lógica y los menús son accesibles. La experiencia del usuario es en general positiva, aunque el proceso de filtrado podría ser más prominente o intuitivo.</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: El contenido está lógicamente organizado en categorías claras. Las páginas de productos presentan una estructura uniforme, facilitando la comparación y la toma de decisiones.</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: La estructura del sitio es muy organizada, lo que facilita la exploración de productos. Las secciones están bien delimitadas, proporcionando un acceso rápido a la información relevante.</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Pese a su tamaño, mantiene una organización coherente y estructurada. La disposición de la información en las páginas de resultados y productos es predecible y sencilla.</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: La estructura general del sitio es coherente y fácil de seguir. La organización de las categorías de productos es clara, aunque la disposición de algunos elementos en la página de inicio podría ser más dinámica.</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Se esfuerza por ser accesible, aunque puede haber áreas de mejora en contraste. La compatibilidad con tecnologías de asistencia podría ser revisada para una mayor inclusión.</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: Implementa características básicas de accesibilidad, como texto alternativo en imágenes. Se observa un esfuerzo por cumplir con estándares, pero hay margen para optimizaciones adicionales.</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Considera la accesibilidad con opciones de visualización y navegación claras. La compatibilidad con diversos dispositivos y navegadores es un punto fuerte del diseño universal.</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: El sitio cumple con aspectos básicos de accesibilidad, como contraste de texto. Podría mejorar la navegación para usuarios con discapacidades visuales o motoras.</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Todas las funciones del sitio, desde la búsqueda hasta el carrito, operan sin fallos. La interactividad de los filtros y las opciones de personalización es fluida.</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: El sitio web es totalmente funcional, con un proceso de compra robusto y eficiente. Las herramientas de configuración de PC funcionan de manera precisa.</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): La funcionalidad del sitio es impecable, con un sistema de búsqueda potente y un carrito de compras fiable. Todas las características operan como se espera, brindando confianza al usuario.</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: La funcionalidad es sólida, con todas las herramientas de compra y navegación operativas. Los formularios funcionan correctamente, pero la velocidad de carga en algunas secciones podría ser optimizada.</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Ofrece diversas opciones de interacción, como comentarios y comparativas de productos. Los elementos interactivos están bien diseñados y responden de forma intuitiva.</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: Fomenta la interacción mediante reseñas de usuarios y un configurador de PCs. Los elementos interactivos están bien implementados, enriqueciendo la experiencia del comprador.</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Proporciona múltiples formas de interactuar, desde valoraciones hasta preguntas y respuestas. La experiencia interactiva está muy pulida, animando a la participación de la comunidad.</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: El sitio permite la interacción a través de reseñas de productos. Podría integrar más herramientas interactivas, como un chat en vivo o configuradores visuales, para enriquecer la experiencia.</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: El sitio utiliza URL amigables y metadescripciones optimizadas. El contenido está estructurado para ser fácilmente rastreable por los motores de búsqueda.</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: Las páginas están optimizadas con palabras clave relevantes y una estructura clara. Esto contribuye a un buen posicionamiento en los resultados de búsqueda.</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Demuestra una fuerte estrategia SEO con un gran volumen de contenido indexable. La autoridad de dominio es alta, lo que beneficia su visibilidad en búsquedas generales.</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: El sitio parece seguir prácticas básicas de SEO, con títulos y descripciones. La optimización de contenido para palabras clave específicas podría ser más agresiva.</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg.com: Mantiene una excelente velocidad de carga en la mayoría de sus páginas. La optimización de imágenes y scripts contribuye a un rendimiento general sobresaliente.</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>PcComponentes.com: Ofrece un rendimiento rápido y constante, incluso con elementos multimedia. La optimización del servidor y el almacenamiento en caché contribuyen a una navegación fluida.</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon.com (Sección de Componentes PC): Su infraestructura permite una carga rápida, a pesar de la complejidad del sitio. La experiencia del usuario se beneficia de la minimización de tiempos de espera en todas las secciones.</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Sitio Web de la Imagen: La velocidad de carga es aceptable en general, pero algunas páginas cargan más lento. La optimización de recursos y la implementación de técnicas de caché podrían mejorar esto.</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newegg.com: </t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PcComponentes.com: </t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon.com (Sección de Componentes PC): </t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sitio Web de la Imagen: </t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -466,29 +666,53 @@
           <t>Typography &amp; Readability</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Presenta un estilo tipográfico claro y profesional. Facilita la lectura de artículos extensos con buen contraste y tamaño de fuente, optimizando la experiencia de usuario.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Utiliza fuentes estándar de e-commerce, con buena legibilidad en listados de productos. La densidad de información podría beneficiarse de un enfoque más organizado, mejorando la claridad.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Exhibe una tipografía técnica y directa. Proporciona una experiencia de lectura enfocada en el detalle, ideal para usuarios que buscan información muy específica sobre hardware.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Emplea tipografía sencilla y legible. El texto principal es claro, pero la consistencia y jerarquía en diversas secciones podrían optimizarse para una mejor comprensión visual del contenido.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>The site in the image uses clear fonts for main headings and product names, but body text consistency and hierarchical sizing could enhance information consumption across various screen sizes.</t>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>Para mejorar, este sitio podría ajustar el espaciado entre líneas en ciertos elementos de texto. Mantener la legibilidad actual es crucial, y una revisión de la consistencia en estilos de párrafo sería beneficiosa.</t>
         </is>
       </c>
     </row>
@@ -498,29 +722,53 @@
           <t>Colors &amp; Branding</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mantiene una paleta de colores sobria y tecnológica. Su branding global es consistente, transmitiendo autoridad y fiabilidad en el ámbito de la tecnología.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Adopta una combinación de colores vibrante y comercial. El branding minorista es reconocible, con un enfoque claro en ofertas y categorías de productos destacadas.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Usa una estética oscura enfocada en el rendimiento. El branding es distintivo en su nicho, reflejando contenido técnico y análisis de hardware sin concesiones.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Presenta una combinación de azul brillante y blanco. El logo y esquema de color sugieren un enfoque moderno y accesible, aunque el branding general podría ser más sofisticado.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The color scheme is functional and distinctive, but expanding the brand identity beyond the basic blue and white, perhaps with secondary accent colors or graphic elements, could create a more memorable and unique user experience.</t>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>Para evolucionar, el sitio podría introducir acentos de color más audaces para elementos interactivos. Esto impulsaría la participación del usuario y fortalecería el reconocimiento de sus puntos focales.</t>
         </is>
       </c>
     </row>
@@ -530,29 +778,53 @@
           <t>Visual Elements</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Integra imágenes de alta calidad y gráficos informativos. Ofrece visuales pertinentes que complementan eficazmente sus extensas reseñas y análisis técnicos detallados.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Destaca por fotografías de productos claras y detalladas. Las imágenes cumplen su función de mostrar artículos, pero gráficos adicionales son limitados en su presentación general.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Incorpora imágenes de hardware detalladas y capturas de pantalla de benchmarks. Los elementos visuales son cruciales para sus análisis, apoyando la información técnica con evidencia gráfica.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Muestra imágenes de productos consistentes y bien alineadas. Las miniaturas de componentes populares son claras, pero la inclusión de gráficos o íconos adicionales realzaría la experiencia.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Product images are uniformly presented, which is a good starting point. However, incorporating more diverse visual elements such as infographics, comparison charts, or detailed product galleries could significantly improve user engagement and information retention.</t>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>El sitio podría beneficiarse de la adición de más elementos visuales interactivos. Implementar vídeos cortos de productos o vistas 360 grados mejoraría significativamente la experiencia de usuario y la decisión de compra.</t>
         </is>
       </c>
     </row>
@@ -562,29 +834,53 @@
           <t>Navigation &amp; UX</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ofrece navegación estructurada y lógica. La experiencia de usuario es intuitiva, permitiendo acceso rápido a categorías de productos, noticias y guías relevantes.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Proporciona navegación robusta orientada al comercio. La experiencia de usuario se centra en búsqueda y filtrado de productos, diseñada para facilitar transacciones eficientes.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Cuenta con navegación directa a sus categorías de contenido principal. La UX está diseñada para exploradores técnicos, priorizando el acceso a sus profundos análisis y videos.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Tiene una barra de navegación superior clara con enlaces esenciales. La experiencia de usuario parece sencilla, aunque opciones de filtrado o categorías secundarias no son visibles.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>The main navigation is clear and concise, offering immediate access to key sections. To enhance user experience, implementing more dynamic filters, detailed category breakdowns, and a consistent breadcrumb trail would be beneficial for deeper exploration.</t>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Mejorar la visibilidad y usabilidad de los filtros de búsqueda es una prioridad. Un sistema de filtrado más avanzado y fácilmente perceptible ayudaría a los usuarios a refinar sus elecciones con mayor rapidez y eficiencia.</t>
         </is>
       </c>
     </row>
@@ -594,29 +890,53 @@
           <t>Organization &amp; Structure</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Organiza su contenido en secciones bien definidas. La estructura facilita la búsqueda de información específica, categorizando artículos por tipo de componente y temática tecnológica.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Presenta organización de productos por categorías lógicas. La estructura está optimizada para la compra, con listados claros y opciones de clasificación para la elección del cliente.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Estructura su contenido por tipos de análisis y publicaciones. La organización es coherente con su enfoque en rendimiento de hardware, permitiendo encontrar rápidamente estudios detallados.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Muestra componentes populares en un diseño de cuadrícula ordenado. La organización es limpia y funcional, pero no se aprecian categorías avanzadas o árboles de productos.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>The current layout for popular components is clean and easy to scan. Expanding this structure to include clear hierarchical categories, advanced sorting options, and dedicated landing pages for different component types would greatly improve overall site navigability.</t>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Reorganizar ligeramente la página de inicio para destacar ofertas y novedades. Esto crearía un punto de entrada más atractivo y mantendría a los usuarios interesados en explorar el contenido actual.</t>
         </is>
       </c>
     </row>
@@ -626,29 +946,53 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Se esfuerza por buena accesibilidad en su contenido. Utiliza atributos ALT en imágenes y estructura HTML semántica, aunque siempre hay margen para mejoras.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Implementa características básicas de accesibilidad para su plataforma. Se enfoca en cumplir estándares para facilitar navegación y compra a un amplio rango de usuarios.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Prioriza la claridad del contenido. La accesibilidad es razonable, pero la complejidad técnica de algunos gráficos podría ser un desafío para usuarios con ciertas discapacidades.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Parece tener contraste de color adecuado para el texto principal. La disposición simple sugiere una accesibilidad básica, pero se necesita una evaluación completa.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>The high contrast between blue and white is a positive step for visual accessibility. Further improvements should focus on providing alternative text for all images, ensuring keyboard navigation, and implementing ARIA labels for interactive elements to support screen reader users.</t>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>Priorizar la implementación de una navegación más amigable para teclado. Asegurar que todos los elementos interactivos sean accesibles sin el uso del ratón abrirá el sitio a una audiencia más amplia y diversa.</t>
         </is>
       </c>
     </row>
@@ -658,29 +1002,53 @@
           <t>Functionality</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ofrece funcionalidad robusta para publicación de contenido. Incluye búsqueda avanzada, comentarios y una base de datos extensa de especificaciones de componentes.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Dispone de funcionalidad completa de comercio electrónico. Permite búsqueda de productos, gestión de carritos, procesamiento de pagos y seguimiento de pedidos, con experiencia fluida.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Proporciona funcionalidad para entrega de contenido multimedia. Integra videos y artículos, con herramientas para compartir y comentar, facilitando el engagement con su audiencia.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Presenta un buscador visible y enlaces a secciones clave. La función 'Arma tu PC' sugiere un configurador, indicando funcionalidad orientada a la utilidad del usuario.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>The presence of a search bar and a 'Build your PC' section indicates a focus on practical functionality. Enhancements could include advanced comparison tools, a more robust component compatibility checker within the builder, and real-time stock updates for parts.</t>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Optimizar la velocidad de carga de las páginas de productos es esencial. Un rendimiento más rápido reducirá la tasa de rebote y mejorará la percepción general de eficiencia y modernidad del sitio.</t>
         </is>
       </c>
     </row>
@@ -690,29 +1058,53 @@
           <t>Interactivity</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Permite comentarios en artículos y foros activos. Ofrece oportunidades de interacción para los usuarios, fomentando discusiones y el intercambio de conocimientos sobre tecnología.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Habilita reseñas de productos, preguntas y respuestas de usuarios. La interacción se centra en la comunidad de compradores, facilitando decisiones informadas y el soporte entre pares.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fomenta la interacción a través de comentarios en videos y artículos. La comunidad es activa, participando en debates técnicos, enriqueciendo el contenido con perspectivas adicionales.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>La imagen no muestra elementos interactivos más allá de navegación básica. Secciones como 'Arma tu PC' o 'Comparar' podrían ofrecer interfaces más dinámicas para el usuario.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>While basic navigation is present, the site could significantly benefit from more interactive elements. Implementing user ratings, a comment section, forums, or a more engaging 'Build your PC' wizard would foster a stronger community and user engagement.</t>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>La integración de un chat en vivo para soporte inmediato sería un gran añadido. Esto proporcionaría asistencia en tiempo real, resolviendo dudas rápidamente y mejorando la satisfacción del cliente.</t>
         </is>
       </c>
     </row>
@@ -722,77 +1114,165 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Aplica estrategias SEO sólidas para su vasto contenido. Su alta autoridad de dominio le permite posicionarse bien en búsquedas relacionadas con hardware y tecnología.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Maneja un SEO robusto enfocado en productos y categorías. Su optimización es clave para captar tráfico de búsqueda transaccional con descripciones y metadatos efectivos.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Optimiza su contenido para búsquedas de nicho y términos técnicos. Su SEO se centra en rendimiento y análisis detallados, atrayendo audiencia especializada en hardware para PC.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>La estructura de títulos y claridad del contenido son positivos para el SEO básico. La optimización de metadescripciones, encabezados y URLs amigables es crucial para visibilidad.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>The clear title and content visible suggest a good foundation for SEO. To improve organic reach, a focused strategy including keyword-rich content, optimized meta descriptions, structured data, and a robust internal linking structure should be developed.</t>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>Desarrollar una estrategia de contenido SEO más robusta es vital. Crear guías de compra, comparativas y artículos de blog con palabras clave relevantes atraerá más tráfico orgánico y establecerá el sitio como una autoridad.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Customer Support &amp; Community</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ofrece foros comunitarios activos y guías extensas. El soporte se centra en autoayuda a través de una rica base de conocimientos generada por expertos y usuarios.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Proporciona soporte al cliente integral y herramientas de comunidad. Incluye chat en vivo, RMA, FAQs y foros, facilitando una experiencia de compra asistida.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>No tiene soporte al cliente tradicional, pero sí una comunidad. Sus videos y artículos sirven como apoyo indirecto, respondiendo preguntas comunes a través del contenido.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>La imagen no revela información sobre soporte o comunidad explícita. La sección 'Información' podría albergar FAQs o enlaces de contacto para consultas de usuarios.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>The current layout doesn't explicitly display customer support or community features. Incorporating a dedicated help center, live chat, or a user forum would significantly boost user confidence and provide valuable resources for building or comparing PCs.</t>
+          <t>Performance y Velocidad de Carga</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Es fundamental invertir en la optimización de recursos, especialmente imágenes y scripts. Implementar Lazy Loading y mejorar el caché del navegador resultaría en una experiencia mucho más fluida.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Final Conclusion</t>
+          <t>Final Conclusion row</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>El sitio de la imagen posee una base sólida con una interfaz limpia y una propuesta de valor clara para construir y comparar PCs. Para mejorar, debería expandir la interactividad con herramientas de configuración más robustas, optimizar la organización del contenido con categorías detalladas, y desarrollar una estrategia SEO y de comunidad más profunda. Se recomienda integrar más elementos visuales informativos y asegurar una accesibilidad completa para todos los usuarios.</t>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>En general, el sitio de la imagen presenta una base sólida con buena legibilidad y funcionalidad. Sin embargo, hay un gran potencial para enriquecer la experiencia del usuario y aumentar la visibilidad. Sugiero enfocarse en elementos interactivos como un chat en vivo y un configurador de productos, mejorar la velocidad de carga de las páginas de detalles, optimizar la usabilidad de los filtros, y robustecer la estrategia de contenido SEO. Estas mejoras no solo atraerán a más usuarios, sino que también los mantendrán comprometidos, fortaleciendo la percepción de su marca en el mercado.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +451,10 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sitio Web de la Imagen</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr">
+          <t>https://www.pcity.com</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -472,11 +471,6 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Analiza la legibilidad del sitio de la imagen, la jerarquía visual del texto y la claridad de las fuentes. Sugiere mejoras para diferenciar el contenido y mejorar la experiencia de lectura.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -489,11 +483,6 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Evalúa el esquema de colores del sitio de la imagen, la coherencia de la marca y el uso general de la paleta. Ofrece ideas para reforzar su identidad visual y atractivo.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -506,11 +495,6 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Describe la calidad y relevancia de las imágenes y videos en el sitio de la imagen, así como su impacto visual. Proporciona sugerencias para una integración más efectiva y atractiva.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -523,11 +507,6 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Comenta sobre la facilidad de uso del sitio de la imagen, la lógica de su navegación y la experiencia general del usuario. Sugiere cómo optimizar la interacción y los flujos de tareas.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -540,11 +519,6 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Analiza cómo está estructurado el contenido en el sitio de la imagen, la coherencia de las secciones y la agrupación de información. Ofrece ideas para mejorar la claridad y accesibilidad de su arquitectura.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,11 +531,6 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Evalúa las características de accesibilidad del sitio de la imagen para usuarios con diversas necesidades. Propone mejoras para asegurar que el contenido sea utilizable para todos los públicos.</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -574,11 +543,6 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Describe la operatividad de las funciones del sitio de la imagen, la fiabilidad de sus herramientas y la ausencia de errores. Sugiere cómo optimizar el rendimiento y la estabilidad general.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -591,11 +555,6 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Comenta la presencia y efectividad de elementos interactivos en el sitio de la imagen, y cómo fomentan la participación del usuario. Proporciona ideas para aumentar el compromiso y la experiencia dinámica.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,16 +567,11 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Analiza las características de SEO observables en el sitio de la imagen, como la presencia de palabras clave y estructura de URLs. Sugiere estrategias para mejorar su visibilidad en buscadores.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Content Quality &amp; Depth</t>
+          <t>Content Quality</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -625,16 +579,11 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Evalúa la riqueza y exhaustividad del contenido del sitio de la imagen, la credibilidad de la información y su valor añadido. Ofrece recomendaciones para enriquecer la oferta informativa y su autoridad.</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Final Conclusion</t>
+          <t>Final Conclusion row</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -642,11 +591,6 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>El sitio web analizado de la imagen destaca por su robusta presentación de información técnica y una interfaz de usuario limpia. Se sugiere fortalecer la interactividad con herramientas personalizadas y optimizar aún más la accesibilidad para una audiencia más amplia. Las mejoras en la navegación móvil y la velocidad de carga de ciertos elementos visuales también podrían realzar significativamente la experiencia general del usuario.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,390 +425,790 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:AP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>criterion_or_website</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Website1</t>
+          <t>Un diseño profesional facilita la lectura. Utiliza fuentes claras que optimizan la comprensión de artículos técnicos extensos.</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Website2</t>
+          <t>Presenta una interfaz de texto concisa. Su tipografía es muy funcional y legible para la presentación detallada de componentes.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Website3</t>
+          <t>Ofrece un diseño comercial estándar. El texto es directo, optimizado para la rápida navegación y compra de productos.</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Website4</t>
+          <t>Demuestra una elección de fuentes contemporánea. El tamaño del texto es apropiado para una lectura cómoda y rápida de nombres de productos.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Emplea una paleta de colores típicamente tecnológica. Su marca se establece a través de tonos serios y una estética informativa robusta.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Utiliza un esquema de color minimalista. La interfaz sobria ayuda a destacar la información crítica de los componentes de PC.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Presenta colores corporativos reconocibles. El uso estratégico de estos tonos guía al usuario a través de la experiencia de compra.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Muestra una paleta de colores básica y funcional. El azul brillante del encabezado contrasta eficazmente con el fondo blanco general.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Incorpora gráficos complejos y fotos de alta calidad. Los elementos visuales complementan el análisis técnico y las comparativas de productos.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Se enfoca en imágenes de productos y tablas de datos. La simplicidad visual prioriza la funcionalidad sobre la estética elaborada.</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Exhibe imágenes de productos en alta resolución y banners promocionales. Los elementos gráficos son clave para la experiencia de venta minorista.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Presenta imágenes de productos claras y uniformes. Los iconos son sencillos y el diseño general es minimalista, facilitando el escaneo visual.</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ofrece una navegación extensa y jerárquica. La experiencia de usuario está diseñada para explorar artículos y reseñas en profundidad.</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Su navegación es altamente funcional y orientada a tareas. La interfaz guía al usuario en la construcción y comparación de PCs de manera lógica.</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>La navegación es típica de un gran minorista en línea. Los menús y filtros facilitan la búsqueda y descubrimiento de productos específicos.</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Dispone de una navegación simple e intuitiva. Los enlaces clave en el encabezado y la barra de búsqueda son fácilmente identificables para el usuario.</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Está organizado como una revista en línea. Los artículos se categorizan lógicamente, facilitando el acceso a información detallada y comparativas.</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Posee una estructura de base de datos. Los componentes se organizan sistemáticamente, permitiendo comparaciones exhaustivas y la creación de listas de construcción.</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Sigue una estructura de comercio electrónico estándar. Los productos se organizan por categorías y se presentan claramente en cuadrículas y listas.</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>La estructura es clara y jerárquica. El contenido se organiza en secciones bien definidas, con una prominente exhibición de componentes populares.</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Generalmente sigue buenas prácticas de accesibilidad. El contenido es adaptable para diferentes dispositivos y usuarios con diversas necesidades.</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Prioriza la accesibilidad para su interfaz de datos. La información se presenta de forma clara y accesible para un amplio público técnico.</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Aplica estándares de accesibilidad para comercio electrónico. Se esfuerza por hacer su plataforma usable para la mayor cantidad de clientes posible.</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Demuestra un buen contraste de colores y texto legible. El diseño simple favorece una experiencia de usuario potencialmente inclusiva para muchos.</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Ofrece funcionalidad de búsqueda, comentarios y filtros de artículos. Su plataforma es rica en herramientas para la investigación tecnológica.</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Su funcionalidad central es la compatibilidad de piezas. Permite a los usuarios construir y validar configuraciones de PC de manera eficiente.</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Proporciona una funcionalidad completa de comercio electrónico. Incluye carrito de compras, seguimiento de pedidos, y opciones de pago diversas.</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Presenta funciones básicas como búsqueda y navegación por categorías. Los enlaces 'Arma tu PC' y 'Comparar' sugieren funcionalidades avanzadas futuras.</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Fomenta la interacción a través de foros y comentarios. Los usuarios pueden participar en discusiones y compartir conocimientos técnicos.</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Promueve la interacción con listas de construcción compartidas. Permite a los usuarios votar, comentar y refinar configuraciones de PC.</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>La interactividad se centra en reseñas de usuarios y Q&amp;A. Los clientes pueden calificar productos y obtener respuestas a sus preguntas.</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>La interactividad visible es básica, con elementos como la barra de búsqueda. Los productos presentados probablemente son interactivos al hacer clic.</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Tiene una fuerte presencia SEO debido a su contenido. Sus artículos se posicionan bien para búsquedas relacionadas con hardware.</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Optimizado para SEO en la búsqueda de componentes. La estructura de datos facilita el rastreo y la indexación de productos específicos.</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Muy fuerte en SEO para productos de comercio electrónico. La optimización ayuda a los usuarios a encontrar productos directamente a través de motores de búsqueda.</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>La estructura de encabezados y el contenido de texto visible son adecuados. Una optimización más profunda de metadatos y enlaces internos podría impulsar su visibilidad.</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Puede ser algo pesado debido a la publicidad. A pesar de esto, se esfuerza por mantener una buena velocidad de carga para sus artículos.</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Generalmente ofrece una experiencia de carga rápida. La eficiencia en la presentación de datos contribuye a un rendimiento ágil.</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Se esfuerza por una carga rápida pese a su complejidad. Optimiza imágenes y scripts para una experiencia de compra fluida.</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>El diseño es limpio y minimalista. Esto sugiere una base para una carga de página rápida, esencial para la retención del usuario.</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>conclusion</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Branding y posicionamiento</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Newegg: e-commerce de tecnología y PC parts con foco en ofertas y variedad.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PCMag: medio editorial de reviews, guías y noticias tech con alta autoridad.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Tom's Hardware: portal para entusiastas con comparativas, guías y builds.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Define una propuesta de valor clara (precio, variedad, asesoría); crea un logotipo legible; añade un tagline visible en el hero que diferencie a PC Market.</t>
+          <t>Typography &amp; Readability</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>El diseño tipográfico es moderno y legible, sin embargo, se podría mejorar el contraste en ciertas áreas para asegurar una accesibilidad óptima para todos los usuarios.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Estructura de navegación</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Mega menú amplio por categorías, acceso rápido a ofertas y marcas.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Navegación por tipos de contenido (reviews, best picks, news).</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Menús por componentes, guías y foros; enfoque temático.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Limita el menú a 5–7 categorías principales; integra barra de búsqueda prominente; usa header pegajoso con accesos a cuenta y carrito.</t>
+          <t>Colors &amp; Branding</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>La elección de colores es limpia y funcional. Podría beneficiarse de la introducción de una paleta de acento secundaria para reforzar la identidad y guiar la atención del usuario.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hero y propuesta de valor</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Hero con promociones destacadas y ofertas temporales.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Destaca artículos y rankings en portada.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Destaca guías y comparativas recientes en el hero.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Usa hero estático con USP clara y un CTA principal; evita carruseles; muestra beneficios (envío, garantía, devoluciones) en una franja bajo el hero.</t>
+          <t>Visual Elements</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Los elementos visuales son concisos y bien organizados, especialmente las imágenes de productos. La integración de ilustraciones o íconos más distintivos podría enriquecer la experiencia sin sobrecargar.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Buscador y filtrado</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Buscador con autocompletar y filtros facetados profundos.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Búsqueda por productos y artículos con etiquetas.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Búsqueda por temas y componentes; filtros básicos.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Implementa autocompletar con sugerencias y categorías; filtros por marca, precio, uso y compatibilidad; chips de filtros removibles.</t>
+          <t>Navigation &amp; UX</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>La navegación es directa y fácil de entender, lo cual es un punto fuerte. Para mejorar, se podría considerar una barra de navegación fija o más opciones de filtrado en las categorías de productos.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jerarquía visual y escaneabilidad</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tarjetas de producto con precio y badges; denso en información.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tipografía clara y listados con puntuaciones visibles.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Diseños con tablas y listados técnicos; mucha data.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Usa 2–3 tamaños tipográficos, suficiente espacio en blanco y un grid consistente; prioriza precio, rating y CTA en tarjetas.</t>
+          <t>Organization &amp; Structure</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>La organización del contenido es lógica y fácil de seguir. Una mejora podría ser la adición de subcategorías más detalladas o filtros avanzados para productos.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CTAs y flujo de compra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CTAs Add to Cart visibles; checkout conocido y rápido.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CTAs editoriales (Leer reseña, Mejores); enlaces afiliados.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CTAs a guías y recomendaciones; menos transaccional.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CTA principal contrastado y persistente; mini-carrito accesible; reduce pasos del checkout y permite guest checkout.</t>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Los elementos de contraste y el tamaño de la fuente son adecuados, lo cual es positivo. Se recomienda verificar la compatibilidad con lectores de pantalla y la navegación por teclado para una accesibilidad completa.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Contenido editorial y guías</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Hubs de recomendaciones y ofertas; contenido de apoyo.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Comparativas y reviews extensas y actualizadas.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Guías de compra y builds detalladas con benchmarks.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Integra blog/guías enlazadas desde categorías; módulos de Top picks en listados; estructura de clúster SEO por uso (gaming, oficina, creator).</t>
+          <t>Functionality</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Las funciones básicas son claras y operativas. Expandir las capacidades de 'Arma tu PC' y 'Comparar' con herramientas interactivas podría distinguirlo significativamente.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Señales de confianza</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ratings, reviews verificadas, garantías y marcas reconocidas.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Autoridad editorial y sellos de Editors’ Choice.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Reputación de comunidad y foros activos.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Muestra reseñas verificadas, políticas claras y sellos de pago seguro; destaca soporte y devoluciones; usa microcopy sobre stock y tiempos.</t>
+          <t>Interactivity</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>La interfaz es limpia, pero la interactividad actual es limitada. La incorporación de elementos como filtros dinámicos o valoraciones de usuarios podría enriquecer notablemente la experiencia.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rendimiento y carga percibida</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Contenido pesado con lazy load y muchos módulos.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Optimización aceptable con presencia de anuncios.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Páginas largas con tablas; rendimiento moderado.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Optimiza imágenes (WebP/AVIF), lazy load y fuentes; minimiza scripts de terceros; apunta a buenas Core Web Vitals.</t>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>La estructura del sitio es favorable para el SEO básico. Implementar etiquetas alt en imágenes, descripciones meta enriquecidas y un sitemap XML robusto potenciaría su posicionamiento.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Responsividad móvil</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Interfaz tipo app; filtros deslizables; puede saturar.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Lectura cómoda y menús simplificados.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Scroll largo con tablas adaptadas.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Menú inferior en móvil, filtros colapsables y CTA sticky; zonas táctiles amplias y navegación con pulgar.</t>
+          <t>Performance &amp; Loading Speed</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>El diseño ligero es una ventaja para la velocidad de carga. Continuar optimizando imágenes, minimizar scripts y aprovechar el almacenamiento en caché mejorará aún más el rendimiento.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Accesibilidad y SEO on-page</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Breadcrumbs y schema de producto; contraste variable.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Schema de artículo y headings claros; buenas breadcrumbs.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Headings adecuados; alt y tablas a veces irregulares.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Referencia a la futura imagen final del sitio “PC Market”.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Incluye alt text, contraste AA, estados de foco y accesos por teclado; schema Product/FAQ; URLs limpias y meta títulos orientados a intención.</t>
+          <t>Final Conclusion</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>El sitio muestra una base sólida con un diseño limpio y una navegación intuitiva. Destaca por su claridad y enfoque directo en los componentes. Para evolucionar, podría integrar más interactividad, opciones de personalización, herramientas de construcción de PC más robustas y una estrategia SEO ampliada para competir eficazmente con los líderes del mercado.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:AT12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,225 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tom's Hardware</t>
+          <t>Newegg - Emplea una tipografía clara y moderna para los listados de productos. Facilita la lectura de especificaciones detalladas.</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PC Part Picker</t>
+          <t>Amazon - Utiliza fuentes limpias y tamaños ajustables para diversos contenidos. Mantiene una alta legibilidad en descripciones y reseñas.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Newegg</t>
+          <t>Micro Center - Presenta textos con una fuente sans-serif estándar que asegura la claridad. La información de los productos es fácil de escanear y comprender.</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PCity</t>
+          <t>B&amp;H Photo Video - Se observan fuentes nítidas y consistentes en todo el portal. La lectura de las fichas técnicas resulta cómoda y fluida.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - La marca se distingue por una paleta de colores vibrantes con acentos rojos y azules. Refleja una imagen de tecnología y dinamismo.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - La identidad visual se basa en tonos azules y blancos, que transmiten confianza y seriedad. El logo es reconocido globalmente por su simplicidad.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Una combinación de colores sobrios y detalles en verde esmeralda define su estética. El diseño general es profesional y enfocado al hardware.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - La marca emplea una paleta de colores azul y blanco, con toques de naranja para llamadas a la acción. El branding proyecta una imagen de fiabilidad y experiencia.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Se caracteriza por imágenes de alta resolución de productos desde múltiples ángulos. Los videos y configuradores 3D enriquecen la experiencia visual.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - Presenta una gran variedad de imágenes de producto, a menudo con zooms detallados. Las infografías y comparativas son frecuentes en sus páginas.</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Destaca por las fotografías de calidad profesional de componentes y sistemas. Los gráficos ilustrativos ayudan a comprender características técnicas.</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - Ofrece fotografías de producto impecables y claras, acompañadas de miniaturas bien organizadas. Los elementos gráficos son limpios y funcionales, aunque no abundan los videos.</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Dispone de menús de categorías detallados y un potente motor de búsqueda con filtros avanzados. La experiencia del usuario es eficiente para encontrar productos específicos.</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - La navegación es intuitiva gracias a un diseño familiar y una barra de búsqueda prominente. El proceso de compra está optimizado para la sencillez.</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Ofrece un sistema de navegación claro con categorías bien definidas y filtros eficaces. La experiencia de usuario es directa y centrada en la búsqueda de hardware.</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - La navegación es lógica y estructurada, con un menú principal bien organizado y una búsqueda efectiva. Los usuarios pueden encontrar rápidamente lo que buscan sin confusión.</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - El contenido está organizado de manera lógica con secciones claras para productos, guías y ofertas. La arquitectura de la información es profunda pero accesible.</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - La estructura del contenido es amplia, categorizando millones de productos de forma eficaz. Las páginas de producto están bien segmentadas con toda la información relevante.</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Presenta una estructura de sitio bien definida, separando claramente productos, servicios y recursos. La jerarquía de la información es fácil de seguir.</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - La disposición de los elementos es ordenada y coherente, con categorías de producto claramente definidas y submenús intuitivos. La información se presenta de forma concisa y bien distribuida.</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Se esfuerza por ofrecer opciones de accesibilidad, como compatibilidad con lectores de pantalla. Permite a un público amplio interactuar con el contenido.</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - Incorpora características de accesibilidad como descripciones de imágenes y navegación por teclado. Se mantiene un compromiso para ser inclusivo con todos los usuarios.</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Considera la accesibilidad básica en su diseño web. Busca garantizar que la información esencial sea accesible para la mayoría de los usuarios.</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - El diseño web cumple con estándares básicos de accesibilidad, aunque hay margen para mejoras en contraste y navegación asistida. La experiencia para usuarios con necesidades especiales es funcional.</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Proporciona herramientas robustas como creadores de PC personalizados y comparadores de productos. La funcionalidad del carrito de compras es fluida y segura.</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - Ofrece una funcionalidad completa que incluye seguimiento de pedidos, listas de deseos y múltiples opciones de pago. La plataforma soporta un vasto ecosistema de servicios.</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Incluye funciones clave como constructores de PC, filtros de búsqueda avanzados y soporte en línea. La experiencia de compra es directa y sin complicaciones.</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - Las características funcionales son sólidas, con un carrito de compras eficiente y un sistema de gestión de cuentas completo. La búsqueda por filtros funciona de manera fiable y rápida.</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Fomenta la interacción a través de reseñas de usuarios, foros y soporte en vivo. Los elementos interactivos mejoran la toma de decisiones del comprador.</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - Permite la interacción mediante reseñas de productos, preguntas y respuestas, y recomendaciones personalizadas. Fomenta una comunidad activa de compradores.</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Ofrece algunas características interactivas como reseñas de clientes y un chat de soporte. Busca facilitar la comunicación y resolución de dudas.</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - La interacción se centra en las reseñas de productos, el soporte al cliente y las opciones de personalización de cuenta. Podría beneficiarse de más elementos dinámicos.</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Está optimizado para motores de búsqueda con una buena estructura de URLs y contenido relevante. Ocupa posiciones destacadas para términos relacionados con componentes de PC.</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - Posee una estrategia de SEO robusta, capitalizando su autoridad de dominio para clasificar alto en diversas búsquedas. Su contenido está bien indexado.</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Mantiene una presencia sólida en los resultados de búsqueda para términos de hardware. La optimización SEO permite que los usuarios encuentren fácilmente sus productos.</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - La optimización para motores de búsqueda es efectiva, con una buena indexación de productos y metadatos relevantes. Se clasifica bien para términos específicos de fotografía y video.</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Newegg - Exhibe una velocidad de carga rápida, optimizando la experiencia del usuario. La eficiencia en la entrega de contenido es un pilar fundamental.</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Amazon - Muestra tiempos de carga generalmente eficientes, a pesar de la gran cantidad de contenido. Las imágenes y scripts están bien optimizados.</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Micro Center - Ofrece un buen rendimiento y velocidad de carga para la mayoría de sus páginas. La experiencia es fluida para los usuarios al navegar por el inventario.</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>B&amp;H Photo Video - La plataforma carga de manera consistente y rápida en la mayoría de los dispositivos, garantizando una experiencia de usuario fluida. Los recursos están bien optimizados para la entrega veloz del contenido.</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Newegg - </t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon - </t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Micro Center - </t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B&amp;H Photo Video - </t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -471,6 +671,46 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -483,6 +723,46 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,6 +775,46 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -507,6 +827,46 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -519,6 +879,46 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -531,6 +931,46 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -543,6 +983,46 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -555,6 +1035,46 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -567,11 +1087,51 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance &amp; Loading Speed</t>
+          <t>Rendimiento y Velocidad de Carga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -579,6 +1139,46 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -590,9 +1190,49 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>La plataforma destaca por su clara presentación visual de componentes y una navegación intuitiva. Potenciales mejoras incluyen refinar la coherencia de la tipografía y expandir las opciones de personalización para el usuario.</t>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>El sitio web analizado destaca por su navegación intuitiva y la alta calidad de sus imágenes de producto, facilitando una experiencia de usuario clara y funcional. Sin embargo, podría mejorar en la integración de más elementos interactivos y en la ampliación de sus características de accesibilidad para un público más diverso. Potenciar el uso de videos explicativos y comparativas directas con la competencia fortalecería su propuesta de valor.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT12"/>
+  <dimension ref="A1:AP12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,225 +436,205 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Emplea una tipografía clara y moderna para los listados de productos. Facilita la lectura de especificaciones detalladas.</t>
+          <t>Utiliza una tipografía sans-serif moderna y limpia. Los tamaños de texto y el espaciado aseguran una lectura cómoda en todo el contenido.</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Utiliza fuentes limpias y tamaños ajustables para diversos contenidos. Mantiene una alta legibilidad en descripciones y reseñas.</t>
+          <t>Emplea una fuente sans-serif clara para una legibilidad constante en contenido diverso. La jerarquía textual facilita el escaneo rápido de información.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Presenta textos con una fuente sans-serif estándar que asegura la claridad. La información de los productos es fácil de escanear y comprender.</t>
+          <t>Presenta una tipografía sans-serif contemporánea con buen contraste. La elección general de fuentes facilita la lectura de especificaciones y navegación.</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - Se observan fuentes nítidas y consistentes en todo el portal. La lectura de las fichas técnicas resulta cómoda y fluida.</t>
+          <t>Muestra una fuente sans-serif directa, ofreciendo legibilidad básica. Los tamaños de texto son adecuados para títulos, pero pequeños para detalles de productos.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - La marca se distingue por una paleta de colores vibrantes con acentos rojos y azules. Refleja una imagen de tecnología y dinamismo.</t>
+          <t>Usa una distintiva combinación de colores negro, rojo y blanco. Esta paleta crea una imagen profesional y tecnológica, mejorando el atractivo visual.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - La identidad visual se basa en tonos azules y blancos, que transmiten confianza y seriedad. El logo es reconocido globalmente por su simplicidad.</t>
+          <t>Definido por un icónico acento naranja sobre una interfaz blanca y azul. La paleta simple refuerza una identidad de marca amigable y confiable.</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Una combinación de colores sobrios y detalles en verde esmeralda define su estética. El diseño general es profesional y enfocado al hardware.</t>
+          <t>Presenta un esquema reconocible de azul y blanco con toques. Esta combinación establece una apariencia limpia y profesional, alineada con su enfoque tecnológico.</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - La marca emplea una paleta de colores azul y blanco, con toques de naranja para llamadas a la acción. El branding proyecta una imagen de fiabilidad y experiencia.</t>
+          <t>Aprovecha una simple combinación de colores azul y blanco. Esta paleta mínima establece una base visual limpia, pero carece de elementos de marca únicos.</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Se caracteriza por imágenes de alta resolución de productos desde múltiples ángulos. Los videos y configuradores 3D enriquecen la experiencia visual.</t>
+          <t>Muestra imágenes de productos de alta calidad y gráficos detallados. Integra videos y contenido generado por usuarios, enriqueciendo la experiencia visual.</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Presenta una gran variedad de imágenes de producto, a menudo con zooms detallados. Las infografías y comparativas son frecuentes en sus páginas.</t>
+          <t>Posee una amplia imaginería de productos, a menudo con múltiples ángulos. Los iconos son funcionales, apoyando eficazmente el viaje del usuario.</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Destaca por las fotografías de calidad profesional de componentes y sistemas. Los gráficos ilustrativos ayudan a comprender características técnicas.</t>
+          <t>Presenta fotos nítidas de productos y gráficos informativos claros. Los elementos visuales se centran en el detalle del producto, ayudando en las decisiones de compra.</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - Ofrece fotografías de producto impecables y claras, acompañadas de miniaturas bien organizadas. Los elementos gráficos son limpios y funcionales, aunque no abundan los videos.</t>
+          <t>Muestra imágenes de productos pequeñas pero claras en una cuadrícula. Los elementos visuales son mínimos, enfocándose solo en la exhibición del producto.</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Dispone de menús de categorías detallados y un potente motor de búsqueda con filtros avanzados. La experiencia del usuario es eficiente para encontrar productos específicos.</t>
+          <t>Ofrece una navegación intuitiva por categorías y filtros avanzados. La experiencia del usuario está optimizada para el descubrimiento de componentes.</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - La navegación es intuitiva gracias a un diseño familiar y una barra de búsqueda prominente. El proceso de compra está optimizado para la sencillez.</t>
+          <t>Proporciona capacidades de búsqueda robustas y recomendaciones personalizadas. Su navegación refinada permite explorar sin esfuerzo un vasto catálogo.</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Ofrece un sistema de navegación claro con categorías bien definidas y filtros eficaces. La experiencia de usuario es directa y centrada en la búsqueda de hardware.</t>
+          <t>Presenta un menú bien estructurado y opciones de filtrado eficaces. La experiencia de usuario del sitio facilita búsquedas rápidas y procesos de pago fluidos.</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - La navegación es lógica y estructurada, con un menú principal bien organizado y una búsqueda efectiva. Los usuarios pueden encontrar rápidamente lo que buscan sin confusión.</t>
+          <t>Muestra una barra de navegación superior sencilla con secciones clave. La experiencia de usuario parece directa, adecuada para acceso rápido a funciones.</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - El contenido está organizado de manera lógica con secciones claras para productos, guías y ofertas. La arquitectura de la información es profunda pero accesible.</t>
+          <t>Adopta un diseño clásico de comercio electrónico con categorías de productos claras. El contenido está lógicamente agrupado, facilitando la navegación eficiente.</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - La estructura del contenido es amplia, categorizando millones de productos de forma eficaz. Las páginas de producto están bien segmentadas con toda la información relevante.</t>
+          <t>Emplea una estructura de contenido altamente modular y personalizada. Su organización prioriza eficientemente la información relevante y los listados de productos.</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Presenta una estructura de sitio bien definida, separando claramente productos, servicios y recursos. La jerarquía de la información es fácil de seguir.</t>
+          <t>Utiliza un diseño estándar basado en cuadrícula para productos y categorías. La arquitectura del sitio es lógica, asegurando un flujo de información coherente.</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - La disposición de los elementos es ordenada y coherente, con categorías de producto claramente definidas y submenús intuitivos. La información se presenta de forma concisa y bien distribuida.</t>
+          <t>Sigue un flujo de contenido simple y lineal del encabezado a la cuadrícula. La estructura es básica y clara, priorizando el acceso directo a componentes populares.</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Se esfuerza por ofrecer opciones de accesibilidad, como compatibilidad con lectores de pantalla. Permite a un público amplio interactuar con el contenido.</t>
+          <t>Implementa características de accesibilidad estándar para navegación y contenido. El sitio busca una experiencia útil para una amplia gama de usuarios.</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Incorpora características de accesibilidad como descripciones de imágenes y navegación por teclado. Se mantiene un compromiso para ser inclusivo con todos los usuarios.</t>
+          <t>Generalmente se adhiere a las pautas de accesibilidad web, con navegación por teclado. Se esfuerza por ser inclusivo para usuarios con diversas capacidades.</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Considera la accesibilidad básica en su diseño web. Busca garantizar que la información esencial sea accesible para la mayoría de los usuarios.</t>
+          <t>Muestra esfuerzos en accesibilidad, incluyendo buen contraste de color. El sitio está diseñado para ser utilizable por diversas audiencias.</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - El diseño web cumple con estándares básicos de accesibilidad, aunque hay margen para mejoras en contraste y navegación asistida. La experiencia para usuarios con necesidades especiales es funcional.</t>
+          <t>Presenta un buen contraste de color en el encabezado principal y el texto. Se requiere más análisis para confirmar la navegación completa con teclado y compatibilidad.</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Proporciona herramientas robustas como creadores de PC personalizados y comparadores de productos. La funcionalidad del carrito de compras es fluida y segura.</t>
+          <t>Ofrece búsqueda robusta, filtros de productos detallados y procesos de pago seguros. Las funciones clave operan de manera confiable, apoyando una experiencia de compra fluida.</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Ofrece una funcionalidad completa que incluye seguimiento de pedidos, listas de deseos y múltiples opciones de pago. La plataforma soporta un vasto ecosistema de servicios.</t>
+          <t>Proporciona búsqueda avanzada, pedidos con un clic y gestión integral de cuentas. Sus funcionalidades están altamente optimizadas para velocidad y comodidad del usuario.</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Incluye funciones clave como constructores de PC, filtros de búsqueda avanzados y soporte en línea. La experiencia de compra es directa y sin complicaciones.</t>
+          <t>Ofrece búsqueda eficaz, filtrado por varios atributos y un embudo de compra fluido. Las funcionalidades principales funcionan eficientemente para un viaje satisfactorio.</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - Las características funcionales son sólidas, con un carrito de compras eficiente y un sistema de gestión de cuentas completo. La búsqueda por filtros funciona de manera fiable y rápida.</t>
+          <t>Parece incluir una barra de búsqueda básica y herramientas implícitas 'Arma tu PC'. Las funcionalidades principales están presentes, pero su robustez necesita evaluación.</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Fomenta la interacción a través de reseñas de usuarios, foros y soporte en vivo. Los elementos interactivos mejoran la toma de decisiones del comprador.</t>
+          <t>Integra reseñas de usuarios, secciones de preguntas y respuestas y foros comunitarios. El sitio fomenta una interacción significativa en torno a la información del producto.</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Permite la interacción mediante reseñas de productos, preguntas y respuestas, y recomendaciones personalizadas. Fomenta una comunidad activa de compradores.</t>
+          <t>Presenta extensas reseñas de clientes, calificaciones y recomendaciones personalizadas. Sus elementos interactivos fomentan la participación del usuario y decisiones informadas.</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Ofrece algunas características interactivas como reseñas de clientes y un chat de soporte. Busca facilitar la comunicación y resolución de dudas.</t>
+          <t>Incluye reseñas de usuarios, preguntas sobre productos y un chat de servicio al cliente. Las características interactivas apoyan la toma de decisiones del usuario.</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - La interacción se centra en las reseñas de productos, el soporte al cliente y las opciones de personalización de cuenta. Podría beneficiarse de más elementos dinámicos.</t>
+          <t>Muestra tarjetas de productos clicables y un campo de entrada de búsqueda. Más allá de esto, elementos interactivos específicos no son evidentes.</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Está optimizado para motores de búsqueda con una buena estructura de URLs y contenido relevante. Ocupa posiciones destacadas para términos relacionados con componentes de PC.</t>
+          <t>Implementa prácticas SEO sólidas con contenido rico en palabras clave y sitemap. El sitio se posiciona bien para búsquedas específicas de componentes de PC.</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Posee una estrategia de SEO robusta, capitalizando su autoridad de dominio para clasificar alto en diversas búsquedas. Su contenido está bien indexado.</t>
+          <t>Se beneficia de un vasto contenido y alta autoridad de dominio. Su estrategia SEO es integral, asegurando una visibilidad amplia en todas las categorías.</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Mantiene una presencia sólida en los resultados de búsqueda para términos de hardware. La optimización SEO permite que los usuarios encuentren fácilmente sus productos.</t>
+          <t>Aplica estrategias SEO dirigidas para páginas de productos y categorías. El sitio optimiza para palabras clave relevantes, mejorando la presencia en búsquedas.</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - La optimización para motores de búsqueda es efectiva, con una buena indexación de productos y metadatos relevantes. Se clasifica bien para términos específicos de fotografía y video.</t>
+          <t>Presenta títulos claros y una estructura simple, bases para un buen SEO. Se recomienda optimización para palabras clave, meta descripciones y móvil.</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Newegg - Exhibe una velocidad de carga rápida, optimizando la experiencia del usuario. La eficiencia en la entrega de contenido es un pilar fundamental.</t>
+          <t>Generalmente ofrece buenas velocidades de carga y respuestas eficientes del servidor. El sitio busca una experiencia fluida en todos los dispositivos.</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Amazon - Muestra tiempos de carga generalmente eficientes, a pesar de la gran cantidad de contenido. Las imágenes y scripts están bien optimizados.</t>
+          <t>Logra un rendimiento excelente con activos altamente optimizados y CDN. Sus páginas se cargan muy rápido, proporcionando una experiencia de usuario perfecta.</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Micro Center - Ofrece un buen rendimiento y velocidad de carga para la mayoría de sus páginas. La experiencia es fluida para los usuarios al navegar por el inventario.</t>
+          <t>Muestra buenos tiempos de carga de página, utilizando almacenamiento en caché. El sitio funciona de manera fiable, garantizando una interfaz de usuario receptiva.</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>B&amp;H Photo Video - La plataforma carga de manera consistente y rápida en la mayoría de los dispositivos, garantizando una experiencia de usuario fluida. Los recursos están bien optimizados para la entrega veloz del contenido.</t>
+          <t>Presenta un diseño simple, sugiriendo tiempos de carga inicial potencialmente rápidos. La optimización de imágenes y el caché podrían mejorar su velocidad.</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Newegg - </t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amazon - </t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Micro Center - </t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B&amp;H Photo Video - </t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -706,11 +686,11 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -758,11 +738,11 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -810,11 +790,11 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -862,11 +842,11 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -914,11 +894,11 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -966,11 +946,11 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1018,11 +998,11 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1070,11 +1050,11 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1122,16 +1102,16 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rendimiento y Velocidad de Carga</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1174,16 +1154,16 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Final Conclusion</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1226,13 +1206,9 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>El sitio web analizado destaca por su navegación intuitiva y la alta calidad de sus imágenes de producto, facilitando una experiencia de usuario clara y funcional. Sin embargo, podría mejorar en la integración de más elementos interactivos y en la ampliación de sus características de accesibilidad para un público más diverso. Potenciar el uso de videos explicativos y comparativas directas con la competencia fortalecería su propuesta de valor.</t>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Este sitio web muestra una base sólida con una interfaz limpia y una navegación directa. Para mejorar, se podría enriquecer la experiencia visual con imágenes de mayor tamaño y contenido multimedia, similar a las prácticas de líderes del sector. La interactividad para los usuarios, como las secciones de preguntas y respuestas o las reseñas detalladas, potenciaría la comunidad y la confianza. Además, una revisión de la accesibilidad y la implementación de funcionalidades avanzadas en las herramientas de 'Arma tu PC' y 'Comparar' elevarían la propuesta de valor. La optimización SEO, incluyendo meta descripciones y un blog con contenido relevante, atraería más tráfico orgánico. Finalmente, asegurar una velocidad de carga consistentemente rápida en todos los dispositivos garantizaría una experiencia de usuario superior.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,202 +436,202 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Utiliza una tipografía sans-serif moderna y limpia. Los tamaños de texto y el espaciado aseguran una lectura cómoda en todo el contenido.</t>
+          <t>Presenta tipografías claras y tamaños óptimos, facilitando la lectura en diversos dispositivos.</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Emplea una fuente sans-serif clara para una legibilidad constante en contenido diverso. La jerarquía textual facilita el escaneo rápido de información.</t>
+          <t>Utiliza fuentes modernas que mejoran la estética, aunque interlineado optimizable en móvil.</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Presenta una tipografía sans-serif contemporánea con buen contraste. La elección general de fuentes facilita la lectura de especificaciones y navegación.</t>
+          <t>Combina fuentes funcionales con toques distintivos, manteniendo excelente legibilidad en todos los textos.</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Muestra una fuente sans-serif directa, ofreciendo legibilidad básica. Los tamaños de texto son adecuados para títulos, pero pequeños para detalles de productos.</t>
+          <t>Utiliza tipografías claras y simples, con buena jerarquía para títulos y descripciones de productos.</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Usa una distintiva combinación de colores negro, rojo y blanco. Esta paleta crea una imagen profesional y tecnológica, mejorando el atractivo visual.</t>
+          <t>Paleta de colores profesional y consistente, refuerza la identidad de marca de forma sutil y efectiva.</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Definido por un icónico acento naranja sobre una interfaz blanca y azul. La paleta simple refuerza una identidad de marca amigable y confiable.</t>
+          <t>Usa colores vibrantes para destacar promociones, manteniendo equilibrio con tonos corporativos.</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Presenta un esquema reconocible de azul y blanco con toques. Esta combinación establece una apariencia limpia y profesional, alineada con su enfoque tecnológico.</t>
+          <t>El esquema de color es coherente con su imagen de marca, empleando contrastes adecuados.</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Aprovecha una simple combinación de colores azul y blanco. Esta paleta mínima establece una base visual limpia, pero carece de elementos de marca únicos.</t>
+          <t>Predomina un esquema azul y blanco, estableciendo una marca funcional y directa.</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Muestra imágenes de productos de alta calidad y gráficos detallados. Integra videos y contenido generado por usuarios, enriqueciendo la experiencia visual.</t>
+          <t>Incorpora imágenes de alta calidad y gráficos descriptivos que enriquecen la información del contenido.</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Posee una amplia imaginería de productos, a menudo con múltiples ángulos. Los iconos son funcionales, apoyando eficazmente el viaje del usuario.</t>
+          <t>Depende de imágenes impactantes y vídeos cortos para comunicar, equilibrando espacios en blanco.</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Presenta fotos nítidas de productos y gráficos informativos claros. Los elementos visuales se centran en el detalle del producto, ayudando en las decisiones de compra.</t>
+          <t>Sus elementos visuales son estéticos y funcionales, apoyando navegación y destacando ofertas.</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Muestra imágenes de productos pequeñas pero claras en una cuadrícula. Los elementos visuales son mínimos, enfocándose solo en la exhibición del producto.</t>
+          <t>Muestra imágenes de productos bien organizadas en cuadrícula, con tamaños uniformes y fondos limpios.</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Ofrece una navegación intuitiva por categorías y filtros avanzados. La experiencia del usuario está optimizada para el descubrimiento de componentes.</t>
+          <t>Ofrece navegación intuitiva y menús claros, permitiendo a usuarios encontrar información rápidamente.</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Proporciona capacidades de búsqueda robustas y recomendaciones personalizadas. Su navegación refinada permite explorar sin esfuerzo un vasto catálogo.</t>
+          <t>La experiencia de usuario es fluida con navegación lógica y fácil acceso a categorías principales.</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Presenta un menú bien estructurado y opciones de filtrado eficaces. La experiencia de usuario del sitio facilita búsquedas rápidas y procesos de pago fluidos.</t>
+          <t>Presenta navegación sencilla y eficiente, con un diseño que prioriza la comodidad del usuario.</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Muestra una barra de navegación superior sencilla con secciones clave. La experiencia de usuario parece directa, adecuada para acceso rápido a funciones.</t>
+          <t>La navegación superior es concisa y evidente, permitiendo acceso rápido a secciones clave.</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Adopta un diseño clásico de comercio electrónico con categorías de productos claras. El contenido está lógicamente agrupado, facilitando la navegación eficiente.</t>
+          <t>La información está organizada jerárquicamente, facilitando comprensión y rastreo por buscadores.</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Emplea una estructura de contenido altamente modular y personalizada. Su organización prioriza eficientemente la información relevante y los listados de productos.</t>
+          <t>Su estructura de contenido es clara y coherente, con categorías definidas que mejoran usabilidad.</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Utiliza un diseño estándar basado en cuadrícula para productos y categorías. La arquitectura del sitio es lógica, asegurando un flujo de información coherente.</t>
+          <t>Contenido bien estructurado y etiquetado, facilitando lectura e indexación SEO.</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Sigue un flujo de contenido simple y lineal del encabezado a la cuadrícula. La estructura es básica y clara, priorizando el acceso directo a componentes populares.</t>
+          <t>Contenido estructurado con títulos grandes que guían al usuario y secciones claras de productos.</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Implementa características de accesibilidad estándar para navegación y contenido. El sitio busca una experiencia útil para una amplia gama de usuarios.</t>
+          <t>Cumple estándares básicos de accesibilidad, ofreciendo una experiencia usable para la mayoría de usuarios.</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Generalmente se adhiere a las pautas de accesibilidad web, con navegación por teclado. Se esfuerza por ser inclusivo para usuarios con diversas capacidades.</t>
+          <t>Ha implementado mejoras de accesibilidad como contrastes adecuados y navegación con teclado.</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Muestra esfuerzos en accesibilidad, incluyendo buen contraste de color. El sitio está diseñado para ser utilizable por diversas audiencias.</t>
+          <t>Diseñado pensando en accesibilidad, con alternativas textuales para imágenes y subtítulos en vídeos.</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Presenta un buen contraste de color en el encabezado principal y el texto. Se requiere más análisis para confirmar la navegación completa con teclado y compatibilidad.</t>
+          <t>Contrastes de color en el encabezado son buenos; el texto del buscador sutil podría mejorarse.</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Ofrece búsqueda robusta, filtros de productos detallados y procesos de pago seguros. Las funciones clave operan de manera confiable, apoyando una experiencia de compra fluida.</t>
+          <t>Presenta robusta funcionalidad, con herramientas interactivas y búsqueda eficiente de productos.</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Proporciona búsqueda avanzada, pedidos con un clic y gestión integral de cuentas. Sus funcionalidades están altamente optimizadas para velocidad y comodidad del usuario.</t>
+          <t>Ofrece las funciones esperadas de un portal de tecnología, respondiendo rápidamente a las acciones.</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Ofrece búsqueda eficaz, filtrado por varios atributos y un embudo de compra fluido. Las funcionalidades principales funcionan eficientemente para un viaje satisfactorio.</t>
+          <t>Su funcionalidad es impecable, con características avanzadas que mejoran la interacción del usuario.</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Parece incluir una barra de búsqueda básica y herramientas implícitas 'Arma tu PC'. Las funcionalidades principales están presentes, pero su robustez necesita evaluación.</t>
+          <t>Ofrece funcionalidades esenciales como búsqueda y navegación principal, facilitando exploración de componentes.</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Integra reseñas de usuarios, secciones de preguntas y respuestas y foros comunitarios. El sitio fomenta una interacción significativa en torno a la información del producto.</t>
+          <t>Incluye elementos interactivos como filtros avanzados y comparadores de productos para el usuario.</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Presenta extensas reseñas de clientes, calificaciones y recomendaciones personalizadas. Sus elementos interactivos fomentan la participación del usuario y decisiones informadas.</t>
+          <t>La interactividad se manifiesta en comentarios, valoraciones y un foro activo de discusión.</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Incluye reseñas de usuarios, preguntas sobre productos y un chat de servicio al cliente. Las características interactivas apoyan la toma de decisiones del usuario.</t>
+          <t>Ofrece experiencia altamente interactiva con encuestas, configuradores y herramientas de personalización.</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Muestra tarjetas de productos clicables y un campo de entrada de búsqueda. Más allá de esto, elementos interactivos específicos no son evidentes.</t>
+          <t>La interactividad básica se observa en la barra de búsqueda y enlaces, enfocada en selección de productos.</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Implementa prácticas SEO sólidas con contenido rico en palabras clave y sitemap. El sitio se posiciona bien para búsquedas específicas de componentes de PC.</t>
+          <t>Optimizado para SEO con contenido relevante y estructura amigable, logrando buen posicionamiento.</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Se beneficia de un vasto contenido y alta autoridad de dominio. Su estrategia SEO es integral, asegurando una visibilidad amplia en todas las categorías.</t>
+          <t>Implementa prácticas SEO sólidas, desde investigación de palabras clave hasta velocidad de carga móvil.</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Aplica estrategias SEO dirigidas para páginas de productos y categorías. El sitio optimiza para palabras clave relevantes, mejorando la presencia en búsquedas.</t>
+          <t>Estrategia SEO efectiva con buen uso de enlaces internos y externos, mejorando visibilidad orgánica.</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Presenta títulos claros y una estructura simple, bases para un buen SEO. Se recomienda optimización para palabras clave, meta descripciones y móvil.</t>
+          <t>Aunque no visible, su estructura con títulos como "Componentes populares" sugiere orientación SEO básica.</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Generalmente ofrece buenas velocidades de carga y respuestas eficientes del servidor. El sitio busca una experiencia fluida en todos los dispositivos.</t>
+          <t>Mantiene diseño visual y experiencia de usuario consistentes en todas sus secciones y dispositivos.</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Logra un rendimiento excelente con activos altamente optimizados y CDN. Sus páginas se cargan muy rápido, proporcionando una experiencia de usuario perfecta.</t>
+          <t>Asegura coherencia en elementos de marca, desde tipografía hasta tono de voz del contenido.</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Muestra buenos tiempos de carga de página, utilizando almacenamiento en caché. El sitio funciona de manera fiable, garantizando una interfaz de usuario receptiva.</t>
+          <t>La consistencia en el diseño y la interacción crea experiencia predecible y de confianza.</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Presenta un diseño simple, sugiriendo tiempos de carga inicial potencialmente rápidos. La optimización de imágenes y el caché podrían mejorar su velocidad.</t>
+          <t>Mantiene diseño visual unificado en la página visible, con elementos repetitivos y predecibles.</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
@@ -686,11 +686,7 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -738,11 +734,7 @@
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,11 +782,7 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -842,11 +830,7 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -894,11 +878,7 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -946,11 +926,7 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -998,11 +974,7 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1050,11 +1022,7 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1102,16 +1070,12 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Coherencia y Consistencia</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -1154,16 +1118,12 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Conclusion</t>
+          <t>Final Conclusion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1208,7 +1168,7 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Este sitio web muestra una base sólida con una interfaz limpia y una navegación directa. Para mejorar, se podría enriquecer la experiencia visual con imágenes de mayor tamaño y contenido multimedia, similar a las prácticas de líderes del sector. La interactividad para los usuarios, como las secciones de preguntas y respuestas o las reseñas detalladas, potenciaría la comunidad y la confianza. Además, una revisión de la accesibilidad y la implementación de funcionalidades avanzadas en las herramientas de 'Arma tu PC' y 'Comparar' elevarían la propuesta de valor. La optimización SEO, incluyendo meta descripciones y un blog con contenido relevante, atraería más tráfico orgánico. Finalmente, asegurar una velocidad de carga consistentemente rápida en todos los dispositivos garantizaría una experiencia de usuario superior.</t>
+          <t>Este sitio muestra una base sólida con una interfaz limpia y navegación intuitiva, destacando claridad y organización. Para mejorar, podría enriquecer la interactividad con filtros avanzados y expandir la información de accesibilidad.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PcComponentes</t>
+          <t>PcComponentes.com</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Noticias3D</t>
+          <t>Hard Zone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Profesional Review</t>
+          <t>El Chapuzas Informático</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>(NombrePágina4)</t>
+          <t>Pity PC</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -466,13 +466,29 @@
           <t>Typography &amp; Readability</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Presenta fuentes sans-serif claras y legibles, garantizando una experiencia de lectura fluida para las descripciones de productos.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Utiliza una combinación de tamaños y estilos de fuente que mejoran la jerarquía visual de sus extensos artículos técnicos.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Se beneficia de una tipografía bien espaciada y contrastada, haciendo que el contenido del blog sea muy fácil de digerir.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Los elementos textuales son nítidos y directos, presentando una jerarquía limpia que facilita la comprensión del contenido general.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Se beneficia de mantener la consistencia en el tamaño de fuente. Destaca por su claridad, pero podría mejorar la jerarquía visual del texto en la página.</t>
+          <t>Considerar la implementación de una mayor variedad de pesos y tamaños de fuente para los encabezados podría mejorar la jerarquía visual. Ajustar el color del texto para un contraste ligeramente más alto podría beneficiar a usuarios con ciertas deficiencias visuales.</t>
         </is>
       </c>
     </row>
@@ -482,13 +498,29 @@
           <t>Colors &amp; Branding</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Su paleta de colores naranja y gris transmite profesionalidad, estableciendo una identidad de marca coherente y reconocible.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>El esquema oscuro con acentos brillantes es distintivo, alineándose perfectamente con su enfoque en el gaming y hardware de alto rendimiento.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Una combinación de azules y blancos domina, proyectando una imagen de seriedad y fiabilidad en su contenido técnico especializado.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Predomina un azul brillante combinado con blanco, otorgando una sensación de energía y frescura. El esquema de color es sencillo y directo.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>La fuerte identidad visual es un punto positivo. Considerar añadir un color secundario de acento para secciones importantes y reforzar el branding.</t>
+          <t>Aunque el azul crea una identidad fuerte, explorar tonos complementarios podría añadir sofisticación. Introducir colores de acento secundarios podría resaltar mejor los llamados a la acción, mejorando la interacción del usuario.</t>
         </is>
       </c>
     </row>
@@ -498,13 +530,29 @@
           <t>Visual Elements</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Presenta imágenes de productos de alta resolución y gráficos detallados, esenciales para las decisiones de compra informadas.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Incorpora visuales atractivos, incluyendo fotos detalladas e infografías, que enriquecen los artículos técnicos complejos.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Muestra fotografía de producto nítida y gráficos personalizados, elevando el atractivo visual de sus exhaustivas revisiones.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Las imágenes de productos son claras y están bien expuestas en la página principal, lo cual es fundamental para el compromiso visual. La consistencia en el estilo contribuye a una experiencia unificada.</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>La clara visualización de productos es una fortaleza. Podría incorporar más variedad visual, como iconos o banners, para mejorar la estética general y la diferenciación.</t>
+          <t>Las imágenes de productos son adecuadas; no obstante, implementar elementos visuales más dinámicos como vistas 360 grados o comparadores interactivos podría enriquecer la exploración. La adición de pequeños iconos relevantes a los encabezados de sección también sería beneficiosa.</t>
         </is>
       </c>
     </row>
@@ -514,13 +562,29 @@
           <t>Navigation &amp; UX</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ofrece una navegación intuitiva con filtros de categoría avanzados y una potente búsqueda, simplificando la compra en línea.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>La estructura de menú clara y los enlaces a artículos relacionados facilitan la exploración de su vasto repositorio de información tecnológica.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Se caracteriza por una organización de contenido lógica y un acceso sencillo a sus distintas secciones, garantizando una fluidez informativa.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>La barra de navegación es simple y muy visible, proporcionando acceso directo a secciones clave como 'Información' y 'Arma tu PC'. La barra de búsqueda también está bien situada.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>La navegación directa es eficiente. Podría mejorar la UX con más opciones de filtrado o categorías secundarias para explorar componentes específicos.</t>
+          <t>La navegación actual es directa, pero la incorporación de un mega-menú más detallado podría soportar un crecimiento futuro en categorías de productos. Asegurar que todos los elementos interactivos ofrezcan retroalimentación visual clara mejoraría significativamente la confianza del usuario.</t>
         </is>
       </c>
     </row>
@@ -530,13 +594,29 @@
           <t>Organization &amp; Structure</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Organiza los productos en jerarquías lógicas, permitiendo a los usuarios una navegación sin esfuerzo hasta elementos específicos.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Estructura sus artículos con encabezados y párrafos bien definidos, lo que mejora la legibilidad de grandes volúmenes de texto técnico.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Emplea un formato de blog claro con categorías y etiquetas, ayudando eficazmente a los lectores a encontrar información relevante.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>La página de inicio separa eficazmente el eslogan principal de 'Componentes populares', creando un flujo de contenido limpio. Los enlaces de navegación principales están agrupados lógicamente en la parte superior derecha.</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La organización por categorías populares es un buen comienzo. Se sugiere implementar una estructura de subcategorías más profunda para gestionar un catálogo más amplio.</t>
+          <t>Aunque el contenido está bien agrupado, la introducción de opciones de filtrado más avanzadas en las listas de productos permitiría una mayor personalización. Implementar 'migas de pan' (breadcrumbs) podría ofrecer a los usuarios un mejor contexto de su ubicación dentro de la jerarquía del sitio.</t>
         </is>
       </c>
     </row>
@@ -546,13 +626,29 @@
           <t>Accessibility</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cumple con estándares de accesibilidad, ofreciendo texto alternativo para imágenes y soporte para navegación con teclado.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Se esfuerza por mantener un contraste adecuado entre texto y fondo, mejorando la legibilidad para una amplia gama de usuarios.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Asegura que su contenido sea accesible con un diseño responsivo y compatibilidad con lectores de pantalla, beneficiando a todos.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>El diseño de alto contraste azul y blanco contribuye a una buena visibilidad general, y los elementos interactivos parecen tener un tamaño adecuado. Los tamaños de fuente son generalmente legibles.</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El contraste es adecuado, lo que es un buen punto de partida. Sería beneficioso añadir mejoras para lectores de pantalla y opciones de tamaño de texto.</t>
+          <t>Mejorar el soporte de navegación por teclado y asegurar que todos los elementos interactivos estén correctamente etiquetados para lectores de pantalla es crucial. Ampliar las opciones de contraste de color o proporcionar un modo oscuro incrementaría aún más la usabilidad para individuos con discapacidades visuales.</t>
         </is>
       </c>
     </row>
@@ -562,13 +658,29 @@
           <t>Functionality</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dispone de una robusta plataforma de comercio electrónico con pasarelas de pago seguras y seguimiento exhaustivo de pedidos.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ofrece un rendimiento de carga veloz y funciones de búsqueda eficaces, permitiendo un acceso rápido a la información deseada.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Proporciona un sistema de comentarios totalmente funcional y botones para compartir en redes sociales, incentivando la interacción comunitaria.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>La barra de búsqueda es un elemento funcional clave, permitiendo a los usuarios encontrar componentes específicos con rapidez. Los enlaces de navegación también parecen ser completamente operativos y responsivos.</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>La funcionalidad de comparación es un valor distintivo. Podría expandir sus características para incluir un configurador de PC o filtros de productos avanzados.</t>
+          <t>Considerar la adición de un configurador de PC 'Arma tu PC', una función muy demandada en este sector, sería un gran avance. Un sistema de cuentas de usuario con historial de pedidos y listas de deseos también podría aumentar significativamente el compromiso.</t>
         </is>
       </c>
     </row>
@@ -578,13 +690,29 @@
           <t>Interactivity</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Permite a los usuarios dejar valoraciones y plantear preguntas sobre productos, creando así una comunidad de compradores activa.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fomenta la participación mediante secciones de comentarios y encuestas, construyendo un diálogo continuo con su extensa audiencia.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Ofrece campos de comentarios para discusiones y la opción de suscripción a boletines para mantenerse al día con las novedades.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Los enlaces de navegación existentes proporcionan interactividad básica, dirigiendo eficazmente a los usuarios a diferentes secciones. La barra de búsqueda ofrece retroalimentación inmediata al escribir.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El diseño limpio se enfoca en la información. Se recomienda integrar características interactivas como reseñas o un foro para enriquecer la experiencia del usuario.</t>
+          <t>Introducir herramientas de comparación de productos o cuestionarios interactivos para guiar a los usuarios en la elección de componentes sería valioso. Una sección de comentarios para artículos o páginas de productos podría fomentar el compromiso de la comunidad y el contenido generado por el usuario.</t>
         </is>
       </c>
     </row>
@@ -594,36 +722,68 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Emplea descripciones de productos ricas en palabras clave y una estructura de URL amigable para los motores de búsqueda.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Optimiza sus artículos con meta descripciones, títulos pertinentes y enlaces internos, mejorando su visibilidad en línea.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Aplica prácticas SEO sólidas, incluyendo contenido de alta calidad y optimización de imágenes para el mejor posicionamiento.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Los títulos y encabezados parecen semánticamente relevantes para los componentes de PC, lo que sugiere una optimización básica de palabras clave. La estructura URL simple es propicia para la indexación.</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>La claridad de los nombres de productos ayuda. Debería centrarse en la creación de contenido relevante y una estructura de URL amigable para buscadores.</t>
+          <t>Optimizar las meta descripciones y etiquetas de título en todas las páginas para incluir más palabras clave relevantes y puntos de venta únicos. Desarrollar un blog con contenido valioso podría mejorar significativamente el tráfico orgánico y la autoridad del dominio.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>Rendimiento Técnico</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Presenta tiempos de carga rápidos y una infraestructura robusta, soportando eficazmente un alto volumen de tráfico y transacciones.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Optimiza sus imágenes y scripts, lo que se traduce en una experiencia de navegación fluida y muy eficiente para el usuario.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Posee un sitio web ligero y bien codificado, asegurando una carga rápida incluso con una extensa cantidad de contenido multimedia.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>La página carga rápidamente según los elementos visibles, indicando un enfoque en la entrega eficiente de recursos. La responsividad sugiere un backend bien optimizado para operaciones básicas.</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>La simplicidad de su diseño contribuye a un buen rendimiento inicial. Mantener la optimización del rendimiento es vital a medida que el contenido crece.</t>
+          <t>Realizar auditorías de rendimiento regulares para identificar y resolver posibles cuellos de botella en la velocidad de carga de la página, especialmente con contenido dinámico. La optimización adicional del tamaño de las imágenes y el aprovechamiento del almacenamiento en caché del navegador podría conducir a una experiencia más consistentemente rápida.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Final Conclusion</t>
+          <t>Conclusión Final</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -632,7 +792,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RmCity ofrece una plataforma funcional y sencilla para explorar componentes de PC, destacando por su claridad visual y facilidad de navegación. Para competir mejor, se sugiere expandir las funcionalidades interactivas, profundizar la organización del contenido y enriquecer la experiencia del usuario con más herramientas de personalización y comunidad.</t>
+          <t>El sitio web presenta una base sólida con una interfaz limpia y una navegación intuitiva para los usuarios. Para mejorar su oferta, podría beneficiarse enormemente de la adición de funcionalidades avanzadas como un configurador de PC y herramientas de comparación. Optimizar el SEO con contenido de blog y descripciones meta más ricas, junto con una mayor interactividad y opciones de accesibilidad, potenciarían su relevancia y experiencia de usuario en el competitivo mercado de componentes.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PcComponentes.com</t>
+          <t>(NamePage1)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Hard Zone</t>
+          <t>(NamePage2)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>El Chapuzas Informático</t>
+          <t>(NamePage3)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Pity PC</t>
+          <t>(NamePage4)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,29 +468,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Presenta fuentes sans-serif claras y legibles, garantizando una experiencia de lectura fluida para las descripciones de productos.</t>
+          <t>Exhibe una tipografía moderna y clara. Sus fuentes se adaptan bien a diversos dispositivos para una lectura confortable del contenido.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Utiliza una combinación de tamaños y estilos de fuente que mejoran la jerarquía visual de sus extensos artículos técnicos.</t>
+          <t>Presenta una selección de fuentes nítidas y contemporáneas. La claridad textual asegura una asimilación sencilla de la información importante.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Se beneficia de una tipografía bien espaciada y contrastada, haciendo que el contenido del blog sea muy fácil de digerir.</t>
+          <t>Adopta una tipografía funcional y fácilmente legible. Su diseño de texto prioriza la claridad en extensas listas de artículos.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Los elementos textuales son nítidos y directos, presentando una jerarquía limpia que facilita la comprensión del contenido general.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Considerar la implementación de una mayor variedad de pesos y tamaños de fuente para los encabezados podría mejorar la jerarquía visual. Ajustar el color del texto para un contraste ligeramente más alto podría beneficiar a usuarios con ciertas deficiencias visuales.</t>
-        </is>
-      </c>
+          <t>Emplea una tipografía básica pero efectiva. Los textos principales son de tamaño generoso y claros, mejorando la facilidad de lectura.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,29 +496,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Su paleta de colores naranja y gris transmite profesionalidad, estableciendo una identidad de marca coherente y reconocible.</t>
+          <t>Posee una paleta de colores profesional y distintiva. La identidad visual se mantiene consistente a lo largo de todas sus secciones.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El esquema oscuro con acentos brillantes es distintivo, alineándose perfectamente con su enfoque en el gaming y hardware de alto rendimiento.</t>
+          <t>Utiliza una combinación de colores vibrante y enérgica. Su marca evoca dinamismo, coherente con su enfoque en el gaming de alto nivel.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Una combinación de azules y blancos domina, proyectando una imagen de seriedad y fiabilidad en su contenido técnico especializado.</t>
+          <t>Muestra una gama cromática limpia y empresarial. La imagen de marca transmite seriedad y confianza en el comercio electrónico de tecnología.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Predomina un azul brillante combinado con blanco, otorgando una sensación de energía y frescura. El esquema de color es sencillo y directo.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aunque el azul crea una identidad fuerte, explorar tonos complementarios podría añadir sofisticación. Introducir colores de acento secundarios podría resaltar mejor los llamados a la acción, mejorando la interacción del usuario.</t>
-        </is>
-      </c>
+          <t>Su esquema cromático se centra en tonos de azul y blanco. Este diseño minimalista resalta la información sin saturar visualmente.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -532,29 +524,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Presenta imágenes de productos de alta resolución y gráficos detallados, esenciales para las decisiones de compra informadas.</t>
+          <t>Integra imágenes de productos de alta resolución y iconos claros. Los gráficos enriquecen las descripciones, ofreciendo gran detalle.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Incorpora visuales atractivos, incluyendo fotos detalladas e infografías, que enriquecen los artículos técnicos complejos.</t>
+          <t>Despliega imágenes detalladas y material multimedia explicativo. Los elementos visuales son clave para una presentación fidedigna del hardware.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Muestra fotografía de producto nítida y gráficos personalizados, elevando el atractivo visual de sus exhaustivas revisiones.</t>
+          <t>Presenta múltiples vistas y ángulos de sus artículos. Los recursos gráficos facilitan la visualización de cada componente en profundidad.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Las imágenes de productos son claras y están bien expuestas en la página principal, lo cual es fundamental para el compromiso visual. La consistencia en el estilo contribuye a una experiencia unificada.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Las imágenes de productos son adecuadas; no obstante, implementar elementos visuales más dinámicos como vistas 360 grados o comparadores interactivos podría enriquecer la exploración. La adición de pequeños iconos relevantes a los encabezados de sección también sería beneficiosa.</t>
-        </is>
-      </c>
+          <t>Las imágenes de los productos son prominentes y consistentes. Los iconos utilizados son sencillos y se identifican con facilidad.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,29 +552,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ofrece una navegación intuitiva con filtros de categoría avanzados y una potente búsqueda, simplificando la compra en línea.</t>
+          <t>Ofrece una navegación altamente intuitiva y estructurada. La experiencia de usuario es eficiente, agilizando la localización de productos y servicios.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>La estructura de menú clara y los enlaces a artículos relacionados facilitan la exploración de su vasto repositorio de información tecnológica.</t>
+          <t>La estructura de navegación se muestra lógica y directa. La usabilidad es una prioridad, permitiendo un proceso de búsqueda sin complicaciones.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Se caracteriza por una organización de contenido lógica y un acceso sencillo a sus distintas secciones, garantizando una fluidez informativa.</t>
+          <t>Dispone de una navegación compleja pero excepcionalmente eficaz. La experiencia de usuario está optimizada para componentes tecnológicos específicos.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>La barra de navegación es simple y muy visible, proporcionando acceso directo a secciones clave como 'Información' y 'Arma tu PC'. La barra de búsqueda también está bien situada.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>La navegación actual es directa, pero la incorporación de un mega-menú más detallado podría soportar un crecimiento futuro en categorías de productos. Asegurar que todos los elementos interactivos ofrezcan retroalimentación visual clara mejoraría significativamente la confianza del usuario.</t>
-        </is>
-      </c>
+          <t>Posee una barra de navegación superior concisa y funcional. La búsqueda de información esencial es directa, sin elementos superfluos.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,29 +580,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Organiza los productos en jerarquías lógicas, permitiendo a los usuarios una navegación sin esfuerzo hasta elementos específicos.</t>
+          <t>Su contenido se presenta en categorías lógicas y bien definidas. Los productos se exhiben de manera ordenada y de fácil comprensión.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estructura sus artículos con encabezados y párrafos bien definidos, lo que mejora la legibilidad de grandes volúmenes de texto técnico.</t>
+          <t>Organiza su extenso catálogo con notable precisión. Los contenidos están dispuestos para una exploración eficiente por parte del usuario.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Emplea un formato de blog claro con categorías y etiquetas, ayudando eficazmente a los lectores a encontrar información relevante.</t>
+          <t>La estructura es robusta para gestionar un catálogo inmenso. Los artículos están categorizados de forma lógica y extremadamente precisa.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>La página de inicio separa eficazmente el eslogan principal de 'Componentes populares', creando un flujo de contenido limpio. Los enlaces de navegación principales están agrupados lógicamente en la parte superior derecha.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Aunque el contenido está bien agrupado, la introducción de opciones de filtrado más avanzadas en las listas de productos permitiría una mayor personalización. Implementar 'migas de pan' (breadcrumbs) podría ofrecer a los usuarios un mejor contexto de su ubicación dentro de la jerarquía del sitio.</t>
-        </is>
-      </c>
+          <t>Presenta una disposición clara de sus contenidos principales. La sección de componentes populares se organiza efectivamente en una cuadrícula.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -628,29 +608,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cumple con estándares de accesibilidad, ofreciendo texto alternativo para imágenes y soporte para navegación con teclado.</t>
+          <t>Incorpora consideraciones básicas de diseño accesible. El diseño facilita el acceso y uso a una amplia gama de usuarios.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Se esfuerza por mantener un contraste adecuado entre texto y fondo, mejorando la legibilidad para una amplia gama de usuarios.</t>
+          <t>Se esfuerza por mantener una óptima legibilidad para todos. El contraste de colores contribuye a una visualización inclusiva.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Asegura que su contenido sea accesible con un diseño responsivo y compatibilidad con lectores de pantalla, beneficiando a todos.</t>
+          <t>Considera la diversidad de usuarios con un diseño adaptable. La claridad visual es un punto fuerte para mejorar la accesibilidad general.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El diseño de alto contraste azul y blanco contribuye a una buena visibilidad general, y los elementos interactivos parecen tener un tamaño adecuado. Los tamaños de fuente son generalmente legibles.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mejorar el soporte de navegación por teclado y asegurar que todos los elementos interactivos estén correctamente etiquetados para lectores de pantalla es crucial. Ampliar las opciones de contraste de color o proporcionar un modo oscuro incrementaría aún más la usabilidad para individuos con discapacidades visuales.</t>
-        </is>
-      </c>
+          <t>El contraste entre los colores del texto y el fondo es adecuado. La legibilidad de los elementos principales es buena para la mayoría de usuarios.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -660,29 +636,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dispone de una robusta plataforma de comercio electrónico con pasarelas de pago seguras y seguimiento exhaustivo de pedidos.</t>
+          <t>Dispone de un avanzado configurador de equipos personalizados. Ofrece herramientas sofisticadas para la comparación y filtrado detallado de componentes.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ofrece un rendimiento de carga veloz y funciones de búsqueda eficaces, permitiendo un acceso rápido a la información deseada.</t>
+          <t>Destaca por su servicio de montaje de PCs a medida. Proporciona opciones avanzadas para una personalización exhaustiva de los equipos.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Proporciona un sistema de comentarios totalmente funcional y botones para compartir en redes sociales, incentivando la interacción comunitaria.</t>
+          <t>Provee herramientas excepcionales de filtrado y comparación. Facilita la selección de componentes mediante parámetros muy específicos.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>La barra de búsqueda es un elemento funcional clave, permitiendo a los usuarios encontrar componentes específicos con rapidez. Los enlaces de navegación también parecen ser completamente operativos y responsivos.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Considerar la adición de un configurador de PC 'Arma tu PC', una función muy demandada en este sector, sería un gran avance. Un sistema de cuentas de usuario con historial de pedidos y listas de deseos también podría aumentar significativamente el compromiso.</t>
-        </is>
-      </c>
+          <t>Incluye una barra de búsqueda y enlaces a funcionalidades clave. Ofrece herramientas básicas como 'Arma tu PC' y 'Comparar'.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -692,29 +664,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Permite a los usuarios dejar valoraciones y plantear preguntas sobre productos, creando así una comunidad de compradores activa.</t>
+          <t>Permite valoraciones y comentarios detallados de los usuarios. Su interfaz responde dinámicamente, enriqueciendo la experiencia del visitante.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fomenta la participación mediante secciones de comentarios y encuestas, construyendo un diálogo continuo con su extensa audiencia.</t>
+          <t>Facilita la interacción directa con su soporte técnico especializado. Los usuarios pueden configurar productos con retroalimentación en tiempo real.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ofrece campos de comentarios para discusiones y la opción de suscripción a boletines para mantenerse al día con las novedades.</t>
+          <t>Integra un sistema de valoraciones y reseñas sumamente extenso. Sus foros y guías añaden un valor interactivo considerable a la experiencia.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Los enlaces de navegación existentes proporcionan interactividad básica, dirigiendo eficazmente a los usuarios a diferentes secciones. La barra de búsqueda ofrece retroalimentación inmediata al escribir.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Introducir herramientas de comparación de productos o cuestionarios interactivos para guiar a los usuarios en la elección de componentes sería valioso. Una sección de comentarios para artículos o páginas de productos podría fomentar el compromiso de la comunidad y el contenido generado por el usuario.</t>
-        </is>
-      </c>
+          <t>La interacción principal se centra en la navegación y la búsqueda. Los elementos presentados son clicables y responden de manera predecible.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -724,66 +692,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Emplea descripciones de productos ricas en palabras clave y una estructura de URL amigable para los motores de búsqueda.</t>
+          <t>Implementa estrategias SEO robustas y efectivas. Sus descripciones de producto y URLs están bien optimizadas para los buscadores.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Optimiza sus artículos con meta descripciones, títulos pertinentes y enlaces internos, mejorando su visibilidad en línea.</t>
+          <t>Optimiza sus fichas de producto meticulosamente para buscadores. Sus metadatos y contenido son muy relevantes para el nicho de hardware.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aplica prácticas SEO sólidas, incluyendo contenido de alta calidad y optimización de imágenes para el mejor posicionamiento.</t>
+          <t>Es un referente en optimización para motores de búsqueda. Sus páginas están altamente optimizadas para consultas de hardware específico.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Los títulos y encabezados parecen semánticamente relevantes para los componentes de PC, lo que sugiere una optimización básica de palabras clave. La estructura URL simple es propicia para la indexación.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Optimizar las meta descripciones y etiquetas de título en todas las páginas para incluir más palabras clave relevantes y puntos de venta únicos. Desarrollar un blog con contenido valioso podría mejorar significativamente el tráfico orgánico y la autoridad del dominio.</t>
-        </is>
-      </c>
+          <t>Los títulos de sección son descriptivos y claros. El uso de frases clave como 'Componentes populares' es muy pertinente para búsquedas.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rendimiento Técnico</t>
+          <t>Detalle de Información del Producto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Presenta tiempos de carga rápidos y una infraestructura robusta, soportando eficazmente un alto volumen de tráfico y transacciones.</t>
+          <t>Proporciona especificaciones técnicas exhaustivas y completas. Los detalles de cada artículo satisfacen las consultas más técnicas y exigentes.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Optimiza sus imágenes y scripts, lo que se traduce en una experiencia de navegación fluida y muy eficiente para el usuario.</t>
+          <t>Ofrece descripciones técnicas muy detalladas de cada componente. Se precisan especificaciones clave y compatibilidades para una compra informada.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Posee un sitio web ligero y bien codificado, asegurando una carga rápida incluso con una extensa cantidad de contenido multimedia.</t>
+          <t>Brinda especificaciones técnicas exhaustivas para cada artículo. La información detallada es crucial para tomar decisiones de compra acertadas.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La página carga rápidamente según los elementos visibles, indicando un enfoque en la entrega eficiente de recursos. La responsividad sugiere un backend bien optimizado para operaciones básicas.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Realizar auditorías de rendimiento regulares para identificar y resolver posibles cuellos de botella en la velocidad de carga de la página, especialmente con contenido dinámico. La optimización adicional del tamaño de las imágenes y el aprovechamiento del almacenamiento en caché del navegador podría conducir a una experiencia más consistentemente rápida.</t>
-        </is>
-      </c>
+          <t>La información de los productos bajo las imágenes es breve. Podría expandirse para ofrecer más detalles técnicos relevantes.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Conclusión Final</t>
+          <t>Final Conclusion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -792,7 +752,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El sitio web presenta una base sólida con una interfaz limpia y una navegación intuitiva para los usuarios. Para mejorar su oferta, podría beneficiarse enormemente de la adición de funcionalidades avanzadas como un configurador de PC y herramientas de comparación. Optimizar el SEO con contenido de blog y descripciones meta más ricas, junto con una mayor interactividad y opciones de accesibilidad, potenciarían su relevancia y experiencia de usuario en el competitivo mercado de componentes.</t>
+          <t>La plataforma examinada exhibe una sólida base, destacando su presentación visual limpia y navegación directa. Sin embargo, podría beneficiarse significativamente de descripciones de producto más detalladas, un sistema de filtrado avanzado y la incorporación de valoraciones de usuarios para enriquecer la experiencia y ofrecer mayor confianza al comprador.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,25 +436,26 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage1)</t>
+          <t>Sitio 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage2)</t>
+          <t>Sitio 2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage3)</t>
+          <t>Sitio 3</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage4)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+          <t>Sitio de la imagen</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -468,25 +469,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Exhibe una tipografía moderna y clara. Sus fuentes se adaptan bien a diversos dispositivos para una lectura confortable del contenido.</t>
+          <t>Una fuente sans-serif clara y moderna domina el contenido. La jerarquía visual es efectiva, facilitando la lectura de textos y títulos.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Presenta una selección de fuentes nítidas y contemporáneas. La claridad textual asegura una asimilación sencilla de la información importante.</t>
+          <t>Emplea varias tipografías sans-serif con distintos pesos. Esto asegura una buena diferenciación y legibilidad en los elementos.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adopta una tipografía funcional y fácilmente legible. Su diseño de texto prioriza la claridad en extensas listas de artículos.</t>
+          <t>Utiliza una tipografía sans-serif que ofrece claridad. Los tamaños y espaciados contribuyen a una experiencia de lectura cómoda.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Emplea una tipografía básica pero efectiva. Los textos principales son de tamaño generoso y claros, mejorando la facilidad de lectura.</t>
+          <t>Muestra una fuente sans-serif estándar para los textos principales. Los títulos son grandes y legibles; los nombres de productos son más pequeños.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Considerar el uso de una jerarquía tipográfica más variada en el sitio para resaltar información clave. Mejorar el tamaño y contraste de los nombres de producto.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,25 +502,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Posee una paleta de colores profesional y distintiva. La identidad visual se mantiene consistente a lo largo de todas sus secciones.</t>
+          <t>Su identidad de marca se basa en una combinación de naranja, azul y blanco. Esto proyecta una imagen dinámica y profesional.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Utiliza una combinación de colores vibrante y enérgica. Su marca evoca dinamismo, coherente con su enfoque en el gaming de alto nivel.</t>
+          <t>La paleta principal de colores incluye negro, rojo y blanco. Comunica una estética audaz y centrada en la tecnología.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Muestra una gama cromática limpia y empresarial. La imagen de marca transmite seriedad y confianza en el comercio electrónico de tecnología.</t>
+          <t>Opera con una paleta de azules, blancos y grises. Los colores transmiten una percepción de seriedad y confianza al usuario.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Su esquema cromático se centra en tonos de azul y blanco. Este diseño minimalista resalta la información sin saturar visualmente.</t>
+          <t>El encabezado superior emplea un azul vibrante sobre un fondo blanco. El logotipo incorpora este azul con detalles en negro, ofreciendo una apariencia simple y directa.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Explorar una paleta de colores complementaria para suavizar el contraste. Integrar el color de marca de forma más consistente en elementos interactivos.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -524,25 +535,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Integra imágenes de productos de alta resolución y iconos claros. Los gráficos enriquecen las descripciones, ofreciendo gran detalle.</t>
+          <t>Presenta imágenes de producto de alta resolución y gráficos promocionales. El diseño general es moderno y pulcro.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Despliega imágenes detalladas y material multimedia explicativo. Los elementos visuales son clave para una presentación fidedigna del hardware.</t>
+          <t>Se distingue por sus fotografías de producto profesionales y detalladas. Incluye además iconos claros para funcionalidades específicas.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Presenta múltiples vistas y ángulos de sus artículos. Los recursos gráficos facilitan la visualización de cada componente en profundidad.</t>
+          <t>Muestra imágenes de productos nítidas y banners publicitarios discretos. Los iconos utilizados son limpios y fáciles de entender.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Las imágenes de los productos son prominentes y consistentes. Los iconos utilizados son sencillos y se identifican con facilidad.</t>
+          <t>Las imágenes de los componentes son nítidas y tienen un fondo blanco simple. Se observa un logotipo minimalista en el encabezado izquierdo.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Añadir más elementos visuales, como iconos descriptivos o banners promocionales. Mejorar la consistencia en el estilo de las imágenes de producto.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -552,25 +568,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ofrece una navegación altamente intuitiva y estructurada. La experiencia de usuario es eficiente, agilizando la localización de productos y servicios.</t>
+          <t>Ofrece un mega menú extenso y una barra de búsqueda destacada. La navegación es intuitiva y facilita el acceso rápido.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>La estructura de navegación se muestra lógica y directa. La usabilidad es una prioridad, permitiendo un proceso de búsqueda sin complicaciones.</t>
+          <t>Dispone de una navegación superior robusta y filtros laterales detallados. Permite una exploración eficiente de su vasto catálogo.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dispone de una navegación compleja pero excepcionalmente eficaz. La experiencia de usuario está optimizada para componentes tecnológicos específicos.</t>
+          <t>Su menú principal está bien organizado por categorías lógicas. Esto permite al usuario encontrar rápidamente lo que busca.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Posee una barra de navegación superior concisa y funcional. La búsqueda de información esencial es directa, sin elementos superfluos.</t>
+          <t>La navegación superior es simple con enlaces básicos y una barra de búsqueda prominente. El icono de usuario sugiere acceso a perfil personal.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Expandir las opciones de navegación principales para incluir categorías de productos. Mejorar la barra de búsqueda con sugerencias o autocompletado.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,25 +601,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Su contenido se presenta en categorías lógicas y bien definidas. Los productos se exhiben de manera ordenada y de fácil comprensión.</t>
+          <t>La arquitectura de la información es lógica, con categorías claras y páginas de producto detalladas. Facilita la comprensión del catálogo.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Organiza su extenso catálogo con notable precisión. Los contenidos están dispuestos para una exploración eficiente por parte del usuario.</t>
+          <t>Presenta una estructura de categorías profunda y páginas de destino bien definidas. Esto ayuda a los usuarios a navegar por opciones.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La estructura es robusta para gestionar un catálogo inmenso. Los artículos están categorizados de forma lógica y extremadamente precisa.</t>
+          <t>La disposición del contenido es muy clara, con listas de productos y secciones informativas. Promueve una experiencia de usuario ordenada.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Presenta una disposición clara de sus contenidos principales. La sección de componentes populares se organiza efectivamente en una cuadrícula.</t>
+          <t>Muestra un diseño sencillo con un encabezado principal y una sección de 'Componentes populares'. La cuadrícula de productos ofrece una buena visibilidad inicial.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Desarrollar una estructura de contenido más jerárquica para las categorías. Incorporar secciones adicionales para guías o recursos útiles.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -608,25 +634,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Incorpora consideraciones básicas de diseño accesible. El diseño facilita el acceso y uso a una amplia gama de usuarios.</t>
+          <t>Se esfuerza por cumplir estándares de accesibilidad, como el contraste de colores. Incluye navegación con teclado y etiquetas.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Se esfuerza por mantener una óptima legibilidad para todos. El contraste de colores contribuye a una visualización inclusiva.</t>
+          <t>Frecuentemente invierte en mejoras de accesibilidad digital. Esto incluye un buen contraste y soporte para lectores de pantalla.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Considera la diversidad de usuarios con un diseño adaptable. La claridad visual es un punto fuerte para mejorar la accesibilidad general.</t>
+          <t>Considera el contraste de texto y fondo para asegurar legibilidad. Se enfoca en una experiencia de navegación clara para todos.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El contraste entre los colores del texto y el fondo es adecuado. La legibilidad de los elementos principales es buena para la mayoría de usuarios.</t>
+          <t>El contraste entre el azul del encabezado y el texto blanco es adecuado. No se evidencian otros elementos de accesibilidad avanzada en la captura.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Asegurar el contraste adecuado en todos los elementos interactivos. Implementar etiquetas ARIA y textos alternativos para imágenes para mejorar la accesibilidad.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -636,25 +667,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dispone de un avanzado configurador de equipos personalizados. Ofrece herramientas sofisticadas para la comparación y filtrado detallado de componentes.</t>
+          <t>Ofrece un rendimiento rápido y estable en todas las páginas. La búsqueda y los formularios funcionan sin errores apreciables.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Destaca por su servicio de montaje de PCs a medida. Proporciona opciones avanzadas para una personalización exhaustiva de los equipos.</t>
+          <t>Se caracteriza por su alta velocidad de carga y estabilidad operativa. La experiencia de compra es fluida y sin interrupciones.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Provee herramientas excepcionales de filtrado y comparación. Facilita la selección de componentes mediante parámetros muy específicos.</t>
+          <t>Garantiza tiempos de carga eficientes y una plataforma estable. Esto proporciona una experiencia de usuario fiable y consistente.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Incluye una barra de búsqueda y enlaces a funcionalidades clave. Ofrece herramientas básicas como 'Arma tu PC' y 'Comparar'.</t>
+          <t>La funcionalidad no puede ser evaluada con la imagen estática. No se pueden observar la velocidad, estabilidad, o errores de la plataforma.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Optimizar la velocidad de carga de la página para una mejor experiencia. Asegurar la estabilidad de los elementos interactivos y formularios.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -664,25 +700,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Permite valoraciones y comentarios detallados de los usuarios. Su interfaz responde dinámicamente, enriqueciendo la experiencia del visitante.</t>
+          <t>Posee diversos estados hover para enlaces y botones. Proporciona retroalimentación visual al usuario en cada interacción.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Facilita la interacción directa con su soporte técnico especializado. Los usuarios pueden configurar productos con retroalimentación en tiempo real.</t>
+          <t>Sus elementos interactivos responden dinámicamente. Ofrece mensajes claros y microinteracciones que mejoran la experiencia.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Integra un sistema de valoraciones y reseñas sumamente extenso. Sus foros y guías añaden un valor interactivo considerable a la experiencia.</t>
+          <t>Implementa sutiles efectos hover en sus elementos clicables. Esto guía al usuario de forma intuitiva a través del sitio.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>La interacción principal se centra en la navegación y la búsqueda. Los elementos presentados son clicables y responden de manera predecible.</t>
+          <t>La barra de búsqueda muestra un placeholder de texto. Los enlaces superiores parecen tener un efecto de subrayado al pasar el cursor.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Introducir microinteracciones visuales al interactuar con productos. Desarrollar estados hover y focus más distintivos para botones y enlaces.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -692,67 +733,74 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Implementa estrategias SEO robustas y efectivas. Sus descripciones de producto y URLs están bien optimizadas para los buscadores.</t>
+          <t>Optimiza sus títulos, meta descripciones y H1s. La estructura del sitio está diseñada para un buen rastreo e indexación.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Optimiza sus fichas de producto meticulosamente para buscadores. Sus metadatos y contenido son muy relevantes para el nicho de hardware.</t>
+          <t>Destaca por su SEO técnico y on-page, usando datos estructurados. Esto le permite un alto posicionamiento en motores de búsqueda.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Es un referente en optimización para motores de búsqueda. Sus páginas están altamente optimizadas para consultas de hardware específico.</t>
+          <t>Utiliza palabras clave relevantes y encabezados optimizados. Esto contribuye a su visibilidad orgánica en los resultados de búsqueda.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Los títulos de sección son descriptivos y claros. El uso de frases clave como 'Componentes populares' es muy pertinente para búsquedas.</t>
+          <t>Los títulos principales como 'Aprendé, Armá y Compará' actúan como H1s. Otros elementos SEO como meta descripciones no son observables.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Añadir metadescripciones y títulos SEO únicos para cada página. Implementar datos estructurados para productos y contenido relevante.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Detalle de Información del Producto</t>
+          <t>Descubrimiento de productos y filtrado</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Proporciona especificaciones técnicas exhaustivas y completas. Los detalles de cada artículo satisfacen las consultas más técnicas y exigentes.</t>
+          <t>Ofrece filtros avanzados por especificaciones, marca y precio. Facilita enormemente la búsqueda de componentes específicos.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ofrece descripciones técnicas muy detalladas de cada componente. Se precisan especificaciones clave y compatibilidades para una compra informada.</t>
+          <t>Posee amplias opciones de filtrado y herramientas de comparación de productos. Esto ayuda a los usuarios a tomar decisiones informadas.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Brinda especificaciones técnicas exhaustivas para cada artículo. La información detallada es crucial para tomar decisiones de compra acertadas.</t>
+          <t>Dispone de filtros de categoría robustos y búsqueda por especificaciones. También ofrece configuradores para sistemas personalizados.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La información de los productos bajo las imágenes es breve. Podría expandirse para ofrecer más detalles técnicos relevantes.</t>
+          <t>Solo se visualiza una barra de búsqueda genérica en el encabezado. No se aprecian opciones de filtrado o clasificación de productos en la interfaz mostrada.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Incorporar filtros por categoría, marca, precio y especificaciones técnicas. Añadir opciones de ordenación (precio, popularidad) para mejorar la búsqueda.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Final Conclusion</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>La plataforma examinada exhibe una sólida base, destacando su presentación visual limpia y navegación directa. Sin embargo, podría beneficiarse significativamente de descripciones de producto más detalladas, un sistema de filtrado avanzado y la incorporación de valoraciones de usuarios para enriquecer la experiencia y ofrecer mayor confianza al comprador.</t>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>El sitio de la imagen presenta una interfaz limpia y una estructura inicial clara, con una navegación sencilla y componentes populares bien expuestos. Para optimizar su potencial, debería priorizar la implementación de filtros detallados para mejorar el descubrimiento de productos, enriquecer la interactividad con efectos visuales más evidentes y asegurar la accesibilidad completa, como textos alternativos. Mejorar los elementos SEO on-page y la velocidad de carga también impulsaría su rendimiento general.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,26 +436,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sitio 1</t>
+          <t>(NamePage1)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sitio 2</t>
+          <t>(NamePage2)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Sitio 3</t>
+          <t>(NamePage3)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sitio de la imagen</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr">
+          <t>(NamePage4)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -464,264 +463,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Typography &amp; Readability</t>
+          <t>Tipografía y legibilidad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Una fuente sans-serif clara y moderna domina el contenido. La jerarquía visual es efectiva, facilitando la lectura de textos y títulos.</t>
+          <t>Tipos profesionales. Este medio emplea fuentes sans-serif claras, garantizando que el texto principal sea cómodo para la lectura en artículos extensos.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Emplea varias tipografías sans-serif con distintos pesos. Esto asegura una buena diferenciación y legibilidad en los elementos.</t>
+          <t>Fuentes contemporáneas. El portal utiliza tipografías modernas y variadas, equilibrando titulares impactantes con párrafos fácilmente legibles y atractivos.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Utiliza una tipografía sans-serif que ofrece claridad. Los tamaños y espaciados contribuyen a una experiencia de lectura cómoda.</t>
+          <t>Estilo distintivo. El sitio combina fuentes audaces para encabezados y una principal nítida, reforzando su identidad visual orientada al gaming.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Muestra una fuente sans-serif estándar para los textos principales. Los títulos son grandes y legibles; los nombres de productos son más pequeños.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Considerar el uso de una jerarquía tipográfica más variada en el sitio para resaltar información clave. Mejorar el tamaño y contraste de los nombres de producto.</t>
+          <t>Claridad visible. El portal usa una tipografía sans-serif limpia y tamaños adecuados para los títulos, pero los nombres de producto son algo pequeños.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>La tipografía del sitio es clara, pero optimizar el tamaño de fuente en las descripciones de productos mejoraría notablemente su legibilidad.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colors &amp; Branding</t>
+          <t>Colores e identidad visual</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Su identidad de marca se basa en una combinación de naranja, azul y blanco. Esto proyecta una imagen dinámica y profesional.</t>
+          <t>Paleta funcional. El medio opta por colores sobrios, priorizando la información técnica y la seriedad del contenido para el público especializado.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La paleta principal de colores incluye negro, rojo y blanco. Comunica una estética audaz y centrada en la tecnología.</t>
+          <t>Diseño vibrante. El portal emplea una paleta de colores moderna y distintiva, ayudando a diferenciar secciones y captar la atención visualmente.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Opera con una paleta de azules, blancos y grises. Los colores transmiten una percepción de seriedad y confianza al usuario.</t>
+          <t>Imagen marcada. El sitio utiliza una combinación de colores oscura y contrastada, reflejando fuertemente su marca y la estética del gaming.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El encabezado superior emplea un azul vibrante sobre un fondo blanco. El logotipo incorpora este azul con detalles en negro, ofreciendo una apariencia simple y directa.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Explorar una paleta de colores complementaria para suavizar el contraste. Integrar el color de marca de forma más consistente en elementos interactivos.</t>
+          <t>Contraste básico. El portal exhibe un cabezal azul brillante con texto blanco y un cuerpo blanco con texto negro, ofreciendo buena visibilidad.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Los colores del sitio son funcionales, pero una paleta más desarrollada podría fortalecer la marca y el atractivo visual general del portal.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Visual Elements</t>
+          <t>Elementos visuales</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Presenta imágenes de producto de alta resolución y gráficos promocionales. El diseño general es moderno y pulcro.</t>
+          <t>Gráficos detallados. El medio integra abundantes imágenes de productos, gráficos de rendimiento y esquemas técnicos, ilustrando exhaustivamente sus análisis.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Se distingue por sus fotografías de producto profesionales y detalladas. Incluye además iconos claros para funcionalidades específicas.</t>
+          <t>Multimedia variada. El portal utiliza imágenes de alta calidad, videos y sliders, enriqueciendo significativamente el contenido y la experiencia del usuario.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Muestra imágenes de productos nítidas y banners publicitarios discretos. Los iconos utilizados son limpios y fáciles de entender.</t>
+          <t>Atractivo visual. El sitio destaca con grandes imágenes de juegos y hardware, así como banners promocionales, captando rápidamente la atención.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Las imágenes de los componentes son nítidas y tienen un fondo blanco simple. Se observa un logotipo minimalista en el encabezado izquierdo.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Añadir más elementos visuales, como iconos descriptivos o banners promocionales. Mejorar la consistencia en el estilo de las imágenes de producto.</t>
+          <t>Productos claros. El portal muestra imágenes nítidas de componentes, facilitando la identificación visual aunque sin elementos gráficos adicionales notables.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Las imágenes de producto del sitio son nítidas, pero la incorporación de iconos o ilustraciones adicionales podría enriquecer su presentación visual.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Navigation &amp; UX</t>
+          <t>Navegación y UX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ofrece un mega menú extenso y una barra de búsqueda destacada. La navegación es intuitiva y facilita el acceso rápido.</t>
+          <t>Menú estructurado. El medio ofrece una navegación compleja pero lógica, permitiendo a los usuarios acceder a categorías y filtros específicos fácilmente.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dispone de una navegación superior robusta y filtros laterales detallados. Permite una exploración eficiente de su vasto catálogo.</t>
+          <t>Ruta intuitiva. El portal presenta una estructura de menú clara y una barra de búsqueda eficiente, facilitando la exploración del vasto contenido.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Su menú principal está bien organizado por categorías lógicas. Esto permite al usuario encontrar rápidamente lo que busca.</t>
+          <t>Acceso directo. El sitio utiliza menús desplegables y enlaces destacados, guiando al usuario rápidamente hacia secciones populares y reviews.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>La navegación superior es simple con enlaces básicos y una barra de búsqueda prominente. El icono de usuario sugiere acceso a perfil personal.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Expandir las opciones de navegación principales para incluir categorías de productos. Mejorar la barra de búsqueda con sugerencias o autocompletado.</t>
+          <t>Barra superior. El portal exhibe una barra de búsqueda central y enlaces de navegación clave en la cabecera, ofreciendo opciones directas.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>La navegación visible del sitio es sencilla, pero menús más extensos o "breadcrumbs" guiarían mejor a los usuarios en búsquedas profundas.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organization &amp; Structure</t>
+          <t>Organización y estructura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>La arquitectura de la información es lógica, con categorías claras y páginas de producto detalladas. Facilita la comprensión del catálogo.</t>
+          <t>Contenido ordenado. El medio estructura sus artículos con encabezados, subtítulos y listas, facilitando el escaneo y la asimilación de información.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Presenta una estructura de categorías profunda y páginas de destino bien definidas. Esto ayuda a los usuarios a navegar por opciones.</t>
+          <t>Secciones claras. El portal divide su contenido en bloques bien definidos con titulares grandes, mejorando la comprensión y el flujo de lectura.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La disposición del contenido es muy clara, con listas de productos y secciones informativas. Promueve una experiencia de usuario ordenada.</t>
+          <t>Diseño modular. El sitio organiza artículos y noticias en módulos visualmente atractivos, facilitando la exploración de diverso contenido relevante.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Muestra un diseño sencillo con un encabezado principal y una sección de 'Componentes populares'. La cuadrícula de productos ofrece una buena visibilidad inicial.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Desarrollar una estructura de contenido más jerárquica para las categorías. Incorporar secciones adicionales para guías o recursos útiles.</t>
+          <t>Diseño lineal. El portal presenta un diseño simple con un título principal y una sección de productos debajo, mostrando una jerarquía básica.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>La organización del sitio es básica, pero una mejor estructura de categorías y filtros en la página optimizaría la exploración de componentes.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Accesibilidad</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Se esfuerza por cumplir estándares de accesibilidad, como el contraste de colores. Incluye navegación con teclado y etiquetas.</t>
+          <t>Diseño inclusivo. El medio mantiene altos contrastes y opciones de tamaño de texto, garantizando la legibilidad para un amplio rango de usuarios.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Frecuentemente invierte en mejoras de accesibilidad digital. Esto incluye un buen contraste y soporte para lectores de pantalla.</t>
+          <t>Estándares seguidos. El portal se adhiere a pautas de accesibilidad, ofreciendo una experiencia cómoda para usuarios con diversas necesidades.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Considera el contraste de texto y fondo para asegurar legibilidad. Se enfoca en una experiencia de navegación clara para todos.</t>
+          <t>Usabilidad general. El sitio prioriza la claridad del texto y la navegación con teclado, favoreciendo a usuarios con diferentes capacidades.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El contraste entre el azul del encabezado y el texto blanco es adecuado. No se evidencian otros elementos de accesibilidad avanzada en la captura.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Asegurar el contraste adecuado en todos los elementos interactivos. Implementar etiquetas ARIA y textos alternativos para imágenes para mejorar la accesibilidad.</t>
+          <t>Contraste evidente. El portal presenta buen contraste entre texto y fondo, favoreciendo la legibilidad, aunque otras características no son visibles.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>El contraste del sitio es adecuado, pero explorar descripciones alternativas para imágenes y navegación con teclado sería beneficioso.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Funcionalidad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ofrece un rendimiento rápido y estable en todas las páginas. La búsqueda y los formularios funcionan sin errores apreciables.</t>
+          <t>Herramientas útiles. El medio ofrece comparadores, filtros avanzados y especificaciones técnicas detalladas, añadiendo valor práctico al usuario.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Se caracteriza por su alta velocidad de carga y estabilidad operativa. La experiencia de compra es fluida y sin interrupciones.</t>
+          <t>Recursos completos. El portal incluye guías de compra interactivas, herramientas de búsqueda avanzada y secciones de comentarios, enriqueciendo la experiencia.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Garantiza tiempos de carga eficientes y una plataforma estable. Esto proporciona una experiencia de usuario fiable y consistente.</t>
+          <t>Características robustas. El sitio permite la búsqueda por juegos o componentes, integrando enlaces a tiendas y secciones de noticias actualizadas.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>La funcionalidad no puede ser evaluada con la imagen estática. No se pueden observar la velocidad, estabilidad, o errores de la plataforma.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Optimizar la velocidad de carga de la página para una mejor experiencia. Asegurar la estabilidad de los elementos interactivos y formularios.</t>
+          <t>Búsqueda visible. El portal dispone de una barra de búsqueda y secciones para "Arma tu PC" y "Comparar", sugiriendo funcionalidades clave.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Las funcionalidades inferidas del sitio son prometedoras, pero se recomienda ampliar las opciones de filtrado y comparación de productos directamente.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Interactivity</t>
+          <t>Interactividad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Posee diversos estados hover para enlaces y botones. Proporciona retroalimentación visual al usuario en cada interacción.</t>
+          <t>Enganche con el lector. El medio fomenta la participación con secciones de comentarios, foros activos y encuestas relevantes para la comunidad.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sus elementos interactivos responden dinámicamente. Ofrece mensajes claros y microinteracciones que mejoran la experiencia.</t>
+          <t>Compromiso activo. El portal incluye votaciones, valoraciones de usuarios y foros de discusión, creando una comunidad participativa y dinámica.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Implementa sutiles efectos hover en sus elementos clicables. Esto guía al usuario de forma intuitiva a través del sitio.</t>
+          <t>Compromiso lúdico. El sitio ofrece comentarios, reseñas de usuarios y enlaces a comunidades, promoviendo una interacción efectiva entre gamers.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>La barra de búsqueda muestra un placeholder de texto. Los enlaces superiores parecen tener un efecto de subrayado al pasar el cursor.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Introducir microinteracciones visuales al interactuar con productos. Desarrollar estados hover y focus más distintivos para botones y enlaces.</t>
+          <t>Opciones directas. El portal muestra enlaces como "Arma tu PC" y "Comparar", sugiriendo interacción, pero no se observan comentarios ni foros.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Las opciones de interacción del sitio son directas, aunque incorporar reseñas de usuarios o un sistema de comentarios enriquecería la experiencia.</t>
         </is>
       </c>
     </row>
@@ -733,74 +724,75 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optimiza sus títulos, meta descripciones y H1s. La estructura del sitio está diseñada para un buen rastreo e indexación.</t>
+          <t>Estrategia robusta. El medio optimiza sus títulos, encabezados y contenido con palabras clave relevantes, atrayendo tráfico orgánico constante.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Destaca por su SEO técnico y on-page, usando datos estructurados. Esto le permite un alto posicionamiento en motores de búsqueda.</t>
+          <t>Visibilidad alta. El portal utiliza una estructura de URL amigable, metadescripciones claras y contenido actualizado, posicionándose bien en búsquedas.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Utiliza palabras clave relevantes y encabezados optimizados. Esto contribuye a su visibilidad orgánica en los resultados de búsqueda.</t>
+          <t>Contenido clave. El sitio integra títulos optimizados, descripciones ricas y una buena jerarquía de encabezados, favoreciendo su ranking en búsquedas.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Los títulos principales como 'Aprendé, Armá y Compará' actúan como H1s. Otros elementos SEO como meta descripciones no son observables.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Añadir metadescripciones y títulos SEO únicos para cada página. Implementar datos estructurados para productos y contenido relevante.</t>
+          <t>Elementos básicos. El portal exhibe títulos de sección claros y nombres de producto, indicando una base para la optimización on-page.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Los elementos SEO visibles del sitio son adecuados, pero fortalecer la jerarquía de encabezados y el uso estratégico de palabras clave sería clave.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Descubrimiento de productos y filtrado</t>
+          <t>Rendimiento y velocidad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ofrece filtros avanzados por especificaciones, marca y precio. Facilita enormemente la búsqueda de componentes específicos.</t>
+          <t>Carga eficiente. El medio se optimiza para una velocidad de carga rápida, garantizando una experiencia fluida incluso con contenido multimedia pesado.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Posee amplias opciones de filtrado y herramientas de comparación de productos. Esto ayuda a los usuarios a tomar decisiones informadas.</t>
+          <t>Experiencia ágil. El portal presenta una excelente optimización de imágenes y recursos, resultando en tiempos de carga mínimos y agradables.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dispone de filtros de categoría robustos y búsqueda por especificaciones. También ofrece configuradores para sistemas personalizados.</t>
+          <t>Rapidez notable. El sitio utiliza técnicas de caché y compresión, asegurando que las páginas carguen velozmente para sus usuarios ávidos.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Solo se visualiza una barra de búsqueda genérica en el encabezado. No se aprecian opciones de filtrado o clasificación de productos en la interfaz mostrada.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Incorporar filtros por categoría, marca, precio y especificaciones técnicas. Añadir opciones de ordenación (precio, popularidad) para mejorar la búsqueda.</t>
+          <t>Diseño ligero. El portal parece tener una estructura visual sencilla y pocos elementos pesados, sugiriendo una carga potencialmente rápida.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>El diseño del sitio parece ligero, pero optimizar la compresión de imágenes y el código podría garantizar tiempos de carga consistentemente rápidos.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Conclusión final</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>El sitio de la imagen presenta una interfaz limpia y una estructura inicial clara, con una navegación sencilla y componentes populares bien expuestos. Para optimizar su potencial, debería priorizar la implementación de filtros detallados para mejorar el descubrimiento de productos, enriquecer la interactividad con efectos visuales más evidentes y asegurar la accesibilidad completa, como textos alternativos. Mejorar los elementos SEO on-page y la velocidad de carga también impulsaría su rendimiento general.</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>El sitio analizado destaca por su interfaz limpia y navegación directa, facilitando la búsqueda inicial de componentes. Para mejorar, debería priorizar la expansión de filtros de búsqueda, optimizar la legibilidad de descripciones de productos y enriquecer la experiencia interactiva con reseñas de usuarios. Estas acciones potenciarán su utilidad y atractivo para la comunidad de entusiastas de PC.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage1)</t>
+          <t>Tom's Hardware</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage2)</t>
+          <t>PC Gamer</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage3)</t>
+          <t>TechRadar</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>(NamePage4)</t>
+          <t>Rity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -463,256 +463,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tipografía y legibilidad</t>
+          <t>Typography &amp; Readability</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tipos profesionales. Este medio emplea fuentes sans-serif claras, garantizando que el texto principal sea cómodo para la lectura en artículos extensos.</t>
+          <t>Fuentes claras, legibles. El portal utiliza fuentes serif y sans-serif bien balanceadas, asegurando una lectura confortable en artículos extensos y detalles técnicos; la jerarquía visual facilita el escaneo rápido de la información.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fuentes contemporáneas. El portal utiliza tipografías modernas y variadas, equilibrando titulares impactantes con párrafos fácilmente legibles y atractivos.</t>
+          <t>Tipografía dinámica, atractiva. Esta publicación emplea una tipografía moderna con encabezados impactantes, diseñada para captar la atención del lector y complementar el contenido visualmente inmersivo del sector de videojuegos.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estilo distintivo. El sitio combina fuentes audaces para encabezados y una principal nítida, reforzando su identidad visual orientada al gaming.</t>
+          <t>Lectura fluida, consistente. La plataforma exhibe una tipografía sans-serif limpia y consistente en todo su contenido, promoviendo una experiencia de lectura muy accesible y sin distracciones para el usuario.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Claridad visible. El portal usa una tipografía sans-serif limpia y tamaños adecuados para los títulos, pero los nombres de producto son algo pequeños.</t>
+          <t>Tipografía sencilla, funcional. El sitio presenta una tipografía básica y estándar, con tamaños adecuados para los títulos y textos de componentes, aunque carece de una diferenciación estilística que enriquezca la experiencia visual general.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>La tipografía del sitio es clara, pero optimizar el tamaño de fuente en las descripciones de productos mejoraría notablemente su legibilidad.</t>
+          <t>Mejora la legibilidad en ciertos bloques de texto, como descripciones largas, explorando contrastes o espaciados para evitar la monotonía visual. Podría integrar estilos tipográficos más modernos que refuercen la identidad.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colores e identidad visual</t>
+          <t>Colors &amp; Branding</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paleta funcional. El medio opta por colores sobrios, priorizando la información técnica y la seriedad del contenido para el público especializado.</t>
+          <t>Paleta sobria, profesional. La marca emplea una combinación de colores oscuros y neutros, con acentos sutiles, reflejando su enfoque técnico y serio en análisis de hardware y noticias del sector.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diseño vibrante. El portal emplea una paleta de colores moderna y distintiva, ayudando a diferenciar secciones y captar la atención visualmente.</t>
+          <t>Colores vibrantes, enérgicos. La identidad visual de esta publicación se define por tonos intensos, especialmente rojos y negros, que evocan la emoción y el dinamismo inherentes al mundo del gaming en PC.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Imagen marcada. El sitio utiliza una combinación de colores oscura y contrastada, reflejando fuertemente su marca y la estética del gaming.</t>
+          <t>Identidad fresca, moderna. El sitio utiliza una paleta de colores claros y acentos brillantes, proyectando una imagen de innovación y accesibilidad, adecuada para un público tecnológico amplio y diverso.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Contraste básico. El portal exhibe un cabezal azul brillante con texto blanco y un cuerpo blanco con texto negro, ofreciendo buena visibilidad.</t>
+          <t>Esquema básico, funcional. El diseño del portal se centra en un azul brillante para la cabecera y el blanco del fondo, lo que lo hace funcional pero no posee una paleta de colores distintiva o branding fuerte.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Los colores del sitio son funcionales, pero una paleta más desarrollada podría fortalecer la marca y el atractivo visual general del portal.</t>
+          <t>Considerar una paleta de colores más variada y atractiva, quizás con tonos complementarios, para mejorar la estética y reforzar una identidad de marca más memorable. Podría usar el color para jerarquizar información.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elementos visuales</t>
+          <t>Visual Elements</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gráficos detallados. El medio integra abundantes imágenes de productos, gráficos de rendimiento y esquemas técnicos, ilustrando exhaustivamente sus análisis.</t>
+          <t>Imágenes técnicas, detalladas. Los elementos visuales consisten en fotografías de alta calidad, gráficos comparativos y diagramas técnicos, apoyando la profundidad analítica de cada artículo y reseña especializada.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Multimedia variada. El portal utiliza imágenes de alta calidad, videos y sliders, enriqueciendo significativamente el contenido y la experiencia del usuario.</t>
+          <t>Gráficos inmersivos, atractivos. Se observa un uso extensivo de capturas de pantalla de juegos, tráilers incrustados y fotografías de productos con un estilo pulcro, diseñados para sumergir al lector en la experiencia.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atractivo visual. El sitio destaca con grandes imágenes de juegos y hardware, así como banners promocionales, captando rápidamente la atención.</t>
+          <t>Iconografía clara, limpia. La plataforma incorpora imágenes de producto grandes y nítidas, así como iconos intuitivos y gráficos de soporte que mejoran la comprensión y el atractivo visual general del contenido.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Productos claros. El portal muestra imágenes nítidas de componentes, facilitando la identificación visual aunque sin elementos gráficos adicionales notables.</t>
+          <t>Imágenes producto, sencillas. El portal muestra fotografías de componentes claras y centradas, con buena calidad, pero la presentación general carece de diversidad gráfica o elementos visuales interactivos que enriquezcan la experiencia.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Las imágenes de producto del sitio son nítidas, pero la incorporación de iconos o ilustraciones adicionales podría enriquecer su presentación visual.</t>
+          <t>Diversificar los elementos visuales más allá de las imágenes de producto, incluyendo iconos personalizados, ilustraciones o gráficos informativos que hagan el contenido más dinámico. Mejoraría la estética general.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Navegación y UX</t>
+          <t>Navigation &amp; UX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Menú estructurado. El medio ofrece una navegación compleja pero lógica, permitiendo a los usuarios acceder a categorías y filtros específicos fácilmente.</t>
+          <t>Navegación lógica, eficiente. La estructura de menú es profunda y bien organizada, permitiendo a los usuarios encontrar rápidamente información específica sobre componentes, benchmarks o guías de compra.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ruta intuitiva. El portal presenta una estructura de menú clara y una barra de búsqueda eficiente, facilitando la exploración del vasto contenido.</t>
+          <t>Experiencia fluida, intuitiva. El diseño prioriza una navegación sencilla con categorías claras y una barra de búsqueda prominente, facilitando el descubrimiento de contenido relevante para jugadores entusiastas.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Acceso directo. El sitio utiliza menús desplegables y enlaces destacados, guiando al usuario rápidamente hacia secciones populares y reviews.</t>
+          <t>Flujo de usuario, directo. La organización de la navegación es muy accesible, con menús bien definidos y enlaces internos coherentes que guían al usuario a través de sus diversas secciones temáticas.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barra superior. El portal exhibe una barra de búsqueda central y enlaces de navegación clave en la cabecera, ofreciendo opciones directas.</t>
+          <t xml:space="preserve">Barra superior, clara. La navegación del portal es básica y funcional, con enlaces principales en la parte superior que permiten acceder a secciones clave como </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>La navegación visible del sitio es sencilla, pero menús más extensos o "breadcrumbs" guiarían mejor a los usuarios en búsquedas profundas.</t>
+          <t xml:space="preserve">Expandir las opciones de navegación, quizás con un menú lateral o filtros avanzados para </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organización y estructura</t>
+          <t>Organization &amp; Structure</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contenido ordenado. El medio estructura sus artículos con encabezados, subtítulos y listas, facilitando el escaneo y la asimilación de información.</t>
+          <t>Estructura jerárquica, robusta. El contenido se organiza en categorías lógicas con subsecciones detalladas, facilitando la exploración de temas complejos desde una perspectiva técnica y muy especializada.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Secciones claras. El portal divide su contenido en bloques bien definidos con titulares grandes, mejorando la comprensión y el flujo de lectura.</t>
+          <t>Disposición temática, atractiva. La organización prioriza una mezcla de noticias, reseñas y artículos destacados en la página principal, estructurados para un consumo rápido y visualmente atractivo para la comunidad gamer.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diseño modular. El sitio organiza artículos y noticias en módulos visualmente atractivos, facilitando la exploración de diverso contenido relevante.</t>
+          <t>Diseño modular, adaptable. El portal presenta una estructura de contenido en bloques que se adapta bien a distintos formatos y dispositivos, facilitando el acceso a noticias, análisis y guías de compra de forma ordenada.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Diseño lineal. El portal presenta un diseño simple con un título principal y una sección de productos debajo, mostrando una jerarquía básica.</t>
+          <t>Diseño lineal, predecible. La disposición del contenido es muy sencilla, con una cabecera, un título central y una sección de componentes populares, lo que proporciona una estructura clara aunque limitada en opciones de presentación.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>La organización del sitio es básica, pero una mejor estructura de categorías y filtros en la página optimizaría la exploración de componentes.</t>
+          <t>Implementar una organización más modular o temática para destacar diferentes tipos de contenido, como guías o novedades, ofreciendo así una experiencia de exploración más rica y estructurada al usuario.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Accesibilidad</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diseño inclusivo. El medio mantiene altos contrastes y opciones de tamaño de texto, garantizando la legibilidad para un amplio rango de usuarios.</t>
+          <t>Contrastes adecuados, buena. Los colores y textos están diseñados para ofrecer un buen contraste, facilitando la lectura a usuarios con diversas capacidades visuales y garantizando una experiencia inclusiva general.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estándares seguidos. El portal se adhiere a pautas de accesibilidad, ofreciendo una experiencia cómoda para usuarios con diversas necesidades.</t>
+          <t>Elementos legibles, funcionales. A pesar de su diseño enfocado en la estética de juego, la plataforma mantiene un buen contraste entre texto y fondo, asegurando que el contenido sea accesible para la mayoría de usuarios.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Usabilidad general. El sitio prioriza la claridad del texto y la navegación con teclado, favoreciendo a usuarios con diferentes capacidades.</t>
+          <t>Estándares cumplidos, buena. El portal se adhiere a pautas de accesibilidad web, proporcionando textos claros, navegación por teclado y descripciones alternativas para imágenes, asegurando una experiencia equitativa.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Contraste evidente. El portal presenta buen contraste entre texto y fondo, favoreciendo la legibilidad, aunque otras características no son visibles.</t>
+          <t>Legibilidad simple, básica. El contraste entre el texto y el fondo es generalmente bueno, lo que favorece la legibilidad, pero no se observan características avanzadas de accesibilidad web implementadas.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El contraste del sitio es adecuado, pero explorar descripciones alternativas para imágenes y navegación con teclado sería beneficioso.</t>
+          <t>Añadir atributos ARIA, navegación por teclado mejorada y descripciones de imágenes (alt text) para cumplir con estándares de accesibilidad, permitiendo a usuarios con discapacidades acceder plenamente al contenido del portal.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Funcionalidad</t>
+          <t>Functionality</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Herramientas útiles. El medio ofrece comparadores, filtros avanzados y especificaciones técnicas detalladas, añadiendo valor práctico al usuario.</t>
+          <t>Herramientas robustas, útiles. El portal ofrece comparadores de rendimiento, bases de datos de productos y filtros avanzados, proporcionando a los usuarios herramientas completas para sus investigaciones de hardware.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Recursos completos. El portal incluye guías de compra interactivas, herramientas de búsqueda avanzada y secciones de comentarios, enriqueciendo la experiencia.</t>
+          <t>Características interactivas, diversas. La plataforma incluye foros activos, secciones de comentarios en artículos y un sistema de búsqueda eficiente, facilitando la interacción y el acceso a información relevante.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Características robustas. El sitio permite la búsqueda por juegos o componentes, integrando enlaces a tiendas y secciones de noticias actualizadas.</t>
+          <t>Módulos operativos, completos. El sitio integra un potente buscador, filtros de categorías y un sistema de recomendación de productos, optimizando la experiencia de usuario y la eficiencia de búsqueda.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Búsqueda visible. El portal dispone de una barra de búsqueda y secciones para "Arma tu PC" y "Comparar", sugiriendo funcionalidades clave.</t>
+          <t xml:space="preserve">Funcionalidades clave, presentes. El portal ofrece un buscador básico y las secciones </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Las funcionalidades inferidas del sitio son prometedoras, pero se recomienda ampliar las opciones de filtrado y comparación de productos directamente.</t>
+          <t>Enriquecer las funcionalidades del comparador y del configurador de PC, añadiendo filtros por precio, marca, rendimiento o compatibilidad, para ofrecer una herramienta más potente y personalizada a los usuarios.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Interactividad</t>
+          <t>Interactivity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enganche con el lector. El medio fomenta la participación con secciones de comentarios, foros activos y encuestas relevantes para la comunidad.</t>
+          <t>Comunidad activa, foros. Los usuarios pueden participar en foros de discusión, dejar comentarios en los artículos y personalizar sus feeds, fomentando una comunidad muy participativa y un intercambio de conocimientos.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Compromiso activo. El portal incluye votaciones, valoraciones de usuarios y foros de discusión, creando una comunidad participativa y dinámica.</t>
+          <t>Participación activa, valorada. Se promueve la interacción mediante encuestas, comentarios dinámicos en reseñas y la integración con redes sociales, construyendo una sólida comunidad de jugadores apasionados.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Compromiso lúdico. El sitio ofrece comentarios, reseñas de usuarios y enlaces a comunidades, promoviendo una interacción efectiva entre gamers.</t>
+          <t>Opciones de interacción, variadas. La plataforma permite a los usuarios comentar, compartir contenido en redes sociales y suscribirse a newsletters, fomentando la participación y manteniendo al público conectado con novedades.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Opciones directas. El portal muestra enlaces como "Arma tu PC" y "Comparar", sugiriendo interacción, pero no se observan comentarios ni foros.</t>
+          <t>Interacción limitada, directa. Las opciones interactivas se reducen a la búsqueda y las herramientas de armado/comparación, sin elementos como comentarios, foros o integración con redes sociales para la comunidad.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Las opciones de interacción del sitio son directas, aunque incorporar reseñas de usuarios o un sistema de comentarios enriquecería la experiencia.</t>
+          <t>Introducir elementos de interacción social como comentarios en productos, un sistema de valoraciones o la integración con foros, para construir una comunidad y enriquecer la experiencia del usuario con opiniones.</t>
         </is>
       </c>
     </row>
@@ -724,66 +724,66 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Estrategia robusta. El medio optimiza sus títulos, encabezados y contenido con palabras clave relevantes, atrayendo tráfico orgánico constante.</t>
+          <t>Optimización profunda, efectiva. El portal utiliza palabras clave relevantes, estructura de enlaces internos robusta y meta descripciones precisas, asegurando alta visibilidad en resultados de búsqueda especializados.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Visibilidad alta. El portal utiliza una estructura de URL amigable, metadescripciones claras y contenido actualizado, posicionándose bien en búsquedas.</t>
+          <t>Posicionamiento orgánico, sólido. La publicación implementa buenas prácticas SEO con títulos optimizados, contenido fresco y una fuerte autoridad de dominio, atrayendo tráfico constante desde búsquedas de juegos y hardware.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Contenido clave. El sitio integra títulos optimizados, descripciones ricas y una buena jerarquía de encabezados, favoreciendo su ranking en búsquedas.</t>
+          <t>Cobertura amplia, relevante. El sitio optimiza su contenido para un gran volumen de palabras clave, con una estructura URL clara y contenido actualizado, posicionándose bien para guías de compra y análisis generales.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elementos básicos. El portal exhibe títulos de sección claros y nombres de producto, indicando una base para la optimización on-page.</t>
+          <t>Optimización básica, incipiente. Los títulos de página son descriptivos, pero la plataforma podría beneficiarse de una estrategia más robusta, con metas descripciones detalladas y una mejor estructura de encabezados para SEO.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Los elementos SEO visibles del sitio son adecuados, pero fortalecer la jerarquía de encabezados y el uso estratégico de palabras clave sería clave.</t>
+          <t>Mejorar la estrategia SEO con optimización de palabras clave más profundas, creación de contenido original y mejora de la estructura de enlaces internos, aumentando la visibilidad y el tráfico orgánico del sitio.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rendimiento y velocidad</t>
+          <t>Performance &amp; Speed</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carga eficiente. El medio se optimiza para una velocidad de carga rápida, garantizando una experiencia fluida incluso con contenido multimedia pesado.</t>
+          <t>Carga rápida, optimizada. El portal muestra un excelente rendimiento, con tiempos de carga muy bajos gracias a la optimización de imágenes, minificación de scripts y un robusto CDN, mejorando la experiencia de usuario.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Experiencia ágil. El portal presenta una excelente optimización de imágenes y recursos, resultando en tiempos de carga mínimos y agradables.</t>
+          <t>Rendimiento eficiente, constante. A pesar de los ricos elementos multimedia, el sitio carga rápidamente gracias a la compresión de imágenes y un buen manejo de recursos, proporcionando una navegación fluida al usuario.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rapidez notable. El sitio utiliza técnicas de caché y compresión, asegurando que las páginas carguen velozmente para sus usuarios ávidos.</t>
+          <t>Velocidad sólida, responsive. La plataforma demuestra una carga ágil y es altamente responsiva, adaptándose bien a diferentes dispositivos y garantizando una experiencia fluida sin demoras significativas para el usuario.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Diseño ligero. El portal parece tener una estructura visual sencilla y pocos elementos pesados, sugiriendo una carga potencialmente rápida.</t>
+          <t>Carga aceptable, mejorable. El sitio presenta tiempos de carga razonables, pero existe margen de mejora en la optimización de recursos como imágenes y scripts, lo que impactaría positivamente la experiencia general.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El diseño del sitio parece ligero, pero optimizar la compresión de imágenes y el código podría garantizar tiempos de carga consistentemente rápidos.</t>
+          <t>Optimizar el rendimiento del sitio web reduciendo el tamaño de las imágenes, utilizando caché del navegador y priorizando la carga de contenido visible, para ofrecer una experiencia de usuario más rápida y eficiente.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Conclusión final</t>
+          <t>Final Conclusion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -792,7 +792,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El sitio analizado destaca por su interfaz limpia y navegación directa, facilitando la búsqueda inicial de componentes. Para mejorar, debería priorizar la expansión de filtros de búsqueda, optimizar la legibilidad de descripciones de productos y enriquecer la experiencia interactiva con reseñas de usuarios. Estas acciones potenciarán su utilidad y atractivo para la comunidad de entusiastas de PC.</t>
+          <t>El portal 'Rity' destaca por su enfoque claro en el armado y comparación de PCs, ofreciendo una base funcional muy sólida. Para mejorar, debería enriquecer su diseño visual y tipográfico, expandir las funcionalidades de sus herramientas con filtros avanzados, e integrar elementos interactivos para fomentar una comunidad más activa. Además, una estrategia SEO más robusta y mejoras de rendimiento asegurarían una mayor visibilidad y una experiencia de usuario superior, elevando su posición frente a competidores establecidos.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Rity</t>
+          <t>PCity</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -468,27 +468,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fuentes claras, legibles. El portal utiliza fuentes serif y sans-serif bien balanceadas, asegurando una lectura confortable en artículos extensos y detalles técnicos; la jerarquía visual facilita el escaneo rápido de la información.</t>
+          <t>Estilo profesional. Utiliza fuentes sans-serif claras y tamaños legibles, optimizados para una lectura prolongada de análisis técnicos y guías detalladas.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tipografía dinámica, atractiva. Esta publicación emplea una tipografía moderna con encabezados impactantes, diseñada para captar la atención del lector y complementar el contenido visualmente inmersivo del sector de videojuegos.</t>
+          <t>Diseño dinámico. Emplea una combinación de tipografías atractivas para títulos y un cuerpo de texto nítido que facilita la inmersión en noticias y reseñas de juegos de PC.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lectura fluida, consistente. La plataforma exhibe una tipografía sans-serif limpia y consistente en todo su contenido, promoviendo una experiencia de lectura muy accesible y sin distracciones para el usuario.</t>
+          <t>Apariencia moderna. Predominan tipografías limpias y bien espaciadas, asegurando una experiencia de lectura cómoda en todos sus artículos sobre tecnología y comparativas de hardware.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tipografía sencilla, funcional. El sitio presenta una tipografía básica y estándar, con tamaños adecuados para los títulos y textos de componentes, aunque carece de una diferenciación estilística que enriquezca la experiencia visual general.</t>
+          <t>Fuentes sencillas. La tipografía principal parece ser una sans-serif estándar que ofrece una legibilidad aceptable, aunque sin un estilo distintivo, lo que podría restarle impacto visual.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mejora la legibilidad en ciertos bloques de texto, como descripciones largas, explorando contrastes o espaciados para evitar la monotonía visual. Podría integrar estilos tipográficos más modernos que refuercen la identidad.</t>
+          <t>PCity se beneficiaría de refinar su selección tipográfica, explorando fuentes modernas o variaciones de peso para crear una jerarquía visual más atractiva. Esto enriquecería la experiencia de lectura y le otorgaría un estilo distintivo.</t>
         </is>
       </c>
     </row>
@@ -500,27 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paleta sobria, profesional. La marca emplea una combinación de colores oscuros y neutros, con acentos sutiles, reflejando su enfoque técnico y serio en análisis de hardware y noticias del sector.</t>
+          <t>Identidad sobria. Su paleta de colores tiende a ser funcional, con tonos neutros y acentos para resaltar información clave, reforzando su imagen de autoridad técnica.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colores vibrantes, enérgicos. La identidad visual de esta publicación se define por tonos intensos, especialmente rojos y negros, que evocan la emoción y el dinamismo inherentes al mundo del gaming en PC.</t>
+          <t>Marca vibrante. Combina colores oscuros con acentos brillantes, creando una estética que resuena con la cultura gamer y sus expectativas de contenido emocionante y visualmente atractivo.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Identidad fresca, moderna. El sitio utiliza una paleta de colores claros y acentos brillantes, proyectando una imagen de innovación y accesibilidad, adecuada para un público tecnológico amplio y diverso.</t>
+          <t>Esquema corporativo. Exhibe una paleta de colores equilibrada, a menudo con azules o verdes que transmiten confianza y modernidad, alineándose con su cobertura tecnológica.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esquema básico, funcional. El diseño del portal se centra en un azul brillante para la cabecera y el blanco del fondo, lo que lo hace funcional pero no posee una paleta de colores distintiva o branding fuerte.</t>
+          <t>Esquema simple. El uso prominente de azul brillante en la cabecera con blanco para el contenido es funcional, pero carece de matices o un diseño de marca que lo distinga claramente.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Considerar una paleta de colores más variada y atractiva, quizás con tonos complementarios, para mejorar la estética y reforzar una identidad de marca más memorable. Podría usar el color para jerarquizar información.</t>
+          <t>Es crucial que PCity desarrolle una paleta de colores más sofisticada y un diseño de logo que transmita una identidad de marca única. Dejar atrás la apariencia genérica le permitirá destacar en el mercado.</t>
         </is>
       </c>
     </row>
@@ -532,27 +532,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Imágenes técnicas, detalladas. Los elementos visuales consisten en fotografías de alta calidad, gráficos comparativos y diagramas técnicos, apoyando la profundidad analítica de cada artículo y reseña especializada.</t>
+          <t>Imágenes técnicas. Presenta fotografías de alta calidad de componentes, gráficos detallados y capturas de pantalla que apoyan exhaustivamente sus análisis y comparativas.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gráficos inmersivos, atractivos. Se observa un uso extensivo de capturas de pantalla de juegos, tráilers incrustados y fotografías de productos con un estilo pulcro, diseñados para sumergir al lector en la experiencia.</t>
+          <t>Gráficos inmersivos. Incorpora abundantes imágenes de juegos, tráilers y videos que capturan la esencia del gaming, complementando sus reseñas y noticias de manera efectiva.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iconografía clara, limpia. La plataforma incorpora imágenes de producto grandes y nítidas, así como iconos intuitivos y gráficos de soporte que mejoran la comprensión y el atractivo visual general del contenido.</t>
+          <t>Contenido multimedia. Utiliza un buen equilibrio de imágenes de productos, infografías y videos explicativos que enriquecen la comprensión de sus guías y análisis tecnológicos.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Imágenes producto, sencillas. El portal muestra fotografías de componentes claras y centradas, con buena calidad, pero la presentación general carece de diversidad gráfica o elementos visuales interactivos que enriquezcan la experiencia.</t>
+          <t>Componentes populares. Muestra imágenes cuadradas de productos sin un fondo coherente o estilo unificado, lo que las hace parecer básicas y no contribuye a una estética profesional.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diversificar los elementos visuales más allá de las imágenes de producto, incluyendo iconos personalizados, ilustraciones o gráficos informativos que hagan el contenido más dinámico. Mejoraría la estética general.</t>
+          <t>PCity podría estandarizar el estilo de sus imágenes de productos, quizás con fondos neutros o recortes uniformes. Integrar más elementos gráficos de apoyo visual a la información mejoraría la estética profesional.</t>
         </is>
       </c>
     </row>
@@ -564,27 +564,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navegación lógica, eficiente. La estructura de menú es profunda y bien organizada, permitiendo a los usuarios encontrar rápidamente información específica sobre componentes, benchmarks o guías de compra.</t>
+          <t>Navegación profunda. Ofrece menús extensos y bien categorizados que permiten a los usuarios acceder rápidamente a diversas secciones, desde noticias hasta guías de compra especializadas.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Experiencia fluida, intuitiva. El diseño prioriza una navegación sencilla con categorías claras y una barra de búsqueda prominente, facilitando el descubrimiento de contenido relevante para jugadores entusiastas.</t>
+          <t>Ruta clara. Su navegación es intuitiva, diseñada para que los aficionados a los videojuegos encuentren fácilmente noticias, reseñas y recursos específicos del ámbito gaming.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Flujo de usuario, directo. La organización de la navegación es muy accesible, con menús bien definidos y enlaces internos coherentes que guían al usuario a través de sus diversas secciones temáticas.</t>
+          <t>Interfaz amigable. Proporciona una experiencia de usuario fluida con menús claros y una estructura lógica, facilitando la exploración de sus amplias categorías de productos tecnológicos.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barra superior, clara. La navegación del portal es básica y funcional, con enlaces principales en la parte superior que permiten acceder a secciones clave como </t>
+          <t>Barra superior limitada. La navegación superior incluye 'Información', 'Arma tu PC' y 'Comparar', lo cual es funcional, pero carece de la profundidad necesaria para una experiencia completa.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Expandir las opciones de navegación, quizás con un menú lateral o filtros avanzados para </t>
+          <t>PCity debería expandir las opciones de navegación con menús desplegables y filtros, mejorando la usabilidad para que los usuarios encuentren componentes o información específica con mayor facilidad.</t>
         </is>
       </c>
     </row>
@@ -596,27 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Estructura jerárquica, robusta. El contenido se organiza en categorías lógicas con subsecciones detalladas, facilitando la exploración de temas complejos desde una perspectiva técnica y muy especializada.</t>
+          <t>Estructura modular. Presenta contenido en bloques bien definidos, con secciones dedicadas a noticias, reseñas, guías de compra y foros, facilitando la búsqueda de información técnica.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Disposición temática, atractiva. La organización prioriza una mezcla de noticias, reseñas y artículos destacados en la página principal, estructurados para un consumo rápido y visualmente atractivo para la comunidad gamer.</t>
+          <t>Maquetación temática. Organiza su contenido por géneros de juegos, noticias recientes y reseñas destacadas, creando un flujo lógico que satisface los intereses de su audiencia gamer.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diseño modular, adaptable. El portal presenta una estructura de contenido en bloques que se adapta bien a distintos formatos y dispositivos, facilitando el acceso a noticias, análisis y guías de compra de forma ordenada.</t>
+          <t>Diseño por categorías. Estructura el sitio con secciones claras para diferentes tipos de tecnología y productos, permitiendo una exploración metódica de su vasto repositorio de información.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Diseño lineal, predecible. La disposición del contenido es muy sencilla, con una cabecera, un título central y una sección de componentes populares, lo que proporciona una estructura clara aunque limitada en opciones de presentación.</t>
+          <t>Disposición simple. El contenido se muestra en una columna central con un encabezado principal y una cuadrícula de productos, lo que resulta en una organización básica y un tanto monótona.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Implementar una organización más modular o temática para destacar diferentes tipos de contenido, como guías o novedades, ofreciendo así una experiencia de exploración más rica y estructurada al usuario.</t>
+          <t>PCity se beneficiaría de una estructura de página más dinámica, utilizando columnas, secciones de contenido destacado y una jerarquía visual que guíe al usuario a través de la información relevante.</t>
         </is>
       </c>
     </row>
@@ -628,27 +628,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Contrastes adecuados, buena. Los colores y textos están diseñados para ofrecer un buen contraste, facilitando la lectura a usuarios con diversas capacidades visuales y garantizando una experiencia inclusiva general.</t>
+          <t>Cumplimiento técnico. Generalmente sigue buenas prácticas de accesibilidad web, asegurando que el contenido sea accesible para una audiencia diversa, incluyendo usuarios con discapacidades.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Elementos legibles, funcionales. A pesar de su diseño enfocado en la estética de juego, la plataforma mantiene un buen contraste entre texto y fondo, asegurando que el contenido sea accesible para la mayoría de usuarios.</t>
+          <t>Diseño inclusivo. Busca optimizar la experiencia para todos los usuarios, prestando atención al contraste de colores y la navegación por teclado, mejorando la usabilidad general.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estándares cumplidos, buena. El portal se adhiere a pautas de accesibilidad web, proporcionando textos claros, navegación por teclado y descripciones alternativas para imágenes, asegurando una experiencia equitativa.</t>
+          <t>Funcionalidad estándar. Implementa características de accesibilidad esenciales como texto alternativo y estructura semántica, facilitando la interacción con herramientas de asistencia.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Legibilidad simple, básica. El contraste entre el texto y el fondo es generalmente bueno, lo que favorece la legibilidad, pero no se observan características avanzadas de accesibilidad web implementadas.</t>
+          <t>Potencial de mejora. Aunque el contraste de colores es adecuado, la ausencia de indicadores visuales o personalización sugiere oportunidades para una mayor inclusividad.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Añadir atributos ARIA, navegación por teclado mejorada y descripciones de imágenes (alt text) para cumplir con estándares de accesibilidad, permitiendo a usuarios con discapacidades acceder plenamente al contenido del portal.</t>
+          <t>PCity necesita incorporar descripciones alternativas para imágenes y asegurar la navegación por teclado en todos los elementos interactivos. Ofrecer opciones de tamaño de texto también mejoraría significativamente la inclusividad.</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Herramientas robustas, útiles. El portal ofrece comparadores de rendimiento, bases de datos de productos y filtros avanzados, proporcionando a los usuarios herramientas completas para sus investigaciones de hardware.</t>
+          <t>Herramientas robustas. Ofrece comparadores de productos, benchmarks interactivos y filtros avanzados, proporcionando una funcionalidad completa para el análisis de hardware.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Características interactivas, diversas. La plataforma incluye foros activos, secciones de comentarios en artículos y un sistema de búsqueda eficiente, facilitando la interacción y el acceso a información relevante.</t>
+          <t>Características interactivas. Incluye filtros de búsqueda de juegos, secciones de comentarios activas y enlaces a tiendas, mejorando la experiencia del usuario y su interacción con el contenido.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Módulos operativos, completos. El sitio integra un potente buscador, filtros de categorías y un sistema de recomendación de productos, optimizando la experiencia de usuario y la eficiencia de búsqueda.</t>
+          <t>Utilidades prácticas. Provee buscadores eficientes, opciones de suscripción y una integración fluida de reseñas y guías de compra, asistiendo al usuario en su proceso de decisión.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funcionalidades clave, presentes. El portal ofrece un buscador básico y las secciones </t>
+          <t>Funciones básicas. La barra de búsqueda y los enlaces de navegación indican funcionalidades clave, pero la imagen no revela la profundidad de sus capacidades, pareciendo aún incipientes.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enriquecer las funcionalidades del comparador y del configurador de PC, añadiendo filtros por precio, marca, rendimiento o compatibilidad, para ofrecer una herramienta más potente y personalizada a los usuarios.</t>
+          <t>PCity requiere expandir sus herramientas con filtros de producto más detallados y un comparador interactivo robusto. Integrar un configurador de PCs guiado ofrecería un valor añadido significativo a los usuarios.</t>
         </is>
       </c>
     </row>
@@ -692,27 +692,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comunidad activa, foros. Los usuarios pueden participar en foros de discusión, dejar comentarios en los artículos y personalizar sus feeds, fomentando una comunidad muy participativa y un intercambio de conocimientos.</t>
+          <t>Compromiso profundo. Permite comentarios, foros de discusión y encuestas, fomentando una comunidad activa y el intercambio de conocimientos entre entusiastas del PC.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Participación activa, valorada. Se promueve la interacción mediante encuestas, comentarios dinámicos en reseñas y la integración con redes sociales, construyendo una sólida comunidad de jugadores apasionados.</t>
+          <t>Comunidad activa. Proporciona secciones de comentarios, integración de redes sociales y contenido generado por usuarios, cultivando una fuerte interacción entre su audiencia gamer.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Opciones de interacción, variadas. La plataforma permite a los usuarios comentar, compartir contenido en redes sociales y suscribirse a newsletters, fomentando la participación y manteniendo al público conectado con novedades.</t>
+          <t>Participación guiada. Ofrece encuestas de satisfacción, comentarios en artículos y un sistema de valoración, animando a los usuarios a expresar sus opiniones y experiencias.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Interacción limitada, directa. Las opciones interactivas se reducen a la búsqueda y las herramientas de armado/comparación, sin elementos como comentarios, foros o integración con redes sociales para la comunidad.</t>
+          <t>Interacción limitada. La imagen no muestra elementos interactivos más allá de la navegación principal y los productos clickeables, lo que sugiere una falta de foros o personalización.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Introducir elementos de interacción social como comentarios en productos, un sistema de valoraciones o la integración con foros, para construir una comunidad y enriquecer la experiencia del usuario con opiniones.</t>
+          <t>Para fomentar el engagement, PCity podría añadir secciones de comentarios en los productos. Implementar un configurador de PCs interactivo y un sistema de votación para componentes aumentaría la participación del usuario.</t>
         </is>
       </c>
     </row>
@@ -724,75 +724,71 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optimización profunda, efectiva. El portal utiliza palabras clave relevantes, estructura de enlaces internos robusta y meta descripciones precisas, asegurando alta visibilidad en resultados de búsqueda especializados.</t>
+          <t>Autoridad establecida. Su antigüedad y contenido técnico de alta calidad le otorgan un fuerte posicionamiento en motores de búsqueda para términos relacionados con hardware y reviews.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Posicionamiento orgánico, sólido. La publicación implementa buenas prácticas SEO con títulos optimizados, contenido fresco y una fuerte autoridad de dominio, atrayendo tráfico constante desde búsquedas de juegos y hardware.</t>
+          <t>Optimización temática. Utiliza palabras clave relevantes para la industria del gaming, estructura de URLs amigable y enlaces internos, logrando una alta visibilidad en búsquedas de juegos y hardware.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cobertura amplia, relevante. El sitio optimiza su contenido para un gran volumen de palabras clave, con una estructura URL clara y contenido actualizado, posicionándose bien para guías de compra y análisis generales.</t>
+          <t>Estrategia integral. Emplea una sólida arquitectura de enlaces, contenido optimizado para palabras clave y una rápida velocidad de carga, asegurando una fuerte presencia en resultados de búsqueda.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Optimización básica, incipiente. Los títulos de página son descriptivos, pero la plataforma podría beneficiarse de una estrategia más robusta, con metas descripciones detalladas y una mejor estructura de encabezados para SEO.</t>
+          <t>Ausencia de evidencia. La información visual no permite inferir su estrategia SEO; sin embargo, necesitaría una optimización cuidadosa de títulos, descripciones y estructura de contenido para competir.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mejorar la estrategia SEO con optimización de palabras clave más profundas, creación de contenido original y mejora de la estructura de enlaces internos, aumentando la visibilidad y el tráfico orgánico del sitio.</t>
+          <t>PCity debe implementar una estrategia SEO robusta que incluya investigación de palabras clave, optimización de metadatos y una estructura de enlaces interna fuerte. Esto es crucial para su visibilidad y para competir eficazmente.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance &amp; Speed</t>
+          <t>Content Freshness</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carga rápida, optimizada. El portal muestra un excelente rendimiento, con tiempos de carga muy bajos gracias a la optimización de imágenes, minificación de scripts y un robusto CDN, mejorando la experiencia de usuario.</t>
+          <t>Contenido actualizado. Publica diariamente noticias, reseñas de hardware recién lanzado y guías actualizadas, manteniendo a su audiencia informada sobre las últimas tendencias.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rendimiento eficiente, constante. A pesar de los ricos elementos multimedia, el sitio carga rápidamente gracias a la compresión de imágenes y un buen manejo de recursos, proporcionando una navegación fluida al usuario.</t>
+          <t>Flujo constante. Ofrece una corriente continua de noticias de juegos, parches, eventos y reseñas de nuevos lanzamientos, manteniendo su contenido pertinente y atractivo para gamers.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Velocidad sólida, responsive. La plataforma demuestra una carga ágil y es altamente responsiva, adaptándose bien a diferentes dispositivos y garantizando una experiencia fluida sin demoras significativas para el usuario.</t>
+          <t>Publicación regular. Actualiza frecuentemente sus artículos con las últimas novedades tecnológicas, cubriendo lanzamientos de productos y tendencias de la industria para mantener la relevancia.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Carga aceptable, mejorable. El sitio presenta tiempos de carga razonables, pero existe margen de mejora en la optimización de recursos como imágenes y scripts, lo que impactaría positivamente la experiencia general.</t>
+          <t>Frecuencia incierta. La imagen no permite determinar la regularidad de las actualizaciones de contenido o la frecuencia de adición de nuevos productos, crucial para la relevancia.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Optimizar el rendimiento del sitio web reduciendo el tamaño de las imágenes, utilizando caché del navegador y priorizando la carga de contenido visible, para ofrecer una experiencia de usuario más rápida y eficiente.</t>
+          <t>PCity debería asegurar una actualización constante de productos y contenido informativo, publicando artículos sobre nuevas tecnologías y lanzamientos. Esto mantendría el interés del usuario y su relevancia en el sector.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Final Conclusion</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El portal 'Rity' destaca por su enfoque claro en el armado y comparación de PCs, ofreciendo una base funcional muy sólida. Para mejorar, debería enriquecer su diseño visual y tipográfico, expandir las funcionalidades de sus herramientas con filtros avanzados, e integrar elementos interactivos para fomentar una comunidad más activa. Además, una estrategia SEO más robusta y mejoras de rendimiento asegurarían una mayor visibilidad y una experiencia de usuario superior, elevando su posición frente a competidores establecidos.</t>
+          <t>PCity muestra una base sólida para la comparación y configuración de PCs. Para maximizar su potencial, debe enriquecer su diseño visual y tipográfico, expandir la profundidad de su navegación y funcionalidades interactivas, e implementar una estrategia SEO y de contenido fresco para atraer y retener usuarios de manera efectiva.</t>
         </is>
       </c>
     </row>

--- a/IA/tablas_generadas/tablita.xlsx
+++ b/IA/tablas_generadas/tablita.xlsx
@@ -436,22 +436,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tom's Hardware</t>
+          <t>(NamePage1)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>PC Gamer</t>
+          <t>(NamePage2)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>TechRadar</t>
+          <t>(NamePage3)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>PCity</t>
+          <t>(NamePage4)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -463,256 +463,256 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Typography &amp; Readability</t>
+          <t>Tipografía y legibilidad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Estilo profesional. Utiliza fuentes sans-serif claras y tamaños legibles, optimizados para una lectura prolongada de análisis técnicos y guías detalladas.</t>
+          <t>El sitio emplea una tipografía sans-serif moderna para títulos y cuerpo. La jerarquía visual se establece mediante tamaños y pesos variados, asegurando una lectura fluida en sus extensos artículos y guías informativas.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diseño dinámico. Emplea una combinación de tipografías atractivas para títulos y un cuerpo de texto nítido que facilita la inmersión en noticias y reseñas de juegos de PC.</t>
+          <t>Este portal utiliza una fuente clara y legible, priorizando el contraste en sus bloques de texto extensos. Los encabezados H1-H3 son distintivos, facilitando el escaneo rápido de las secciones principales del contenido editorial.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Apariencia moderna. Predominan tipografías limpias y bien espaciadas, asegurando una experiencia de lectura cómoda en todos sus artículos sobre tecnología y comparativas de hardware.</t>
+          <t>La plataforma presenta una tipografía estándar con excelente espaciado entre líneas y párrafos. La legibilidad general es alta, permitiendo a los usuarios absorber información técnica detallada sin fatiga visual innecesaria.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fuentes sencillas. La tipografía principal parece ser una sans-serif estándar que ofrece una legibilidad aceptable, aunque sin un estilo distintivo, lo que podría restarle impacto visual.</t>
+          <t>La interfaz usa una tipografía sans-serif que parece ser estándar y limpia. Los títulos principales son grandes y audaces, mientras que los textos de productos tienen un tamaño más pequeño con un contraste adecuado sobre fondo blanco.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PCity se beneficiaría de refinar su selección tipográfica, explorando fuentes modernas o variaciones de peso para crear una jerarquía visual más atractiva. Esto enriquecería la experiencia de lectura y le otorgaría un estilo distintivo.</t>
+          <t>Se sugiere explorar una familia tipográfica más distintiva que complemente la marca. Mantener la buena legibilidad de los títulos, pero revisar los tamaños del texto secundario para optimizar la comodidad visual en dispositivos variados.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Colors &amp; Branding</t>
+          <t>Colores y branding</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Identidad sobria. Su paleta de colores tiende a ser funcional, con tonos neutros y acentos para resaltar información clave, reforzando su imagen de autoridad técnica.</t>
+          <t>La paleta de colores del sitio combina tonos oscuros con acentos brillantes. La consistencia del logo y los elementos de marca se extiende a través de todo el sitio, reforzando su reconocimiento global y propuesta de valor tecnológico.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marca vibrante. Combina colores oscuros con acentos brillantes, creando una estética que resuena con la cultura gamer y sus expectativas de contenido emocionante y visualmente atractivo.</t>
+          <t>Este portal exhibe una paleta de colores vibrantes, a menudo asociada con el gaming y la alta energía. El logo es prominente y se integra bien en un diseño que evoca pasión y dinamismo por el sector.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Esquema corporativo. Exhibe una paleta de colores equilibrada, a menudo con azules o verdes que transmiten confianza y modernidad, alineándose con su cobertura tecnológica.</t>
+          <t>La plataforma utiliza una combinación de azules y grises para transmitir seriedad y profesionalidad. El uso estratégico del logo refuerza la autoridad del medio en el ámbito técnico, proyectando una imagen de fiabilidad constante.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esquema simple. El uso prominente de azul brillante en la cabecera con blanco para el contenido es funcional, pero carece de matices o un diseño de marca que lo distinga claramente.</t>
+          <t>El sitio presenta una cabecera azul brillante que contrasta fuertemente con un fondo blanco principal. El logo, un ratón con texto "Rity", es simple y se percibe como una imagen de marca básica y directa en su diseño general.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Es crucial que PCity desarrolle una paleta de colores más sofisticada y un diseño de logo que transmita una identidad de marca única. Dejar atrás la apariencia genérica le permitirá destacar en el mercado.</t>
+          <t>Considerar una paleta de colores más rica o matizada que el azul primario y el blanco. Desarrollar elementos visuales de marca consistentes que se extiendan más allá del logo para fortalecer la identidad y cohesión.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Visual Elements</t>
+          <t>Elementos visuales</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Imágenes técnicas. Presenta fotografías de alta calidad de componentes, gráficos detallados y capturas de pantalla que apoyan exhaustivamente sus análisis y comparativas.</t>
+          <t>El sitio integra fotografías de alta calidad, gráficos comparativos y videos explicativos. Los banners publicitarios son visibles pero no intrusivos, manteniendo el foco en el contenido editorial relevante y atractivo para el lector.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gráficos inmersivos. Incorpora abundantes imágenes de juegos, tráilers y videos que capturan la esencia del gaming, complementando sus reseñas y noticias de manera efectiva.</t>
+          <t>Este portal destaca por sus imágenes de juego inmersivas y capturas de pantalla de alta resolución en sus artículos. La iconografía es funcional, y las ilustraciones refuerzan la estética gamer, manteniendo la coherencia visual del medio.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Contenido multimedia. Utiliza un buen equilibrio de imágenes de productos, infografías y videos explicativos que enriquecen la comprensión de sus guías y análisis tecnológicos.</t>
+          <t>La plataforma emplea diagramas técnicos, tablas comparativas y fotos detalladas de componentes para ilustrar sus análisis. El diseño minimalista permite que las imágenes técnicas y los gráficos transmitan la información esencial de manera efectiva.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Componentes populares. Muestra imágenes cuadradas de productos sin un fondo coherente o estilo unificado, lo que las hace parecer básicas y no contribuye a una estética profesional.</t>
+          <t>Se observan imágenes de productos en formato de tarjeta, mostrando componentes de PC sobre fondos blancos uniformes. No se aprecian ilustraciones, iconografía diversa ni elementos visuales complejos más allá del logo y las fotografías de productos.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PCity podría estandarizar el estilo de sus imágenes de productos, quizás con fondos neutros o recortes uniformes. Integrar más elementos gráficos de apoyo visual a la información mejoraría la estética profesional.</t>
+          <t>Incorporar elementos visuales como ilustraciones o iconos para enriquecer la experiencia más allá de las fotografías de productos. Potenciar la sección de cabecera con un "hero" visual que capte la atención y comunique claramente el propósito del sitio.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Navigation &amp; UX</t>
+          <t>Navegación y UX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navegación profunda. Ofrece menús extensos y bien categorizados que permiten a los usuarios acceder rápidamente a diversas secciones, desde noticias hasta guías de compra especializadas.</t>
+          <t>El sitio ofrece un menú principal intuitivo con categorías claras y un buscador eficaz. Los breadcrumbs y los filtros avanzados mejoran la capacidad del usuario para explorar el contenido extenso y complejo con facilidad.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ruta clara. Su navegación es intuitiva, diseñada para que los aficionados a los videojuegos encuentren fácilmente noticias, reseñas y recursos específicos del ámbito gaming.</t>
+          <t>Este portal cuenta con una barra de navegación superior bien organizada y un buscador prominente. La estructura de menús facilita el acceso rápido a noticias, reseñas y guías, optimizando la experiencia de usuario general del visitante.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Interfaz amigable. Proporciona una experiencia de usuario fluida con menús claros y una estructura lógica, facilitando la exploración de sus amplias categorías de productos tecnológicos.</t>
+          <t>La plataforma presenta una navegación estructurada con menús desplegables y un robusto sistema de filtrado. La experiencia de usuario se beneficia de una jerarquía lógica que guía eficientemente por su vasto contenido técnico disponible.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barra superior limitada. La navegación superior incluye 'Información', 'Arma tu PC' y 'Comparar', lo cual es funcional, pero carece de la profundidad necesaria para una experiencia completa.</t>
+          <t>La navegación superior es simple con enlaces ("Información", "Arma tu PC", "Comparar") y un buscador visible. No se aprecian breadcrumbs ni opciones de filtrado avanzadas en la vista principal, lo que simplifica la interacción inicial del usuario.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PCity debería expandir las opciones de navegación con menús desplegables y filtros, mejorando la usabilidad para que los usuarios encuentren componentes o información específica con mayor facilidad.</t>
+          <t>Implementar un sistema de breadcrumbs para mejorar la ubicación del usuario dentro del sitio, especialmente en secciones de productos o detalladas. Considerar la inclusión de filtros y categorías más específicas para la exploración eficiente de componentes.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Organization &amp; Structure</t>
+          <t>Organización y estructura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Estructura modular. Presenta contenido en bloques bien definidos, con secciones dedicadas a noticias, reseñas, guías de compra y foros, facilitando la búsqueda de información técnica.</t>
+          <t>El contenido se organiza en un diseño de rejilla flexible, priorizando las noticias y reseñas más recientes. Las secciones están bien delimitadas, facilitando la comprensión y el acceso rápido a la información clave y actual.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maquetación temática. Organiza su contenido por géneros de juegos, noticias recientes y reseñas destacadas, creando un flujo lógico que satisface los intereses de su audiencia gamer.</t>
+          <t>Este portal presenta una disposición de contenido dinámica, con énfasis en grandes bloques de noticias y análisis de juegos. La estructura fomenta la exploración de artículos relacionados, manteniendo el interés continuo del visitante.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diseño por categorías. Estructura el sitio con secciones claras para diferentes tipos de tecnología y productos, permitiendo una exploración metódica de su vasto repositorio de información.</t>
+          <t>La plataforma adopta una disposición clara y estructurada, a menudo en columnas, para presentar sus análisis y guías. La priorización de contenidos se logra mediante encabezados y sumarios concisos en la página principal, orientando al usuario.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Disposición simple. El contenido se muestra en una columna central con un encabezado principal y una cuadrícula de productos, lo que resulta en una organización básica y un tanto monótona.</t>
+          <t>La estructura se observa con una cabecera, un título principal y una sección de "Componentes populares" en formato de rejilla. La disposición parece simple y directa, priorizando la visualización de los productos destacados en la página de inicio.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PCity se beneficiaría de una estructura de página más dinámica, utilizando columnas, secciones de contenido destacado y una jerarquía visual que guíe al usuario a través de la información relevante.</t>
+          <t>Es aconsejable introducir una jerarquía más marcada en la página de inicio, quizás con secciones dedicadas a noticias o guías. Mejorar la priorización de contenidos más allá de los productos populares para ofrecer una visión más completa y estructurada.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Accesibilidad</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cumplimiento técnico. Generalmente sigue buenas prácticas de accesibilidad web, asegurando que el contenido sea accesible para una audiencia diversa, incluyendo usuarios con discapacidades.</t>
+          <t>El sitio suele cumplir con estándares de accesibilidad, ofreciendo buen contraste y navegación por teclado eficiente. Las etiquetas ARIA y el texto alternativo en imágenes son comunes, mejorando la experiencia para todos los usuarios.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diseño inclusivo. Busca optimizar la experiencia para todos los usuarios, prestando atención al contraste de colores y la navegación por teclado, mejorando la usabilidad general.</t>
+          <t>Este portal se esfuerza por la accesibilidad, con un contraste de color generalmente adecuado y foco visible en elementos interactivos. El texto alternativo en imágenes contribuye a una experiencia inclusiva para gamers diversos y con distintas necesidades.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Funcionalidad estándar. Implementa características de accesibilidad esenciales como texto alternativo y estructura semántica, facilitando la interacción con herramientas de asistencia.</t>
+          <t>La plataforma muestra un compromiso con la accesibilidad, utilizando buen contraste y permitiendo la navegación con teclado. El texto alternativo descriptivo en imágenes técnicas es un punto fuerte, ayudando a la comprensión general.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Potencial de mejora. Aunque el contraste de colores es adecuado, la ausencia de indicadores visuales o personalización sugiere oportunidades para una mayor inclusividad.</t>
+          <t>El contraste general del texto sobre fondos claros parece ser adecuado, aunque los enlaces de la cabecera sobre azul podrían ser optimizados. No se aprecia foco visible ni texto alternativo en la imagen, siendo aspectos importantes a revisar.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PCity necesita incorporar descripciones alternativas para imágenes y asegurar la navegación por teclado en todos los elementos interactivos. Ofrecer opciones de tamaño de texto también mejoraría significativamente la inclusividad.</t>
+          <t>Es crucial añadir texto alternativo descriptivo a todas las imágenes de productos y elementos gráficos para usuarios con discapacidad visual. Realizar pruebas de contraste para asegurar la legibilidad de todos los textos, especialmente los enlaces y el placeholder del buscador.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Functionality</t>
+          <t>Funcionalidad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Herramientas robustas. Ofrece comparadores de productos, benchmarks interactivos y filtros avanzados, proporcionando una funcionalidad completa para el análisis de hardware.</t>
+          <t>El buscador avanzado del sitio, los filtros por categoría y los comparadores de productos son robustos y fiables. La estabilidad de sus componentes interactivos garantiza una experiencia fluida y confiable al usuario al explorar.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Características interactivas. Incluye filtros de búsqueda de juegos, secciones de comentarios activas y enlaces a tiendas, mejorando la experiencia del usuario y su interacción con el contenido.</t>
+          <t>Este portal ofrece un buscador eficaz y la posibilidad de filtrar contenidos por tipo o género de juego. La funcionalidad es sólida, permitiendo a los usuarios encontrar rápidamente análisis específicos o noticias relevantes del sector.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Utilidades prácticas. Provee buscadores eficientes, opciones de suscripción y una integración fluida de reseñas y guías de compra, asistiendo al usuario en su proceso de decisión.</t>
+          <t>La plataforma cuenta con herramientas de comparación detalladas y un sistema de búsqueda potente y preciso. La funcionalidad es excelente, proporcionando datos técnicos fiables y herramientas útiles para la toma de decisiones informadas.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Funciones básicas. La barra de búsqueda y los enlaces de navegación indican funcionalidades clave, pero la imagen no revela la profundidad de sus capacidades, pareciendo aún incipientes.</t>
+          <t>Se observa un campo de búsqueda funcional y enlaces para "Arma tu PC" y "Comparar", sugiriendo herramientas subyacentes. La visualización de productos en rejilla implica una funcionalidad básica de catálogo y exploración, aunque no se aprecian filtros en la vista.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PCity requiere expandir sus herramientas con filtros de producto más detallados y un comparador interactivo robusto. Integrar un configurador de PCs guiado ofrecería un valor añadido significativo a los usuarios.</t>
+          <t>Implementar filtros avanzados para la sección de productos, permitiendo a los usuarios refinar búsquedas por marca, tipo de componente o especificaciones. Asegurar que las herramientas "Arma tu PC" y "Comparar" sean intuitivas y robustas, ofreciendo una experiencia completa y útil.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Interactivity</t>
+          <t>Interactividad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Compromiso profundo. Permite comentarios, foros de discusión y encuestas, fomentando una comunidad activa y el intercambio de conocimientos entre entusiastas del PC.</t>
+          <t>El sitio incorpora microinteracciones sutiles en botones y enlaces, proporcionando feedback visual instantáneo. Las animaciones son discretas, mejorando la experiencia sin distraer del contenido esencial y principal del portal.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Comunidad activa. Proporciona secciones de comentarios, integración de redes sociales y contenido generado por usuarios, cultivando una fuerte interacción entre su audiencia gamer.</t>
+          <t>Este portal presenta estados hover y focus bien definidos en sus elementos interactivos, lo cual es muy útil. Las animaciones se utilizan de forma estratégica para enriquecer la interfaz de usuario, especialmente en secciones multimedia o de noticias destacadas.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Participación guiada. Ofrece encuestas de satisfacción, comentarios en artículos y un sistema de valoración, animando a los usuarios a expresar sus opiniones y experiencias.</t>
+          <t>La plataforma ofrece interactividad clara con estados hover para enlaces y botones, mejorando la usabilidad general. Las transiciones son suaves y las microinteracciones son funcionales, apoyando la navegación precisa y eficiente del usuario.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Interacción limitada. La imagen no muestra elementos interactivos más allá de la navegación principal y los productos clickeables, lo que sugiere una falta de foros o personalización.</t>
+          <t>No se pueden observar directamente las microinteracciones ni los estados hover/focus desde la imagen estática. Se esperaría que los enlaces y la barra de búsqueda tuvieran algún tipo de feedback visual al interactuar, como cambios de color o subrayados.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Para fomentar el engagement, PCity podría añadir secciones de comentarios en los productos. Implementar un configurador de PCs interactivo y un sistema de votación para componentes aumentaría la participación del usuario.</t>
+          <t>Implementar estados hover y focus visualmente claros para todos los elementos interactivos, como enlaces de navegación y botones. Introducir microinteracciones sutiles para proporcionar feedback al usuario, mejorando la percepción de reactividad y dinamismo del sitio.</t>
         </is>
       </c>
     </row>
@@ -724,71 +724,75 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Autoridad establecida. Su antigüedad y contenido técnico de alta calidad le otorgan un fuerte posicionamiento en motores de búsqueda para términos relacionados con hardware y reviews.</t>
+          <t>El sitio optimiza sus títulos y meta descripciones, usando encabezados de forma lógica y datos estructurados. La buena arquitectura de enlaces internos y el rendimiento de carga contribuyen a su alta visibilidad en buscadores.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Optimización temática. Utiliza palabras clave relevantes para la industria del gaming, estructura de URLs amigable y enlaces internos, logrando una alta visibilidad en búsquedas de juegos y hardware.</t>
+          <t>Este portal utiliza meta descripciones atractivas y una estructura de encabezados coherente para el SEO. Los datos estructurados para reseñas y noticias, junto con un rápido tiempo de carga, favorecen su posicionamiento en Google.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estrategia integral. Emplea una sólida arquitectura de enlaces, contenido optimizado para palabras clave y una rápida velocidad de carga, asegurando una fuerte presencia en resultados de búsqueda.</t>
+          <t>La plataforma implementa títulos y meta descripciones precisas, con uso adecuado de canonicals y robots.txt. Su rendimiento es sólido, y la organización del contenido con encabezados beneficia directamente su clasificación SEO orgánica.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ausencia de evidencia. La información visual no permite inferir su estrategia SEO; sin embargo, necesitaría una optimización cuidadosa de títulos, descripciones y estructura de contenido para competir.</t>
+          <t>Se observan títulos principales y subtítulos (H1-H2) con texto relevante, lo que es positivo para el SEO. Sin embargo, no se pueden inferir meta descripciones, datos estructurados o un rendimiento de carga desde la captura de pantalla estática.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PCity debe implementar una estrategia SEO robusta que incluya investigación de palabras clave, optimización de metadatos y una estructura de enlaces interna fuerte. Esto es crucial para su visibilidad y para competir eficazmente.</t>
+          <t>Revisar y optimizar los meta títulos y descripciones para cada página, incluyendo palabras clave relevantes del sector. Considerar la implementación de datos estructurados para los productos y las herramientas de comparación, mejorando la visibilidad en resultados enriquecidos.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Content Freshness</t>
+          <t>Coherencia de diseño</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Contenido actualizado. Publica diariamente noticias, reseñas de hardware recién lanzado y guías actualizadas, manteniendo a su audiencia informada sobre las últimas tendencias.</t>
+          <t>El sitio mantiene una coherencia de diseño notable a través de su tipografía, paleta de colores y estilo gráfico general. La uniformidad visual en sus diferentes secciones refuerza la identidad de marca, generando confianza en los usuarios.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Flujo constante. Ofrece una corriente continua de noticias de juegos, parches, eventos y reseñas de nuevos lanzamientos, manteniendo su contenido pertinente y atractivo para gamers.</t>
+          <t>Este portal exhibe una fuerte coherencia de diseño, donde los elementos visuales y el estilo se alinean con su público objetivo. La uniformidad en la presentación de contenido y branding crea una experiencia inmersiva y muy atractiva.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Publicación regular. Actualiza frecuentemente sus artículos con las últimas novedades tecnológicas, cubriendo lanzamientos de productos y tendencias de la industria para mantener la relevancia.</t>
+          <t>La plataforma demuestra una alta coherencia de diseño en su estructura, uso de colores y elementos tipográficos clave. Esta uniformidad contribuye a una experiencia de usuario predecible y profesional a lo largo de todo el sitio.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Frecuencia incierta. La imagen no permite determinar la regularidad de las actualizaciones de contenido o la frecuencia de adición de nuevos productos, crucial para la relevancia.</t>
+          <t>La cabecera, los títulos y las tarjetas de productos muestran una coherencia básica en su estilo visual. La simplicidad del diseño, aunque funcional, carece de elementos unificadores que aporten una estética más elaborada y distintiva al conjunto.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PCity debería asegurar una actualización constante de productos y contenido informativo, publicando artículos sobre nuevas tecnologías y lanzamientos. Esto mantendría el interés del usuario y su relevancia en el sector.</t>
+          <t>Desarrollar una guía de estilos clara para asegurar que todos los componentes visuales futuros mantengan la misma línea estética. Incorporar patrones de diseño consistentes para los elementos interactivos y los módulos de contenido, elevando la profesionalidad.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Conclusión final</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PCity muestra una base sólida para la comparación y configuración de PCs. Para maximizar su potencial, debe enriquecer su diseño visual y tipográfico, expandir la profundidad de su navegación y funcionalidades interactivas, e implementar una estrategia SEO y de contenido fresco para atraer y retener usuarios de manera efectiva.</t>
+          <t>Para Website4, las mejoras prioritarias incluyen enriquecer la paleta de colores y elementos visuales con un "hero" distintivo en la cabecera. Es crucial implementar texto alternativo y asegurar el contraste para la accesibilidad, además de añadir filtros avanzados para productos y robustecer las herramientas de "Arma tu PC" y "Comparar". Finalmente, optimizar el SEO con metadatos estructurados y mejorar la interactividad con estados visuales claros elevará significativamente la experiencia de usuario y la visibilidad del portal.</t>
         </is>
       </c>
     </row>
